--- a/Datas/NPCBehaviorData.xlsx
+++ b/Datas/NPCBehaviorData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
   <si>
     <t>dailyTasks</t>
   </si>
@@ -195,6 +195,23 @@
   <si>
     <t>900,1080132</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>int</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>home</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>gameTimeRanges</t>
+  </si>
+  <si>
+    <t>visitMaps</t>
+  </si>
+  <si>
+    <t>int[]</t>
   </si>
 </sst>
 </file>
@@ -549,157 +566,185 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:N9"/>
+  <dimension ref="A2:Q9"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="3" max="14" width="16.25" customWidth="1"/>
+    <col min="4" max="5" width="16.25" customWidth="1"/>
+    <col min="6" max="7" width="8.875" customWidth="1"/>
+    <col min="8" max="9" width="9.25" customWidth="1"/>
+    <col min="10" max="11" width="10.75" customWidth="1"/>
+    <col min="12" max="12" width="16.25" customWidth="1"/>
+    <col min="13" max="13" width="11.25" customWidth="1"/>
+    <col min="14" max="15" width="16.25" customWidth="1"/>
+    <col min="16" max="17" width="16.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>22</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>7</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>17</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>18</v>
       </c>
       <c r="N2" s="4" t="s">
         <v>18</v>
       </c>
+      <c r="O2" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="P2" t="s">
+        <v>51</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:17" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
         <v>23</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="E3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="L3" s="3" t="s">
+      <c r="M3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="N3" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="O3" s="4" t="s">
         <v>2</v>
       </c>
+      <c r="P3" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>50</v>
+      </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A4" s="2">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C4" s="3">
+        <v>1014</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E4" s="2">
+      <c r="F4" s="2">
         <v>30000</v>
       </c>
-      <c r="F4" s="2">
+      <c r="G4" s="2">
         <v>30001</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="2">
         <v>30002</v>
       </c>
-      <c r="H4" s="2">
+      <c r="I4" s="2">
         <v>30003</v>
       </c>
-      <c r="I4" s="2">
+      <c r="J4" s="2">
         <v>30004</v>
       </c>
-      <c r="J4" s="2">
+      <c r="K4" s="2">
         <v>30005</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="L4" s="3" t="s">
+      <c r="M4" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="N4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="N4" s="4"/>
+      <c r="O4" s="4"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="2">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="C5" s="2">
+        <v>0</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>31</v>
-      </c>
-      <c r="E5" s="2">
-        <v>0</v>
       </c>
       <c r="F5" s="2">
         <v>0</v>
@@ -716,186 +761,201 @@
       <c r="J5" s="2">
         <v>0</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="K5" s="2">
+        <v>0</v>
+      </c>
+      <c r="L5" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="L5" s="3"/>
-      <c r="M5" s="4"/>
+      <c r="M5" s="3"/>
       <c r="N5" s="4"/>
+      <c r="O5" s="4"/>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A6" s="2">
         <v>5</v>
       </c>
       <c r="B6" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="C6" s="1" t="s">
+      <c r="C6" s="5">
+        <v>948</v>
+      </c>
+      <c r="D6" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E6" s="2">
+      <c r="F6" s="2">
         <v>30000</v>
       </c>
-      <c r="F6" s="2">
+      <c r="G6" s="2">
         <v>30001</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="2">
         <v>30002</v>
       </c>
-      <c r="H6" s="2">
+      <c r="I6" s="2">
         <v>30003</v>
       </c>
-      <c r="I6" s="2">
+      <c r="J6" s="2">
         <v>30004</v>
       </c>
-      <c r="J6" s="2">
+      <c r="K6" s="2">
         <v>30005</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="L6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="L6" s="3" t="s">
+      <c r="M6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="M6" s="4" t="s">
+      <c r="N6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="N6" s="4" t="s">
+      <c r="O6" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="2">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="C7" s="5">
+        <v>948</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>30000</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>30001</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>30002</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>30003</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>30004</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>30005</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="L7" s="3" t="s">
+      <c r="M7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="M7" s="4" t="s">
+      <c r="N7" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="N7" s="4" t="s">
+      <c r="O7" s="4" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="2">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="3">
+        <v>900</v>
+      </c>
+      <c r="D8" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E8" s="2">
+      <c r="F8" s="2">
         <v>30000</v>
       </c>
-      <c r="F8" s="2">
+      <c r="G8" s="2">
         <v>30001</v>
       </c>
-      <c r="G8" s="2">
+      <c r="H8" s="2">
         <v>30002</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <v>30003</v>
       </c>
-      <c r="I8" s="2">
+      <c r="J8" s="2">
         <v>30004</v>
       </c>
-      <c r="J8" s="2">
+      <c r="K8" s="2">
         <v>30005</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="L8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="L8" s="3" t="s">
+      <c r="M8" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="M8" s="4" t="s">
+      <c r="N8" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="N8" s="4" t="s">
+      <c r="O8" s="4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="2">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C9" s="3">
+        <v>900</v>
+      </c>
+      <c r="D9" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="2">
+      <c r="F9" s="2">
         <v>30000</v>
       </c>
-      <c r="F9" s="2">
+      <c r="G9" s="2">
         <v>30001</v>
       </c>
-      <c r="G9" s="2">
+      <c r="H9" s="2">
         <v>30002</v>
       </c>
-      <c r="H9" s="2">
+      <c r="I9" s="2">
         <v>30003</v>
       </c>
-      <c r="I9" s="2">
+      <c r="J9" s="2">
         <v>30004</v>
       </c>
-      <c r="J9" s="2">
+      <c r="K9" s="2">
         <v>30005</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="L9" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="L9" s="3" t="s">
+      <c r="M9" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="M9" s="4" t="s">
+      <c r="N9" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="N9" s="4" t="s">
+      <c r="O9" s="4" t="s">
         <v>44</v>
       </c>
     </row>

--- a/Datas/NPCBehaviorData.xlsx
+++ b/Datas/NPCBehaviorData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="52">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
   <si>
     <t>dailyTasks</t>
   </si>
@@ -145,10 +145,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1,2,3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>1014,1089143</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -160,10 +156,6 @@
     <t>布莱兹</t>
   </si>
   <si>
-    <t>1,2,3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>948,1070089</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -212,6 +204,10 @@
   </si>
   <si>
     <t>int[]</t>
+  </si>
+  <si>
+    <t>0,1,2,3</t>
+    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -587,7 +583,7 @@
         <v>20</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>3</v>
@@ -626,10 +622,10 @@
         <v>18</v>
       </c>
       <c r="P2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="Q2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="28.5" x14ac:dyDescent="0.2">
@@ -640,7 +636,7 @@
         <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>8</v>
@@ -679,10 +675,10 @@
         <v>2</v>
       </c>
       <c r="P3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="Q3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
@@ -723,10 +719,10 @@
         <v>24</v>
       </c>
       <c r="M4" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="N4" s="4" t="s">
         <v>33</v>
-      </c>
-      <c r="N4" s="4" t="s">
-        <v>34</v>
       </c>
       <c r="O4" s="4"/>
     </row>
@@ -765,7 +761,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M5" s="3"/>
       <c r="N5" s="4"/>
@@ -806,16 +802,16 @@
         <v>30005</v>
       </c>
       <c r="L6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="N6" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="M6" s="3" t="s">
+      <c r="O6" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="N6" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="O6" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -853,16 +849,16 @@
         <v>30005</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="M7" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="N7" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="O7" s="4" t="s">
         <v>37</v>
-      </c>
-      <c r="N7" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="O7" s="4" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
@@ -900,16 +896,16 @@
         <v>30005</v>
       </c>
       <c r="L8" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="N8" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="O8" s="4" t="s">
         <v>42</v>
-      </c>
-      <c r="M8" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="N8" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="O8" s="4" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
@@ -947,16 +943,16 @@
         <v>30005</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>37</v>
+        <v>50</v>
       </c>
       <c r="N9" s="4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="O9" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/NPCBehaviorData.xlsx
+++ b/Datas/NPCBehaviorData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="133" uniqueCount="108">
   <si>
     <t>dailyTasks</t>
   </si>
@@ -208,6 +208,193 @@
   <si>
     <t>0,1,2,3</t>
     <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+  </si>
+  <si>
+    <t>琼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强尼</t>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+  </si>
+  <si>
+    <t>3115,1164186</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3115,1164186</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2180,1165443</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1167153</t>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+  </si>
+  <si>
+    <t>2180,1167153</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>艾琳娜</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2180,1166370</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+  </si>
+  <si>
+    <t>1112,1090312</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1112,1090881</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希拉</t>
+  </si>
+  <si>
+    <t>夏佐</t>
+  </si>
+  <si>
+    <t>1147517</t>
+  </si>
+  <si>
+    <t>希尔达</t>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+  </si>
+  <si>
+    <t>1153488</t>
+  </si>
+  <si>
+    <t>1153081</t>
+  </si>
+  <si>
+    <t>5013,1154408</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5013,1154408</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1071058</t>
+  </si>
+  <si>
+    <t>1080475</t>
+  </si>
+  <si>
+    <t>莱特</t>
+  </si>
+  <si>
+    <t>布拉德利</t>
+  </si>
+  <si>
+    <t>1756,1019120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布蓝达</t>
+  </si>
+  <si>
+    <t>希贝儿</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>梅林</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1070049</t>
+  </si>
+  <si>
+    <t>1166131</t>
+  </si>
+  <si>
+    <t>1166294</t>
+  </si>
+  <si>
+    <t>1019972</t>
+  </si>
+  <si>
+    <t>1071591</t>
+  </si>
+  <si>
+    <t>帕特里克</t>
+  </si>
+  <si>
+    <t>1139029</t>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+  </si>
+  <si>
+    <t>1042715</t>
+  </si>
+  <si>
+    <t>阿普敦</t>
+  </si>
+  <si>
+    <t>1168177</t>
+  </si>
+  <si>
+    <t>2497,1116139</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>摩尔根</t>
+  </si>
+  <si>
+    <t>1162796</t>
+  </si>
+  <si>
+    <t>1001440</t>
+  </si>
+  <si>
+    <t>马勒第兹</t>
+  </si>
+  <si>
+    <t>考波特</t>
+  </si>
+  <si>
+    <t>1001490</t>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+  </si>
+  <si>
+    <t>1080779</t>
+  </si>
+  <si>
+    <t>1080613</t>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+  </si>
+  <si>
+    <t>1014,1088635</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -265,7 +452,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -282,6 +469,11 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -562,7 +754,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:Q9"/>
+  <dimension ref="A2:Q35"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="5" width="16.25" customWidth="1"/>
@@ -571,7 +763,7 @@
     <col min="10" max="11" width="10.75" customWidth="1"/>
     <col min="12" max="12" width="16.25" customWidth="1"/>
     <col min="13" max="13" width="11.25" customWidth="1"/>
-    <col min="14" max="15" width="16.25" customWidth="1"/>
+    <col min="14" max="15" width="16.25" style="7" customWidth="1"/>
     <col min="16" max="17" width="16.375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -955,6 +1147,412 @@
         <v>42</v>
       </c>
     </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>51</v>
+      </c>
+      <c r="C10">
+        <v>5170</v>
+      </c>
+      <c r="N10" s="7">
+        <v>1156253</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
+        <v>10</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C11">
+        <v>5170</v>
+      </c>
+      <c r="N11" s="7">
+        <v>1156284</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A12">
+        <v>31</v>
+      </c>
+      <c r="B12" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12">
+        <v>5170</v>
+      </c>
+      <c r="N12" s="7">
+        <v>1156900</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13">
+        <v>4800</v>
+      </c>
+      <c r="N13" s="7">
+        <v>1143244</v>
+      </c>
+      <c r="O13" s="7">
+        <v>1144907</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A14">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14">
+        <v>2270</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A15">
+        <v>40</v>
+      </c>
+      <c r="B15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C15">
+        <v>2270</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="A16" s="6">
+        <v>36</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16">
+        <v>2270</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17">
+        <v>1112</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>65</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18">
+        <v>1112</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A19">
+        <v>29</v>
+      </c>
+      <c r="B19" t="s">
+        <v>68</v>
+      </c>
+      <c r="C19">
+        <v>4918</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A20">
+        <v>18</v>
+      </c>
+      <c r="B20" t="s">
+        <v>70</v>
+      </c>
+      <c r="C20">
+        <v>5013</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="O20" s="7" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A21">
+        <v>38</v>
+      </c>
+      <c r="B21" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21">
+        <v>5013</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="O21" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A22">
+        <v>37</v>
+      </c>
+      <c r="B22" t="s">
+        <v>78</v>
+      </c>
+      <c r="C22">
+        <v>1856</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="O22" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A23">
+        <v>19</v>
+      </c>
+      <c r="B23" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23">
+        <v>1856</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="O23" s="7" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A24">
+        <v>21</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24">
+        <v>3300</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
+        <v>22</v>
+      </c>
+      <c r="B25" s="6" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25">
+        <v>3056</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="O25" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
+        <v>25</v>
+      </c>
+      <c r="B26" s="6" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26">
+        <v>3056</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="O26" s="7" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A27">
+        <v>23</v>
+      </c>
+      <c r="B27" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27">
+        <v>2015</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A28">
+        <v>24</v>
+      </c>
+      <c r="B28" t="s">
+        <v>91</v>
+      </c>
+      <c r="C28">
+        <v>4765</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A29">
+        <v>35</v>
+      </c>
+      <c r="B29" t="s">
+        <v>93</v>
+      </c>
+      <c r="C29">
+        <v>4696</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A30">
+        <v>26</v>
+      </c>
+      <c r="B30" t="s">
+        <v>96</v>
+      </c>
+      <c r="C30">
+        <v>2902</v>
+      </c>
+      <c r="N30" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="O30" s="7" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A31">
+        <v>28</v>
+      </c>
+      <c r="B31" t="s">
+        <v>100</v>
+      </c>
+      <c r="C31">
+        <v>5476</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A32">
+        <v>27</v>
+      </c>
+      <c r="B32" t="s">
+        <v>99</v>
+      </c>
+      <c r="C32">
+        <v>5476</v>
+      </c>
+      <c r="N32" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A33">
+        <v>30</v>
+      </c>
+      <c r="B33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C33">
+        <v>5293</v>
+      </c>
+      <c r="N33" s="7" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
+        <v>34</v>
+      </c>
+      <c r="B34" t="s">
+        <v>106</v>
+      </c>
+      <c r="C34">
+        <v>1912</v>
+      </c>
+      <c r="N34" s="7" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A35" s="2">
+        <v>39</v>
+      </c>
+      <c r="B35" t="s">
+        <v>105</v>
+      </c>
+      <c r="C35">
+        <v>1912</v>
+      </c>
+      <c r="N35" s="7" t="s">
+        <v>104</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Datas/NPCBehaviorData.xlsx
+++ b/Datas/NPCBehaviorData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="128">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -297,235 +297,237 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2180,1166370</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002,1004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏佐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希尔达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5013,1154408</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002,1004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1756,1019120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1756,1019120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿普敦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>摩尔根</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考波特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马勒第兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5170,1156253</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5170,1156284</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5170,1156900</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2270,1167153</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2270,1166370</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2270,1167418</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4918,1147517</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5013,1153081</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5013,1153488</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1856,1071058</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1856,1080475</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3300,1070049</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3056,1166131</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3056,1166294</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2015,1071591</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4765,1139029</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4696,1042715</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2902,1168177</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5476,1162796</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5476,1001440</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5293,1001490</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1912,1080779</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1912,1080613</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4800,1144907</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纺织婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5309,1081691</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5309,1159783</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,0,9,0,9,0,17,30,17,30,19,30,19,30, 22,0,22,0,24,0</t>
+  </si>
+  <si>
+    <t>60001,60002,60003,60004,60005</t>
+  </si>
+  <si>
+    <t>6,0,9,0,9,0,17,30,17,30,19,30,19,30, 22,0,22,0,24,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3056,1019972</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>2180,1165443</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2180,1166370</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希拉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1002,1004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>夏佐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希尔达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5013,1154408</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>莱特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1002,1004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1756,1019120</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布拉德利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1756,1019120</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布蓝达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1019972</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1019972</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>朵儿洁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿普敦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>摩尔根</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>考波特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>马勒第兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱格伯特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿尔杰农</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5170,1156253</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5170,1156284</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5170,1156900</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4800.1143244</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2270,1167153</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2270,1166370</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2270,1167418</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4918,1147517</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5013,1153081</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5013,1153488</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1856,1071058</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1856,1080475</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3300,1070049</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3056,1166131</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3056,1166294</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2015,1071591</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4765,1139029</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4696,1042715</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2902,1168177</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5476,1162796</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5476,1001440</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5293,1001490</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1912,1080779</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1912,1080613</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4800,1144907</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>纺织婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5309,1081691</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5309,1159783</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>x</t>
+    <t>4800,1143244</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -868,7 +870,8 @@
     <col min="12" max="12" width="16.25" style="1" customWidth="1"/>
     <col min="13" max="13" width="11.25" style="1" customWidth="1"/>
     <col min="14" max="15" width="16.25" style="2" customWidth="1"/>
-    <col min="16" max="17" width="16.375" style="2" customWidth="1"/>
+    <col min="16" max="16" width="51.125" style="2" customWidth="1"/>
+    <col min="17" max="17" width="47.625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
@@ -1013,13 +1016,19 @@
         <v>30005</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="M4" s="1" t="s">
         <v>39</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>40</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
@@ -1106,6 +1115,12 @@
       <c r="O6" s="2" t="s">
         <v>47</v>
       </c>
+      <c r="P6" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
@@ -1153,6 +1168,12 @@
       <c r="O7" s="2" t="s">
         <v>53</v>
       </c>
+      <c r="P7" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
@@ -1200,6 +1221,12 @@
       <c r="O8" s="2" t="s">
         <v>56</v>
       </c>
+      <c r="P8" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
@@ -1247,6 +1274,12 @@
       <c r="O9" s="2" t="s">
         <v>56</v>
       </c>
+      <c r="P9" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>123</v>
+      </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
@@ -1289,7 +1322,13 @@
         <v>39</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
@@ -1333,10 +1372,16 @@
         <v>60</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
@@ -1380,10 +1425,16 @@
         <v>39</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>10</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
@@ -1427,13 +1478,16 @@
         <v>60</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>100</v>
+        <v>127</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
@@ -1477,10 +1531,16 @@
         <v>39</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>69</v>
+        <v>126</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
@@ -1488,7 +1548,7 @@
         <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C15" s="1">
         <v>2270</v>
@@ -1524,10 +1584,16 @@
         <v>45</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="O15" s="2" t="s">
         <v>11</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
@@ -1571,18 +1637,24 @@
         <v>39</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="17" spans="1:15" x14ac:dyDescent="0.2">
+        <v>70</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C17" s="1">
         <v>1112</v>
@@ -1623,13 +1695,19 @@
       <c r="O17" s="2" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="18" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P17" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q17" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C18" s="1">
         <v>1112</v>
@@ -1638,7 +1716,7 @@
         <v>41</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F18" s="1">
         <v>30000</v>
@@ -1667,13 +1745,19 @@
       <c r="N18" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="19" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P18" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q18" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C19" s="1">
         <v>4918</v>
@@ -1709,15 +1793,21 @@
         <v>45</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="20" spans="1:15" x14ac:dyDescent="0.2">
+        <v>100</v>
+      </c>
+      <c r="P19" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q19" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C20" s="1">
         <v>5013</v>
@@ -1753,18 +1843,24 @@
         <v>39</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="21" spans="1:15" x14ac:dyDescent="0.2">
+        <v>76</v>
+      </c>
+      <c r="P20" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q20" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>38</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C21" s="1">
         <v>5013</v>
@@ -1800,18 +1896,24 @@
         <v>39</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="O21" s="2" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="22" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P21" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q21" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>37</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="C22" s="1">
         <v>1856</v>
@@ -1820,45 +1922,51 @@
         <v>7</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G22" s="1">
+        <v>30001</v>
+      </c>
+      <c r="H22" s="1">
+        <v>30002</v>
+      </c>
+      <c r="I22" s="1">
+        <v>30003</v>
+      </c>
+      <c r="J22" s="1">
+        <v>30004</v>
+      </c>
+      <c r="K22" s="1">
+        <v>30005</v>
+      </c>
+      <c r="L22" s="1" t="s">
         <v>80</v>
-      </c>
-      <c r="F22" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G22" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H22" s="1">
-        <v>30002</v>
-      </c>
-      <c r="I22" s="1">
-        <v>30003</v>
-      </c>
-      <c r="J22" s="1">
-        <v>30004</v>
-      </c>
-      <c r="K22" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L22" s="1" t="s">
-        <v>81</v>
       </c>
       <c r="M22" s="1" t="s">
         <v>51</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="O22" s="2" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="23" spans="1:15" x14ac:dyDescent="0.2">
+        <v>81</v>
+      </c>
+      <c r="P22" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q22" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>19</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C23" s="1">
         <v>1856</v>
@@ -1894,18 +2002,24 @@
         <v>39</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="24" spans="1:15" x14ac:dyDescent="0.2">
+        <v>83</v>
+      </c>
+      <c r="P23" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q23" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C24" s="1">
         <v>3300</v>
@@ -1941,10 +2055,16 @@
         <v>60</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="25" spans="1:15" x14ac:dyDescent="0.2">
+        <v>105</v>
+      </c>
+      <c r="P24" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q24" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -1985,13 +2105,19 @@
         <v>39</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="26" spans="1:15" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+      <c r="P25" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q25" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -2032,18 +2158,21 @@
         <v>45</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="27" spans="1:15" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+      <c r="P26" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q26" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>23</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C27" s="1">
         <v>2015</v>
@@ -2079,15 +2208,21 @@
         <v>39</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="28" spans="1:15" x14ac:dyDescent="0.2">
+        <v>108</v>
+      </c>
+      <c r="P27" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q27" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>24</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="C28" s="1">
         <v>4765</v>
@@ -2123,15 +2258,21 @@
         <v>39</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="29" spans="1:15" x14ac:dyDescent="0.2">
+        <v>109</v>
+      </c>
+      <c r="P28" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q28" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="C29" s="1">
         <v>4696</v>
@@ -2140,7 +2281,7 @@
         <v>7</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F29" s="1">
         <v>30000</v>
@@ -2167,15 +2308,21 @@
         <v>39</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="30" spans="1:15" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+      <c r="P29" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q29" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>26</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C30" s="1">
         <v>2902</v>
@@ -2211,18 +2358,24 @@
         <v>39</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="31" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="P30" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q30" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="C31" s="1">
         <v>5476</v>
@@ -2258,15 +2411,21 @@
         <v>60</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="32" spans="1:15" x14ac:dyDescent="0.2">
+        <v>112</v>
+      </c>
+      <c r="P31" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q31" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>27</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C32" s="1">
         <v>5476</v>
@@ -2302,15 +2461,21 @@
         <v>39</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="33" spans="1:15" x14ac:dyDescent="0.2">
+        <v>113</v>
+      </c>
+      <c r="P32" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q32" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C33" s="1">
         <v>5293</v>
@@ -2346,15 +2511,21 @@
         <v>39</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="34" spans="1:15" x14ac:dyDescent="0.2">
+        <v>114</v>
+      </c>
+      <c r="P33" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q33" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="C34" s="1">
         <v>1912</v>
@@ -2384,21 +2555,27 @@
         <v>30005</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M34" s="1" t="s">
         <v>39</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="35" spans="1:15" x14ac:dyDescent="0.2">
+        <v>115</v>
+      </c>
+      <c r="P34" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q34" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>39</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="C35" s="1">
         <v>1912</v>
@@ -2434,15 +2611,21 @@
         <v>39</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="36" spans="1:15" x14ac:dyDescent="0.2">
+        <v>116</v>
+      </c>
+      <c r="P35" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q35" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>41</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C36" s="1">
         <v>5309</v>
@@ -2478,10 +2661,16 @@
         <v>39</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="O36" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
+      </c>
+      <c r="P36" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="Q36" s="2" t="s">
+        <v>123</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/NPCBehaviorData.xlsx
+++ b/Datas/NPCBehaviorData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="129">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -528,6 +528,10 @@
   </si>
   <si>
     <t>4800,1143244</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,11,12,3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -870,7 +874,7 @@
     <col min="12" max="12" width="16.25" style="1" customWidth="1"/>
     <col min="13" max="13" width="11.25" style="1" customWidth="1"/>
     <col min="14" max="15" width="16.25" style="2" customWidth="1"/>
-    <col min="16" max="16" width="51.125" style="2" customWidth="1"/>
+    <col min="16" max="16" width="51.125" style="2" hidden="1" customWidth="1"/>
     <col min="17" max="17" width="47.625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="9" style="1"/>
   </cols>
@@ -1019,7 +1023,7 @@
         <v>118</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="N4" s="2" t="s">
         <v>40</v>
@@ -1319,7 +1323,7 @@
         <v>42</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>94</v>
@@ -1740,7 +1744,7 @@
         <v>38</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>14</v>
@@ -1790,7 +1794,7 @@
         <v>42</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>45</v>
+        <v>128</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>100</v>
@@ -2052,7 +2056,7 @@
         <v>42</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="N24" s="2" t="s">
         <v>105</v>
@@ -2155,7 +2159,7 @@
         <v>42</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>45</v>
+        <v>128</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>107</v>
@@ -2205,7 +2209,7 @@
         <v>42</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="N27" s="2" t="s">
         <v>108</v>
@@ -2255,7 +2259,7 @@
         <v>42</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>109</v>
@@ -2305,7 +2309,7 @@
         <v>68</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>110</v>
@@ -2408,7 +2412,7 @@
         <v>42</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>60</v>
+        <v>128</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>112</v>
@@ -2458,7 +2462,7 @@
         <v>42</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="N32" s="2" t="s">
         <v>113</v>
@@ -2508,7 +2512,7 @@
         <v>42</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>114</v>
@@ -2558,7 +2562,7 @@
         <v>80</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="N34" s="2" t="s">
         <v>115</v>
@@ -2608,7 +2612,7 @@
         <v>42</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>39</v>
+        <v>128</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>116</v>

--- a/Datas/NPCBehaviorData.xlsx
+++ b/Datas/NPCBehaviorData.xlsx
@@ -874,7 +874,7 @@
     <col min="12" max="12" width="16.25" style="1" customWidth="1"/>
     <col min="13" max="13" width="11.25" style="1" customWidth="1"/>
     <col min="14" max="15" width="16.25" style="2" customWidth="1"/>
-    <col min="16" max="16" width="51.125" style="2" hidden="1" customWidth="1"/>
+    <col min="16" max="16" width="42.875" style="2" customWidth="1"/>
     <col min="17" max="17" width="47.625" style="2" customWidth="1"/>
     <col min="18" max="16384" width="9" style="1"/>
   </cols>

--- a/Datas/NPCBehaviorData.xlsx
+++ b/Datas/NPCBehaviorData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="128">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -62,10 +62,6 @@
   </si>
   <si>
     <t>3115,1164186</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2180,1167153</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -884,19 +880,19 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>0</v>
@@ -914,36 +910,36 @@
         <v>0</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="M2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="M2" s="1" t="s">
-        <v>21</v>
-      </c>
       <c r="N2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="O2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>25</v>
-      </c>
       <c r="Q2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>26</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>27</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>1</v>
@@ -961,28 +957,28 @@
         <v>5</v>
       </c>
       <c r="J3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="P3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.2">
@@ -990,7 +986,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="C4" s="1">
         <v>1014</v>
@@ -1020,19 +1016,19 @@
         <v>30005</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="M4" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="P4" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.2">
@@ -1046,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>8</v>
@@ -1070,7 +1066,7 @@
         <v>0</v>
       </c>
       <c r="L5" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.2">
@@ -1078,7 +1074,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C6" s="1">
         <v>948</v>
@@ -1087,43 +1083,43 @@
         <v>7</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F6" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G6" s="1">
+        <v>30001</v>
+      </c>
+      <c r="H6" s="1">
+        <v>30002</v>
+      </c>
+      <c r="I6" s="1">
+        <v>30003</v>
+      </c>
+      <c r="J6" s="1">
+        <v>30004</v>
+      </c>
+      <c r="K6" s="1">
+        <v>30005</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="F6" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G6" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H6" s="1">
-        <v>30002</v>
-      </c>
-      <c r="I6" s="1">
-        <v>30003</v>
-      </c>
-      <c r="J6" s="1">
-        <v>30004</v>
-      </c>
-      <c r="K6" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M6" s="1" t="s">
+      <c r="N6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="O6" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="P6" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.2">
@@ -1131,52 +1127,52 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C7" s="1">
         <v>948</v>
       </c>
       <c r="D7" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="F7" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G7" s="1">
+        <v>30001</v>
+      </c>
+      <c r="H7" s="1">
+        <v>30002</v>
+      </c>
+      <c r="I7" s="1">
+        <v>30003</v>
+      </c>
+      <c r="J7" s="1">
+        <v>30004</v>
+      </c>
+      <c r="K7" s="1">
+        <v>30005</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="M7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="F7" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G7" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H7" s="1">
-        <v>30002</v>
-      </c>
-      <c r="I7" s="1">
-        <v>30003</v>
-      </c>
-      <c r="J7" s="1">
-        <v>30004</v>
-      </c>
-      <c r="K7" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="M7" s="1" t="s">
+      <c r="N7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="O7" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="P7" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.2">
@@ -1184,13 +1180,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C8" s="1">
         <v>900</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E8" s="1" t="s">
         <v>8</v>
@@ -1214,22 +1210,22 @@
         <v>30005</v>
       </c>
       <c r="L8" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M8" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="O8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="O8" s="2" t="s">
-        <v>56</v>
-      </c>
       <c r="P8" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q8" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.2">
@@ -1237,13 +1233,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C9" s="1">
         <v>900</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>8</v>
@@ -1267,22 +1263,22 @@
         <v>30005</v>
       </c>
       <c r="L9" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="N9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="N9" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="O9" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="P9" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q9" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.2">
@@ -1290,7 +1286,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C10" s="1">
         <v>5170</v>
@@ -1299,7 +1295,7 @@
         <v>7</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F10" s="1">
         <v>30000</v>
@@ -1320,19 +1316,19 @@
         <v>30005</v>
       </c>
       <c r="L10" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M10" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N10" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="P10" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q10" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.2">
@@ -1340,7 +1336,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C11" s="1">
         <v>5170</v>
@@ -1370,22 +1366,22 @@
         <v>30005</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M11" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="P11" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q11" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.2">
@@ -1393,13 +1389,13 @@
         <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C12" s="1">
         <v>5170</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>8</v>
@@ -1423,22 +1419,22 @@
         <v>30005</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M12" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="O12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="P12" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q12" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.2">
@@ -1446,7 +1442,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C13" s="1">
         <v>4800</v>
@@ -1476,22 +1472,22 @@
         <v>30005</v>
       </c>
       <c r="L13" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M13" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="O13" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="P13" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q13" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.2">
@@ -1499,7 +1495,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C14" s="1">
         <v>2270</v>
@@ -1508,7 +1504,7 @@
         <v>7</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F14" s="1">
         <v>30000</v>
@@ -1529,22 +1525,22 @@
         <v>30005</v>
       </c>
       <c r="L14" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="O14" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="P14" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q14" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.2">
@@ -1552,7 +1548,7 @@
         <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C15" s="1">
         <v>2270</v>
@@ -1582,22 +1578,22 @@
         <v>30005</v>
       </c>
       <c r="L15" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M15" s="1" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>11</v>
+        <v>125</v>
       </c>
       <c r="P15" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q15" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.2">
@@ -1605,7 +1601,7 @@
         <v>36</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C16" s="1">
         <v>2270</v>
@@ -1635,22 +1631,22 @@
         <v>30005</v>
       </c>
       <c r="L16" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M16" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="O16" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="P16" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q16" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.2">
@@ -1658,7 +1654,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C17" s="1">
         <v>1112</v>
@@ -1688,22 +1684,22 @@
         <v>30005</v>
       </c>
       <c r="L17" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M17" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O17" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="P17" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q17" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.2">
@@ -1711,16 +1707,16 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C18" s="1">
         <v>1112</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F18" s="1">
         <v>30000</v>
@@ -1741,19 +1737,19 @@
         <v>30005</v>
       </c>
       <c r="L18" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M18" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="P18" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q18" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.2">
@@ -1761,7 +1757,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C19" s="1">
         <v>4918</v>
@@ -1791,19 +1787,19 @@
         <v>30005</v>
       </c>
       <c r="L19" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M19" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P19" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q19" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.2">
@@ -1811,7 +1807,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C20" s="1">
         <v>5013</v>
@@ -1841,22 +1837,22 @@
         <v>30005</v>
       </c>
       <c r="L20" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M20" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="P20" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q20" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.2">
@@ -1864,16 +1860,16 @@
         <v>38</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C21" s="1">
         <v>5013</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F21" s="1">
         <v>30000</v>
@@ -1894,22 +1890,22 @@
         <v>30005</v>
       </c>
       <c r="L21" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="M21" s="1" t="s">
-        <v>39</v>
-      </c>
       <c r="N21" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="P21" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q21" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.2">
@@ -1917,7 +1913,7 @@
         <v>37</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C22" s="1">
         <v>1856</v>
@@ -1926,43 +1922,43 @@
         <v>7</v>
       </c>
       <c r="E22" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" s="1">
+        <v>30000</v>
+      </c>
+      <c r="G22" s="1">
+        <v>30001</v>
+      </c>
+      <c r="H22" s="1">
+        <v>30002</v>
+      </c>
+      <c r="I22" s="1">
+        <v>30003</v>
+      </c>
+      <c r="J22" s="1">
+        <v>30004</v>
+      </c>
+      <c r="K22" s="1">
+        <v>30005</v>
+      </c>
+      <c r="L22" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="F22" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G22" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H22" s="1">
-        <v>30002</v>
-      </c>
-      <c r="I22" s="1">
-        <v>30003</v>
-      </c>
-      <c r="J22" s="1">
-        <v>30004</v>
-      </c>
-      <c r="K22" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L22" s="1" t="s">
+      <c r="M22" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="N22" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="O22" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="M22" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="N22" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="O22" s="2" t="s">
-        <v>81</v>
-      </c>
       <c r="P22" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q22" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.2">
@@ -1970,7 +1966,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C23" s="1">
         <v>1856</v>
@@ -1979,7 +1975,7 @@
         <v>7</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F23" s="1">
         <v>30000</v>
@@ -2000,22 +1996,22 @@
         <v>30005</v>
       </c>
       <c r="L23" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M23" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="O23" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P23" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q23" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.2">
@@ -2023,7 +2019,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C24" s="1">
         <v>3300</v>
@@ -2053,19 +2049,19 @@
         <v>30005</v>
       </c>
       <c r="L24" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M24" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="P24" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q24" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.2">
@@ -2073,7 +2069,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C25" s="1">
         <v>3056</v>
@@ -2103,22 +2099,22 @@
         <v>30005</v>
       </c>
       <c r="L25" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M25" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N25" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="O25" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="P25" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q25" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.2">
@@ -2126,7 +2122,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C26" s="1">
         <v>3056</v>
@@ -2156,19 +2152,19 @@
         <v>30005</v>
       </c>
       <c r="L26" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M26" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="P26" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q26" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.2">
@@ -2176,13 +2172,13 @@
         <v>23</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C27" s="1">
         <v>2015</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>8</v>
@@ -2206,19 +2202,19 @@
         <v>30005</v>
       </c>
       <c r="L27" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M27" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="P27" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q27" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.2">
@@ -2226,13 +2222,13 @@
         <v>24</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C28" s="1">
         <v>4765</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>8</v>
@@ -2256,19 +2252,19 @@
         <v>30005</v>
       </c>
       <c r="L28" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M28" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="P28" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q28" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.2">
@@ -2276,7 +2272,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C29" s="1">
         <v>4696</v>
@@ -2285,7 +2281,7 @@
         <v>7</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F29" s="1">
         <v>30000</v>
@@ -2306,19 +2302,19 @@
         <v>30005</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="M29" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="P29" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q29" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
@@ -2326,7 +2322,7 @@
         <v>26</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C30" s="1">
         <v>2902</v>
@@ -2356,22 +2352,22 @@
         <v>30005</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M30" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="O30" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="P30" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q30" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
@@ -2379,7 +2375,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C31" s="1">
         <v>5476</v>
@@ -2388,7 +2384,7 @@
         <v>7</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="F31" s="1">
         <v>30000</v>
@@ -2409,19 +2405,19 @@
         <v>30005</v>
       </c>
       <c r="L31" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M31" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="P31" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q31" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.2">
@@ -2429,13 +2425,13 @@
         <v>27</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C32" s="1">
         <v>5476</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E32" s="1" t="s">
         <v>8</v>
@@ -2459,19 +2455,19 @@
         <v>30005</v>
       </c>
       <c r="L32" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M32" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="P32" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q32" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.2">
@@ -2479,7 +2475,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C33" s="1">
         <v>5293</v>
@@ -2509,19 +2505,19 @@
         <v>30005</v>
       </c>
       <c r="L33" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M33" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="P33" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q33" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.2">
@@ -2529,7 +2525,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C34" s="1">
         <v>1912</v>
@@ -2559,19 +2555,19 @@
         <v>30005</v>
       </c>
       <c r="L34" s="1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M34" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="P34" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q34" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.2">
@@ -2579,7 +2575,7 @@
         <v>39</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C35" s="1">
         <v>1912</v>
@@ -2588,7 +2584,7 @@
         <v>7</v>
       </c>
       <c r="E35" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F35" s="1">
         <v>30000</v>
@@ -2609,19 +2605,19 @@
         <v>30005</v>
       </c>
       <c r="L35" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M35" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="N35" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="P35" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q35" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.2">
@@ -2629,7 +2625,7 @@
         <v>41</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C36" s="1">
         <v>5309</v>
@@ -2638,7 +2634,7 @@
         <v>7</v>
       </c>
       <c r="E36" s="1" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F36" s="1">
         <v>30000</v>
@@ -2659,22 +2655,22 @@
         <v>30005</v>
       </c>
       <c r="L36" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M36" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N36" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="O36" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="O36" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="P36" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q36" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/NPCBehaviorData.xlsx
+++ b/Datas/NPCBehaviorData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="132">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -528,6 +528,22 @@
   </si>
   <si>
     <t>10,11,12,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>workMap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>homeAreas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>wrokMapAreas</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -859,23 +875,23 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:Q36"/>
+  <dimension ref="A2:T36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="9" style="1"/>
-    <col min="4" max="5" width="16.25" style="1" hidden="1" customWidth="1"/>
-    <col min="6" max="7" width="8.875" style="1" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="9.25" style="1" hidden="1" customWidth="1"/>
-    <col min="10" max="11" width="10.75" style="1" hidden="1" customWidth="1"/>
-    <col min="12" max="12" width="16.25" style="1" customWidth="1"/>
-    <col min="13" max="13" width="11.25" style="1" customWidth="1"/>
-    <col min="14" max="15" width="16.25" style="2" customWidth="1"/>
-    <col min="16" max="16" width="42.875" style="2" customWidth="1"/>
-    <col min="17" max="17" width="47.625" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="1"/>
+    <col min="1" max="6" width="9" style="1"/>
+    <col min="7" max="8" width="16.25" style="1" customWidth="1"/>
+    <col min="9" max="10" width="8.875" style="1" customWidth="1"/>
+    <col min="11" max="12" width="9.25" style="1" customWidth="1"/>
+    <col min="13" max="14" width="10.75" style="1" customWidth="1"/>
+    <col min="15" max="15" width="16.25" style="1" customWidth="1"/>
+    <col min="16" max="16" width="11.25" style="1" customWidth="1"/>
+    <col min="17" max="18" width="16.25" style="2" customWidth="1"/>
+    <col min="19" max="19" width="42.875" style="2" customWidth="1"/>
+    <col min="20" max="20" width="47.625" style="2" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -889,19 +905,19 @@
         <v>20</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>0</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>0</v>
@@ -910,25 +926,34 @@
         <v>0</v>
       </c>
       <c r="L2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="P2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
@@ -939,49 +964,58 @@
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="Q3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="O3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="P3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -991,47 +1025,50 @@
       <c r="C4" s="1">
         <v>1014</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="E4" s="1">
+        <v>0</v>
+      </c>
+      <c r="G4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="1" t="s">
+      <c r="H4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G4" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H4" s="1">
-        <v>30002</v>
-      </c>
       <c r="I4" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J4" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K4" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L4" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L4" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M4" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N4" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O4" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="M4" s="1" t="s">
+      <c r="P4" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="N4" s="2" t="s">
+      <c r="Q4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="P4" s="2" t="s">
+      <c r="S4" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="Q4" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="T4" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1041,20 +1078,14 @@
       <c r="C5" s="1">
         <v>0</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="E5" s="1">
+        <v>0</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>8</v>
-      </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
-      <c r="G5" s="1">
-        <v>0</v>
-      </c>
-      <c r="H5" s="1">
-        <v>0</v>
       </c>
       <c r="I5" s="1">
         <v>0</v>
@@ -1065,11 +1096,20 @@
       <c r="K5" s="1">
         <v>0</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" s="1">
+        <v>0</v>
+      </c>
+      <c r="M5" s="1">
+        <v>0</v>
+      </c>
+      <c r="N5" s="1">
+        <v>0</v>
+      </c>
+      <c r="O5" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1079,50 +1119,53 @@
       <c r="C6" s="1">
         <v>948</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="E6" s="1">
+        <v>948</v>
+      </c>
+      <c r="G6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E6" s="1" t="s">
+      <c r="H6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F6" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G6" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H6" s="1">
-        <v>30002</v>
-      </c>
       <c r="I6" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J6" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K6" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L6" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L6" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M6" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N6" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M6" s="1" t="s">
+      <c r="P6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="Q6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="R6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="P6" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q6" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S6" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T6" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1132,50 +1175,53 @@
       <c r="C7" s="1">
         <v>948</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="E7" s="1">
+        <v>948</v>
+      </c>
+      <c r="G7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E7" s="1" t="s">
+      <c r="H7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F7" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G7" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H7" s="1">
-        <v>30002</v>
-      </c>
       <c r="I7" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J7" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K7" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L7" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L7" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M7" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N7" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="P7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="N7" s="2" t="s">
+      <c r="Q7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="O7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="P7" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q7" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S7" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T7" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1185,50 +1231,53 @@
       <c r="C8" s="1">
         <v>900</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="E8" s="1">
+        <v>900</v>
+      </c>
+      <c r="G8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="H8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F8" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G8" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H8" s="1">
-        <v>30002</v>
-      </c>
       <c r="I8" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J8" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K8" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L8" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L8" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M8" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N8" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="P8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="O8" s="2" t="s">
+      <c r="R8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="P8" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q8" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S8" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1238,50 +1287,53 @@
       <c r="C9" s="1">
         <v>900</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="E9" s="1">
+        <v>900</v>
+      </c>
+      <c r="G9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="H9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G9" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H9" s="1">
-        <v>30002</v>
-      </c>
       <c r="I9" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J9" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K9" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L9" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L9" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M9" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N9" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="M9" s="1" t="s">
+      <c r="P9" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N9" s="2" t="s">
+      <c r="Q9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="O9" s="2" t="s">
+      <c r="R9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="P9" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S9" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1291,47 +1343,53 @@
       <c r="C10" s="1">
         <v>5170</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="1">
+        <v>51702</v>
+      </c>
+      <c r="E10" s="1">
+        <v>0</v>
+      </c>
+      <c r="G10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="1" t="s">
+      <c r="H10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F10" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G10" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H10" s="1">
-        <v>30002</v>
-      </c>
       <c r="I10" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J10" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K10" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L10" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L10" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M10" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N10" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="P10" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="Q10" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="P10" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q10" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S10" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1341,50 +1399,56 @@
       <c r="C11" s="1">
         <v>5170</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="1">
+        <v>51700</v>
+      </c>
+      <c r="E11" s="1">
+        <v>3115</v>
+      </c>
+      <c r="G11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E11" s="1" t="s">
+      <c r="H11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F11" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G11" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H11" s="1">
-        <v>30002</v>
-      </c>
       <c r="I11" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J11" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K11" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L11" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L11" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M11" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N11" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="P11" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="Q11" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="O11" s="2" t="s">
+      <c r="R11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P11" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q11" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S11" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>31</v>
       </c>
@@ -1394,50 +1458,56 @@
       <c r="C12" s="1">
         <v>5170</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="1">
+        <v>51701</v>
+      </c>
+      <c r="E12" s="1">
+        <v>3115</v>
+      </c>
+      <c r="G12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="H12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F12" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G12" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H12" s="1">
-        <v>30002</v>
-      </c>
       <c r="I12" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J12" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K12" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L12" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L12" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M12" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N12" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="P12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="Q12" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="O12" s="2" t="s">
+      <c r="R12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="P12" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q12" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1447,50 +1517,53 @@
       <c r="C13" s="1">
         <v>4800</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="E13" s="1">
+        <v>4800</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="H13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F13" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G13" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H13" s="1">
-        <v>30002</v>
-      </c>
       <c r="I13" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J13" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K13" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L13" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L13" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M13" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N13" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="P13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="Q13" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="O13" s="2" t="s">
+      <c r="R13" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="P13" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q13" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S13" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>14</v>
       </c>
@@ -1500,50 +1573,53 @@
       <c r="C14" s="1">
         <v>2270</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="E14" s="1">
+        <v>2180</v>
+      </c>
+      <c r="G14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E14" s="1" t="s">
+      <c r="H14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F14" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G14" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H14" s="1">
-        <v>30002</v>
-      </c>
       <c r="I14" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J14" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K14" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L14" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L14" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M14" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N14" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O14" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="P14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="Q14" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="O14" s="2" t="s">
+      <c r="R14" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="P14" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q14" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S14" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>40</v>
       </c>
@@ -1553,50 +1629,53 @@
       <c r="C15" s="1">
         <v>2270</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="E15" s="1">
+        <v>2180</v>
+      </c>
+      <c r="G15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E15" s="1" t="s">
+      <c r="H15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G15" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H15" s="1">
-        <v>30002</v>
-      </c>
       <c r="I15" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J15" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K15" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L15" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L15" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M15" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N15" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="P15" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="N15" s="2" t="s">
+      <c r="Q15" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="O15" s="2" t="s">
+      <c r="R15" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="P15" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q15" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S15" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>36</v>
       </c>
@@ -1606,50 +1685,53 @@
       <c r="C16" s="1">
         <v>2270</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="E16" s="1">
+        <v>2180</v>
+      </c>
+      <c r="G16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E16" s="1" t="s">
+      <c r="H16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F16" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G16" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H16" s="1">
-        <v>30002</v>
-      </c>
       <c r="I16" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J16" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K16" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L16" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L16" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M16" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N16" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="P16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N16" s="2" t="s">
+      <c r="Q16" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="O16" s="2" t="s">
+      <c r="R16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="P16" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S16" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1659,50 +1741,53 @@
       <c r="C17" s="1">
         <v>1112</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="E17" s="1">
+        <v>1014</v>
+      </c>
+      <c r="G17" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E17" s="1" t="s">
+      <c r="H17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F17" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G17" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H17" s="1">
-        <v>30002</v>
-      </c>
       <c r="I17" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J17" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K17" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L17" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L17" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M17" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N17" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="P17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N17" s="2" t="s">
+      <c r="Q17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="O17" s="2" t="s">
+      <c r="R17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="P17" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q17" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S17" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1712,47 +1797,50 @@
       <c r="C18" s="1">
         <v>1112</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="E18" s="1">
+        <v>1014</v>
+      </c>
+      <c r="G18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E18" s="1" t="s">
+      <c r="H18" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F18" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G18" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H18" s="1">
-        <v>30002</v>
-      </c>
       <c r="I18" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J18" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K18" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L18" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L18" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M18" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N18" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="M18" s="1" t="s">
+      <c r="P18" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="N18" s="2" t="s">
+      <c r="Q18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="P18" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q18" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S18" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T18" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>29</v>
       </c>
@@ -1762,47 +1850,50 @@
       <c r="C19" s="1">
         <v>4918</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="E19" s="1">
+        <v>0</v>
+      </c>
+      <c r="G19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E19" s="1" t="s">
+      <c r="H19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F19" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G19" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H19" s="1">
-        <v>30002</v>
-      </c>
       <c r="I19" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J19" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K19" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L19" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L19" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M19" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N19" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M19" s="1" t="s">
+      <c r="P19" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="N19" s="2" t="s">
+      <c r="Q19" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="P19" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q19" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S19" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T19" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1812,50 +1903,53 @@
       <c r="C20" s="1">
         <v>5013</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="E20" s="1">
+        <v>5013</v>
+      </c>
+      <c r="G20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E20" s="1" t="s">
+      <c r="H20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F20" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G20" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H20" s="1">
-        <v>30002</v>
-      </c>
       <c r="I20" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J20" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K20" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L20" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L20" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M20" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N20" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M20" s="1" t="s">
+      <c r="P20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N20" s="2" t="s">
+      <c r="Q20" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="O20" s="2" t="s">
+      <c r="R20" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="P20" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q20" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S20" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T20" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>38</v>
       </c>
@@ -1865,50 +1959,53 @@
       <c r="C21" s="1">
         <v>5013</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="E21" s="1">
+        <v>5013</v>
+      </c>
+      <c r="G21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="1" t="s">
+      <c r="H21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F21" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G21" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H21" s="1">
-        <v>30002</v>
-      </c>
       <c r="I21" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J21" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K21" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L21" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L21" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M21" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N21" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O21" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="M21" s="1" t="s">
+      <c r="P21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N21" s="2" t="s">
+      <c r="Q21" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="O21" s="2" t="s">
+      <c r="R21" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="P21" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q21" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S21" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T21" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>37</v>
       </c>
@@ -1918,50 +2015,53 @@
       <c r="C22" s="1">
         <v>1856</v>
       </c>
-      <c r="D22" s="1" t="s">
+      <c r="E22" s="1">
+        <v>1756</v>
+      </c>
+      <c r="G22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E22" s="1" t="s">
+      <c r="H22" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="F22" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G22" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H22" s="1">
-        <v>30002</v>
-      </c>
       <c r="I22" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J22" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K22" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L22" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L22" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M22" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N22" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O22" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="M22" s="1" t="s">
+      <c r="P22" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="N22" s="2" t="s">
+      <c r="Q22" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="O22" s="2" t="s">
+      <c r="R22" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="P22" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q22" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S22" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T22" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -1971,50 +2071,53 @@
       <c r="C23" s="1">
         <v>1856</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="E23" s="1">
+        <v>1756</v>
+      </c>
+      <c r="G23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E23" s="1" t="s">
+      <c r="H23" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F23" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G23" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H23" s="1">
-        <v>30002</v>
-      </c>
       <c r="I23" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J23" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K23" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L23" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L23" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M23" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N23" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M23" s="1" t="s">
+      <c r="P23" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N23" s="2" t="s">
+      <c r="Q23" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="O23" s="2" t="s">
+      <c r="R23" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="P23" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q23" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S23" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T23" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -2024,47 +2127,50 @@
       <c r="C24" s="1">
         <v>3300</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="E24" s="1">
+        <v>3297</v>
+      </c>
+      <c r="G24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="H24" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F24" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G24" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H24" s="1">
-        <v>30002</v>
-      </c>
       <c r="I24" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J24" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K24" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L24" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L24" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M24" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N24" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O24" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M24" s="1" t="s">
+      <c r="P24" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="Q24" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="P24" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q24" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S24" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T24" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -2074,50 +2180,53 @@
       <c r="C25" s="1">
         <v>3056</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="E25" s="1">
+        <v>3056</v>
+      </c>
+      <c r="G25" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="H25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F25" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G25" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H25" s="1">
-        <v>30002</v>
-      </c>
       <c r="I25" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J25" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K25" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L25" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L25" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M25" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N25" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O25" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M25" s="1" t="s">
+      <c r="P25" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N25" s="2" t="s">
+      <c r="Q25" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="O25" s="2" t="s">
+      <c r="R25" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="P25" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q25" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S25" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T25" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -2127,47 +2236,50 @@
       <c r="C26" s="1">
         <v>3056</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="E26" s="1">
+        <v>3056</v>
+      </c>
+      <c r="G26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="H26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F26" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G26" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H26" s="1">
-        <v>30002</v>
-      </c>
       <c r="I26" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J26" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K26" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L26" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L26" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M26" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N26" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O26" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M26" s="1" t="s">
+      <c r="P26" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="N26" s="2" t="s">
+      <c r="Q26" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="P26" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q26" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S26" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T26" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -2177,47 +2289,50 @@
       <c r="C27" s="1">
         <v>2015</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="E27" s="1">
+        <v>0</v>
+      </c>
+      <c r="G27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E27" s="1" t="s">
+      <c r="H27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F27" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G27" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H27" s="1">
-        <v>30002</v>
-      </c>
       <c r="I27" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J27" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K27" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L27" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L27" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M27" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N27" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O27" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M27" s="1" t="s">
+      <c r="P27" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="N27" s="2" t="s">
+      <c r="Q27" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="P27" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q27" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S27" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T27" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -2227,47 +2342,50 @@
       <c r="C28" s="1">
         <v>4765</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="E28" s="1">
+        <v>0</v>
+      </c>
+      <c r="G28" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="E28" s="1" t="s">
+      <c r="H28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F28" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G28" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H28" s="1">
-        <v>30002</v>
-      </c>
       <c r="I28" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J28" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K28" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L28" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L28" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M28" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N28" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O28" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M28" s="1" t="s">
+      <c r="P28" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="N28" s="2" t="s">
+      <c r="Q28" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="P28" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q28" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S28" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T28" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>35</v>
       </c>
@@ -2277,47 +2395,50 @@
       <c r="C29" s="1">
         <v>4696</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="E29" s="1">
+        <v>0</v>
+      </c>
+      <c r="G29" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="1" t="s">
+      <c r="H29" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F29" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G29" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H29" s="1">
-        <v>30002</v>
-      </c>
       <c r="I29" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J29" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K29" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L29" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L29" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M29" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N29" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O29" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="M29" s="1" t="s">
+      <c r="P29" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="N29" s="2" t="s">
+      <c r="Q29" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="P29" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q29" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S29" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -2327,50 +2448,53 @@
       <c r="C30" s="1">
         <v>2902</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="E30" s="1">
+        <v>0</v>
+      </c>
+      <c r="G30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E30" s="1" t="s">
+      <c r="H30" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F30" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G30" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H30" s="1">
-        <v>30002</v>
-      </c>
       <c r="I30" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J30" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K30" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L30" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L30" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M30" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N30" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O30" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M30" s="1" t="s">
+      <c r="P30" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N30" s="2" t="s">
+      <c r="Q30" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="O30" s="2" t="s">
+      <c r="R30" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="P30" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q30" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S30" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -2380,47 +2504,53 @@
       <c r="C31" s="1">
         <v>5476</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="1">
+        <v>547601</v>
+      </c>
+      <c r="E31" s="1">
+        <v>0</v>
+      </c>
+      <c r="G31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E31" s="1" t="s">
+      <c r="H31" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="F31" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G31" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H31" s="1">
-        <v>30002</v>
-      </c>
       <c r="I31" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J31" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K31" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L31" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L31" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M31" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N31" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O31" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M31" s="1" t="s">
+      <c r="P31" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="N31" s="2" t="s">
+      <c r="Q31" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="P31" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q31" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S31" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T31" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>27</v>
       </c>
@@ -2430,47 +2560,53 @@
       <c r="C32" s="1">
         <v>5476</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="1">
+        <v>547600</v>
+      </c>
+      <c r="E32" s="1">
+        <v>0</v>
+      </c>
+      <c r="G32" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E32" s="1" t="s">
+      <c r="H32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F32" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G32" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H32" s="1">
-        <v>30002</v>
-      </c>
       <c r="I32" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J32" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K32" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L32" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L32" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M32" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N32" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O32" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M32" s="1" t="s">
+      <c r="P32" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="N32" s="2" t="s">
+      <c r="Q32" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="P32" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q32" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S32" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T32" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -2480,47 +2616,50 @@
       <c r="C33" s="1">
         <v>5293</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="E33" s="1">
+        <v>0</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="1" t="s">
+      <c r="H33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F33" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G33" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H33" s="1">
-        <v>30002</v>
-      </c>
       <c r="I33" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J33" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K33" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L33" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L33" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M33" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N33" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O33" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M33" s="1" t="s">
+      <c r="P33" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="N33" s="2" t="s">
+      <c r="Q33" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="P33" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q33" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S33" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T33" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>34</v>
       </c>
@@ -2530,47 +2669,50 @@
       <c r="C34" s="1">
         <v>1912</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="E34" s="1">
+        <v>0</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E34" s="1" t="s">
+      <c r="H34" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F34" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G34" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H34" s="1">
-        <v>30002</v>
-      </c>
       <c r="I34" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J34" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K34" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L34" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L34" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M34" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N34" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O34" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="M34" s="1" t="s">
+      <c r="P34" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="N34" s="2" t="s">
+      <c r="Q34" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="P34" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q34" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S34" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T34" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>39</v>
       </c>
@@ -2580,47 +2722,50 @@
       <c r="C35" s="1">
         <v>1912</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="E35" s="1">
+        <v>0</v>
+      </c>
+      <c r="G35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E35" s="1" t="s">
+      <c r="H35" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F35" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G35" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H35" s="1">
-        <v>30002</v>
-      </c>
       <c r="I35" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J35" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K35" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L35" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L35" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M35" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N35" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O35" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M35" s="1" t="s">
+      <c r="P35" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="N35" s="2" t="s">
+      <c r="Q35" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="P35" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q35" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="S35" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T35" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>41</v>
       </c>
@@ -2630,46 +2775,55 @@
       <c r="C36" s="1">
         <v>5309</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="1">
+        <v>530900</v>
+      </c>
+      <c r="E36" s="1">
+        <v>5309</v>
+      </c>
+      <c r="F36" s="1">
+        <v>539001</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E36" s="1" t="s">
+      <c r="H36" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="F36" s="1">
-        <v>30000</v>
-      </c>
-      <c r="G36" s="1">
-        <v>30001</v>
-      </c>
-      <c r="H36" s="1">
-        <v>30002</v>
-      </c>
       <c r="I36" s="1">
-        <v>30003</v>
+        <v>30000</v>
       </c>
       <c r="J36" s="1">
-        <v>30004</v>
+        <v>30001</v>
       </c>
       <c r="K36" s="1">
-        <v>30005</v>
-      </c>
-      <c r="L36" s="1" t="s">
+        <v>30002</v>
+      </c>
+      <c r="L36" s="1">
+        <v>30003</v>
+      </c>
+      <c r="M36" s="1">
+        <v>30004</v>
+      </c>
+      <c r="N36" s="1">
+        <v>30005</v>
+      </c>
+      <c r="O36" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="M36" s="1" t="s">
+      <c r="P36" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="N36" s="2" t="s">
+      <c r="Q36" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="O36" s="2" t="s">
+      <c r="R36" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="P36" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="Q36" s="2" t="s">
+      <c r="S36" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="T36" s="2" t="s">
         <v>122</v>
       </c>
     </row>

--- a/Datas/NPCBehaviorData.xlsx
+++ b/Datas/NPCBehaviorData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="135">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -545,6 +545,16 @@
   <si>
     <t>wrokMapAreas</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int2&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visitShops</t>
+  </si>
+  <si>
+    <t>1000,500|1001,500|1002,500|1003,500|1004,500|1005,500|1006,500|1007,500|1008,500|1009,500|1010,500|1011,500</t>
   </si>
 </sst>
 </file>
@@ -875,23 +885,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:T36"/>
+  <dimension ref="A2:U36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
-    <col min="7" max="8" width="16.25" style="1" customWidth="1"/>
-    <col min="9" max="10" width="8.875" style="1" customWidth="1"/>
-    <col min="11" max="12" width="9.25" style="1" customWidth="1"/>
-    <col min="13" max="14" width="10.75" style="1" customWidth="1"/>
-    <col min="15" max="15" width="16.25" style="1" customWidth="1"/>
-    <col min="16" max="16" width="11.25" style="1" customWidth="1"/>
-    <col min="17" max="18" width="16.25" style="2" customWidth="1"/>
-    <col min="19" max="19" width="42.875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="47.625" style="2" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="1"/>
+    <col min="7" max="7" width="26.5" style="1" customWidth="1"/>
+    <col min="8" max="9" width="16.25" style="1" customWidth="1"/>
+    <col min="10" max="11" width="8.875" style="1" customWidth="1"/>
+    <col min="12" max="13" width="9.25" style="1" customWidth="1"/>
+    <col min="14" max="15" width="10.75" style="1" customWidth="1"/>
+    <col min="16" max="16" width="16.25" style="1" customWidth="1"/>
+    <col min="17" max="17" width="11.25" style="1" customWidth="1"/>
+    <col min="18" max="19" width="16.25" style="2" customWidth="1"/>
+    <col min="20" max="20" width="42.875" style="2" customWidth="1"/>
+    <col min="21" max="21" width="47.625" style="2" customWidth="1"/>
+    <col min="22" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -911,17 +922,17 @@
         <v>0</v>
       </c>
       <c r="G2" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>129</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>0</v>
-      </c>
       <c r="K2" s="1" t="s">
         <v>0</v>
       </c>
@@ -935,25 +946,28 @@
         <v>0</v>
       </c>
       <c r="O2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="P2" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="Q2" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="T2" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="U2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
@@ -973,49 +987,52 @@
         <v>131</v>
       </c>
       <c r="G3" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="K3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="L3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="M3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="M3" s="1" t="s">
+      <c r="N3" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="N3" s="1" t="s">
+      <c r="O3" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="S3" s="2" t="s">
+      <c r="T3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1028,47 +1045,53 @@
       <c r="E4" s="1">
         <v>0</v>
       </c>
+      <c r="F4" s="1">
+        <v>0</v>
+      </c>
       <c r="G4" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="1" t="s">
+      <c r="I4" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I4" s="1">
-        <v>30000</v>
-      </c>
       <c r="J4" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K4" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L4" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M4" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N4" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O4" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O4" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P4" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="P4" s="1" t="s">
+      <c r="Q4" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="Q4" s="2" t="s">
+      <c r="R4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="S4" s="2" t="s">
+      <c r="T4" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="T4" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U4" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1081,15 +1104,18 @@
       <c r="E5" s="1">
         <v>0</v>
       </c>
+      <c r="F5" s="1">
+        <v>0</v>
+      </c>
       <c r="G5" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H5" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H5" s="1" t="s">
+      <c r="I5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="1">
-        <v>0</v>
-      </c>
       <c r="J5" s="1">
         <v>0</v>
       </c>
@@ -1105,11 +1131,14 @@
       <c r="N5" s="1">
         <v>0</v>
       </c>
-      <c r="O5" s="1" t="s">
+      <c r="O5" s="1">
+        <v>0</v>
+      </c>
+      <c r="P5" s="1" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1122,50 +1151,56 @@
       <c r="E6" s="1">
         <v>948</v>
       </c>
+      <c r="F6" s="1">
+        <v>0</v>
+      </c>
       <c r="G6" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="1" t="s">
+      <c r="I6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I6" s="1">
-        <v>30000</v>
-      </c>
       <c r="J6" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K6" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L6" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M6" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N6" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O6" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O6" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P6" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="Q6" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="R6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="T6" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T6" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U6" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1178,50 +1213,56 @@
       <c r="E7" s="1">
         <v>948</v>
       </c>
+      <c r="F7" s="1">
+        <v>0</v>
+      </c>
       <c r="G7" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H7" s="1" t="s">
+      <c r="I7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I7" s="1">
-        <v>30000</v>
-      </c>
       <c r="J7" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K7" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L7" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M7" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N7" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O7" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O7" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P7" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="Q7" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="Q7" s="2" t="s">
+      <c r="R7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="S7" s="2" t="s">
+      <c r="T7" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T7" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U7" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1234,50 +1275,56 @@
       <c r="E8" s="1">
         <v>900</v>
       </c>
+      <c r="F8" s="1">
+        <v>0</v>
+      </c>
       <c r="G8" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H8" s="1" t="s">
+      <c r="I8" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I8" s="1">
-        <v>30000</v>
-      </c>
       <c r="J8" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K8" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L8" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M8" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N8" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O8" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O8" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P8" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P8" s="1" t="s">
+      <c r="Q8" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="R8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="S8" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="S8" s="2" t="s">
+      <c r="T8" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T8" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U8" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1290,50 +1337,56 @@
       <c r="E9" s="1">
         <v>900</v>
       </c>
+      <c r="F9" s="1">
+        <v>0</v>
+      </c>
       <c r="G9" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="H9" s="1" t="s">
+      <c r="I9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I9" s="1">
-        <v>30000</v>
-      </c>
       <c r="J9" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K9" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L9" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M9" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N9" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O9" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O9" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="P9" s="1" t="s">
+      <c r="Q9" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="Q9" s="2" t="s">
+      <c r="R9" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="R9" s="2" t="s">
+      <c r="S9" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="S9" s="2" t="s">
+      <c r="T9" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T9" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U9" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1349,47 +1402,53 @@
       <c r="E10" s="1">
         <v>0</v>
       </c>
+      <c r="F10" s="1">
+        <v>0</v>
+      </c>
       <c r="G10" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="1" t="s">
+      <c r="I10" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I10" s="1">
-        <v>30000</v>
-      </c>
       <c r="J10" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K10" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L10" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M10" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N10" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O10" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O10" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P10" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P10" s="1" t="s">
+      <c r="Q10" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="Q10" s="2" t="s">
+      <c r="R10" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="S10" s="2" t="s">
+      <c r="T10" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T10" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U10" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1405,50 +1464,56 @@
       <c r="E11" s="1">
         <v>3115</v>
       </c>
+      <c r="F11" s="1">
+        <v>0</v>
+      </c>
       <c r="G11" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H11" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="1" t="s">
+      <c r="I11" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I11" s="1">
-        <v>30000</v>
-      </c>
       <c r="J11" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K11" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L11" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M11" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N11" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O11" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O11" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P11" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P11" s="1" t="s">
+      <c r="Q11" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="Q11" s="2" t="s">
+      <c r="R11" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="R11" s="2" t="s">
+      <c r="S11" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="S11" s="2" t="s">
+      <c r="T11" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T11" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U11" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>31</v>
       </c>
@@ -1464,50 +1529,56 @@
       <c r="E12" s="1">
         <v>3115</v>
       </c>
+      <c r="F12" s="1">
+        <v>0</v>
+      </c>
       <c r="G12" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H12" s="1" t="s">
+      <c r="I12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I12" s="1">
-        <v>30000</v>
-      </c>
       <c r="J12" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K12" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L12" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M12" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N12" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O12" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O12" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P12" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P12" s="1" t="s">
+      <c r="Q12" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="R12" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="R12" s="2" t="s">
+      <c r="S12" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="S12" s="2" t="s">
+      <c r="T12" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T12" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U12" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1520,50 +1591,56 @@
       <c r="E13" s="1">
         <v>4800</v>
       </c>
+      <c r="F13" s="1">
+        <v>0</v>
+      </c>
       <c r="G13" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H13" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H13" s="1" t="s">
+      <c r="I13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I13" s="1">
-        <v>30000</v>
-      </c>
       <c r="J13" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K13" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L13" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M13" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N13" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O13" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O13" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P13" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P13" s="1" t="s">
+      <c r="Q13" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="Q13" s="2" t="s">
+      <c r="R13" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="R13" s="2" t="s">
+      <c r="S13" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="S13" s="2" t="s">
+      <c r="T13" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T13" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U13" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>14</v>
       </c>
@@ -1576,50 +1653,56 @@
       <c r="E14" s="1">
         <v>2180</v>
       </c>
+      <c r="F14" s="1">
+        <v>0</v>
+      </c>
       <c r="G14" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H14" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="1" t="s">
+      <c r="I14" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I14" s="1">
-        <v>30000</v>
-      </c>
       <c r="J14" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K14" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L14" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M14" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N14" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O14" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O14" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P14" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="P14" s="1" t="s">
+      <c r="Q14" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Q14" s="2" t="s">
+      <c r="R14" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="R14" s="2" t="s">
+      <c r="S14" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="S14" s="2" t="s">
+      <c r="T14" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T14" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U14" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>40</v>
       </c>
@@ -1632,50 +1715,56 @@
       <c r="E15" s="1">
         <v>2180</v>
       </c>
+      <c r="F15" s="1">
+        <v>0</v>
+      </c>
       <c r="G15" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H15" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H15" s="1" t="s">
+      <c r="I15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I15" s="1">
-        <v>30000</v>
-      </c>
       <c r="J15" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K15" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L15" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M15" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N15" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O15" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O15" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P15" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P15" s="1" t="s">
+      <c r="Q15" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="Q15" s="2" t="s">
+      <c r="R15" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="R15" s="2" t="s">
+      <c r="S15" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="S15" s="2" t="s">
+      <c r="T15" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T15" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U15" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>36</v>
       </c>
@@ -1688,50 +1777,56 @@
       <c r="E16" s="1">
         <v>2180</v>
       </c>
+      <c r="F16" s="1">
+        <v>0</v>
+      </c>
       <c r="G16" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="1" t="s">
+      <c r="I16" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I16" s="1">
-        <v>30000</v>
-      </c>
       <c r="J16" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K16" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L16" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M16" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N16" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O16" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O16" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P16" s="1" t="s">
+      <c r="Q16" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Q16" s="2" t="s">
+      <c r="R16" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="R16" s="2" t="s">
+      <c r="S16" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="S16" s="2" t="s">
+      <c r="T16" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T16" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="17" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U16" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1744,50 +1839,56 @@
       <c r="E17" s="1">
         <v>1014</v>
       </c>
+      <c r="F17" s="1">
+        <v>0</v>
+      </c>
       <c r="G17" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H17" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H17" s="1" t="s">
+      <c r="I17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I17" s="1">
-        <v>30000</v>
-      </c>
       <c r="J17" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K17" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L17" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M17" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N17" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O17" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O17" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P17" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P17" s="1" t="s">
+      <c r="Q17" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Q17" s="2" t="s">
+      <c r="R17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="R17" s="2" t="s">
+      <c r="S17" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="S17" s="2" t="s">
+      <c r="T17" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T17" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="18" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U17" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1800,47 +1901,53 @@
       <c r="E18" s="1">
         <v>1014</v>
       </c>
+      <c r="F18" s="1">
+        <v>0</v>
+      </c>
       <c r="G18" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H18" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H18" s="1" t="s">
+      <c r="I18" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I18" s="1">
-        <v>30000</v>
-      </c>
       <c r="J18" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K18" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L18" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M18" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N18" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O18" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O18" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P18" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="P18" s="1" t="s">
+      <c r="Q18" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="Q18" s="2" t="s">
+      <c r="R18" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="S18" s="2" t="s">
+      <c r="T18" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T18" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="19" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U18" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>29</v>
       </c>
@@ -1853,47 +1960,53 @@
       <c r="E19" s="1">
         <v>0</v>
       </c>
+      <c r="F19" s="1">
+        <v>0</v>
+      </c>
       <c r="G19" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H19" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H19" s="1" t="s">
+      <c r="I19" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I19" s="1">
-        <v>30000</v>
-      </c>
       <c r="J19" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K19" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L19" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M19" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N19" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O19" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O19" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P19" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P19" s="1" t="s">
+      <c r="Q19" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="Q19" s="2" t="s">
+      <c r="R19" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="S19" s="2" t="s">
+      <c r="T19" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T19" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="20" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U19" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -1906,50 +2019,56 @@
       <c r="E20" s="1">
         <v>5013</v>
       </c>
+      <c r="F20" s="1">
+        <v>0</v>
+      </c>
       <c r="G20" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H20" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H20" s="1" t="s">
+      <c r="I20" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I20" s="1">
-        <v>30000</v>
-      </c>
       <c r="J20" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K20" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L20" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M20" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N20" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O20" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O20" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P20" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P20" s="1" t="s">
+      <c r="Q20" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Q20" s="2" t="s">
+      <c r="R20" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="R20" s="2" t="s">
+      <c r="S20" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="S20" s="2" t="s">
+      <c r="T20" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T20" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="21" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U20" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>38</v>
       </c>
@@ -1962,50 +2081,56 @@
       <c r="E21" s="1">
         <v>5013</v>
       </c>
+      <c r="F21" s="1">
+        <v>0</v>
+      </c>
       <c r="G21" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H21" s="1" t="s">
+      <c r="I21" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I21" s="1">
-        <v>30000</v>
-      </c>
       <c r="J21" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K21" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L21" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M21" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N21" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O21" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O21" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P21" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="P21" s="1" t="s">
+      <c r="Q21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Q21" s="2" t="s">
+      <c r="R21" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="R21" s="2" t="s">
+      <c r="S21" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="S21" s="2" t="s">
+      <c r="T21" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T21" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="22" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U21" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>37</v>
       </c>
@@ -2018,50 +2143,56 @@
       <c r="E22" s="1">
         <v>1756</v>
       </c>
+      <c r="F22" s="1">
+        <v>0</v>
+      </c>
       <c r="G22" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H22" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H22" s="1" t="s">
+      <c r="I22" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="I22" s="1">
-        <v>30000</v>
-      </c>
       <c r="J22" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K22" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L22" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M22" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N22" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O22" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O22" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P22" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="P22" s="1" t="s">
+      <c r="Q22" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="Q22" s="2" t="s">
+      <c r="R22" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="R22" s="2" t="s">
+      <c r="S22" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="S22" s="2" t="s">
+      <c r="T22" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T22" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="23" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U22" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -2074,50 +2205,56 @@
       <c r="E23" s="1">
         <v>1756</v>
       </c>
+      <c r="F23" s="1">
+        <v>0</v>
+      </c>
       <c r="G23" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H23" s="1" t="s">
+      <c r="I23" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I23" s="1">
-        <v>30000</v>
-      </c>
       <c r="J23" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K23" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L23" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M23" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N23" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O23" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O23" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P23" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P23" s="1" t="s">
+      <c r="Q23" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Q23" s="2" t="s">
+      <c r="R23" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="R23" s="2" t="s">
+      <c r="S23" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="S23" s="2" t="s">
+      <c r="T23" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T23" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="24" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U23" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -2130,47 +2267,53 @@
       <c r="E24" s="1">
         <v>3297</v>
       </c>
+      <c r="F24" s="1">
+        <v>0</v>
+      </c>
       <c r="G24" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H24" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H24" s="1" t="s">
+      <c r="I24" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I24" s="1">
-        <v>30000</v>
-      </c>
       <c r="J24" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K24" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L24" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M24" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N24" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O24" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O24" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P24" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P24" s="1" t="s">
+      <c r="Q24" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="Q24" s="2" t="s">
+      <c r="R24" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="S24" s="2" t="s">
+      <c r="T24" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T24" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="25" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U24" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -2183,50 +2326,56 @@
       <c r="E25" s="1">
         <v>3056</v>
       </c>
+      <c r="F25" s="1">
+        <v>0</v>
+      </c>
       <c r="G25" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H25" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H25" s="1" t="s">
+      <c r="I25" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I25" s="1">
-        <v>30000</v>
-      </c>
       <c r="J25" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K25" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L25" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M25" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N25" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O25" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O25" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P25" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P25" s="1" t="s">
+      <c r="Q25" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Q25" s="2" t="s">
+      <c r="R25" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="R25" s="2" t="s">
+      <c r="S25" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="S25" s="2" t="s">
+      <c r="T25" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T25" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="26" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U25" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -2239,47 +2388,53 @@
       <c r="E26" s="1">
         <v>3056</v>
       </c>
+      <c r="F26" s="1">
+        <v>0</v>
+      </c>
       <c r="G26" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H26" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H26" s="1" t="s">
+      <c r="I26" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I26" s="1">
-        <v>30000</v>
-      </c>
       <c r="J26" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K26" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L26" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M26" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N26" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O26" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O26" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P26" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P26" s="1" t="s">
+      <c r="Q26" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="Q26" s="2" t="s">
+      <c r="R26" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="S26" s="2" t="s">
+      <c r="T26" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T26" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="27" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U26" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -2292,47 +2447,53 @@
       <c r="E27" s="1">
         <v>0</v>
       </c>
+      <c r="F27" s="1">
+        <v>0</v>
+      </c>
       <c r="G27" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H27" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="H27" s="1" t="s">
+      <c r="I27" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I27" s="1">
-        <v>30000</v>
-      </c>
       <c r="J27" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K27" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L27" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M27" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N27" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O27" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O27" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P27" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P27" s="1" t="s">
+      <c r="Q27" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="Q27" s="2" t="s">
+      <c r="R27" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="S27" s="2" t="s">
+      <c r="T27" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T27" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="28" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U27" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -2345,47 +2506,53 @@
       <c r="E28" s="1">
         <v>0</v>
       </c>
+      <c r="F28" s="1">
+        <v>0</v>
+      </c>
       <c r="G28" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H28" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="H28" s="1" t="s">
+      <c r="I28" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I28" s="1">
-        <v>30000</v>
-      </c>
       <c r="J28" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K28" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L28" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M28" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N28" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O28" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O28" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P28" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P28" s="1" t="s">
+      <c r="Q28" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="Q28" s="2" t="s">
+      <c r="R28" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="S28" s="2" t="s">
+      <c r="T28" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T28" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="29" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U28" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>35</v>
       </c>
@@ -2398,47 +2565,53 @@
       <c r="E29" s="1">
         <v>0</v>
       </c>
+      <c r="F29" s="1">
+        <v>0</v>
+      </c>
       <c r="G29" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H29" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H29" s="1" t="s">
+      <c r="I29" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I29" s="1">
-        <v>30000</v>
-      </c>
       <c r="J29" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K29" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L29" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M29" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N29" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O29" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O29" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P29" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="P29" s="1" t="s">
+      <c r="Q29" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="Q29" s="2" t="s">
+      <c r="R29" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="S29" s="2" t="s">
+      <c r="T29" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T29" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="30" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U29" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -2451,50 +2624,56 @@
       <c r="E30" s="1">
         <v>0</v>
       </c>
+      <c r="F30" s="1">
+        <v>0</v>
+      </c>
       <c r="G30" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H30" s="1" t="s">
+      <c r="I30" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I30" s="1">
-        <v>30000</v>
-      </c>
       <c r="J30" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K30" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L30" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M30" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N30" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O30" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O30" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P30" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P30" s="1" t="s">
+      <c r="Q30" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Q30" s="2" t="s">
+      <c r="R30" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="R30" s="2" t="s">
+      <c r="S30" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="S30" s="2" t="s">
+      <c r="T30" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T30" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="31" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U30" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -2510,47 +2689,53 @@
       <c r="E31" s="1">
         <v>0</v>
       </c>
+      <c r="F31" s="1">
+        <v>0</v>
+      </c>
       <c r="G31" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H31" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H31" s="1" t="s">
+      <c r="I31" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I31" s="1">
-        <v>30000</v>
-      </c>
       <c r="J31" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K31" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L31" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M31" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N31" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O31" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O31" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P31" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P31" s="1" t="s">
+      <c r="Q31" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="Q31" s="2" t="s">
+      <c r="R31" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="S31" s="2" t="s">
+      <c r="T31" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T31" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="32" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U31" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>27</v>
       </c>
@@ -2566,47 +2751,53 @@
       <c r="E32" s="1">
         <v>0</v>
       </c>
+      <c r="F32" s="1">
+        <v>0</v>
+      </c>
       <c r="G32" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H32" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="H32" s="1" t="s">
+      <c r="I32" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I32" s="1">
-        <v>30000</v>
-      </c>
       <c r="J32" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K32" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L32" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M32" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N32" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O32" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O32" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P32" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P32" s="1" t="s">
+      <c r="Q32" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="Q32" s="2" t="s">
+      <c r="R32" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="S32" s="2" t="s">
+      <c r="T32" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T32" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="33" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U32" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -2619,47 +2810,53 @@
       <c r="E33" s="1">
         <v>0</v>
       </c>
+      <c r="F33" s="1">
+        <v>0</v>
+      </c>
       <c r="G33" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H33" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H33" s="1" t="s">
+      <c r="I33" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I33" s="1">
-        <v>30000</v>
-      </c>
       <c r="J33" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K33" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L33" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M33" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N33" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O33" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O33" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P33" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P33" s="1" t="s">
+      <c r="Q33" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="Q33" s="2" t="s">
+      <c r="R33" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="S33" s="2" t="s">
+      <c r="T33" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T33" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="34" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U33" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>34</v>
       </c>
@@ -2672,47 +2869,53 @@
       <c r="E34" s="1">
         <v>0</v>
       </c>
+      <c r="F34" s="1">
+        <v>0</v>
+      </c>
       <c r="G34" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H34" s="1" t="s">
+      <c r="I34" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="I34" s="1">
-        <v>30000</v>
-      </c>
       <c r="J34" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K34" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L34" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M34" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N34" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O34" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O34" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P34" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="P34" s="1" t="s">
+      <c r="Q34" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="Q34" s="2" t="s">
+      <c r="R34" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="S34" s="2" t="s">
+      <c r="T34" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T34" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="35" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U34" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>39</v>
       </c>
@@ -2725,47 +2928,53 @@
       <c r="E35" s="1">
         <v>0</v>
       </c>
+      <c r="F35" s="1">
+        <v>0</v>
+      </c>
       <c r="G35" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H35" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H35" s="1" t="s">
+      <c r="I35" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I35" s="1">
-        <v>30000</v>
-      </c>
       <c r="J35" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K35" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L35" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M35" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N35" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O35" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O35" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P35" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P35" s="1" t="s">
+      <c r="Q35" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="Q35" s="2" t="s">
+      <c r="R35" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="S35" s="2" t="s">
+      <c r="T35" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T35" s="2" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="36" spans="1:20" x14ac:dyDescent="0.2">
+      <c r="U35" s="2" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>41</v>
       </c>
@@ -2785,45 +2994,48 @@
         <v>539001</v>
       </c>
       <c r="G36" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="H36" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="H36" s="1" t="s">
+      <c r="I36" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="I36" s="1">
-        <v>30000</v>
-      </c>
       <c r="J36" s="1">
-        <v>30001</v>
+        <v>30000</v>
       </c>
       <c r="K36" s="1">
-        <v>30002</v>
+        <v>30001</v>
       </c>
       <c r="L36" s="1">
-        <v>30003</v>
+        <v>30002</v>
       </c>
       <c r="M36" s="1">
-        <v>30004</v>
+        <v>30003</v>
       </c>
       <c r="N36" s="1">
-        <v>30005</v>
-      </c>
-      <c r="O36" s="1" t="s">
+        <v>30004</v>
+      </c>
+      <c r="O36" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P36" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="P36" s="1" t="s">
+      <c r="Q36" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="Q36" s="2" t="s">
+      <c r="R36" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="R36" s="2" t="s">
+      <c r="S36" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="S36" s="2" t="s">
+      <c r="T36" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="T36" s="2" t="s">
+      <c r="U36" s="2" t="s">
         <v>122</v>
       </c>
     </row>

--- a/Datas/NPCBehaviorData.xlsx
+++ b/Datas/NPCBehaviorData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="136">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -153,408 +153,412 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>gameTimeRanges</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visitMaps</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>班尼迪克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,1,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1014,1089143</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,1007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>玛德琳</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002,1004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,1,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>948,1070089</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>948,1068306</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,1007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002,1004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,1,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>948,1071156</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>948,1068306</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丝特芬妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900,1081513</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900,1079546</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>格吉尔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,1007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,1,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900,1080132</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>琼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强尼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1001,1007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2180,1166370</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002,1004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏佐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希尔达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5013,1154408</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1002,1004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1756,1019120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1756,1019120</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿普敦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>摩尔根</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考波特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马勒第兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5170,1156253</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5170,1156284</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5170,1156900</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2270,1167153</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2270,1166370</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2270,1167418</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4918,1147517</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5013,1153081</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5013,1153488</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1856,1071058</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1856,1080475</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3300,1070049</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3056,1166131</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3056,1166294</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2015,1071591</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4765,1139029</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4696,1042715</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2902,1168177</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5476,1162796</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5476,1001440</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5293,1001490</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1912,1080779</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1912,1080613</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4800,1144907</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纺织婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5309,1081691</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5309,1159783</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,0,9,0,9,0,17,30,17,30,19,30,19,30, 22,0,22,0,24,0</t>
+  </si>
+  <si>
+    <t>60001,60002,60003,60004,60005</t>
+  </si>
+  <si>
+    <t>6,0,9,0,9,0,17,30,17,30,19,30,19,30, 22,0,22,0,24,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3056,1019972</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2180,1165443</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4800,1143244</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,11,12,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>workMap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int2&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000,500|1001,500|1002,500|1003,500|1004,500|1005,500|1006,500|1007,500|1008,500|1009,500|1010,500|1011,500</t>
+  </si>
+  <si>
     <t>workItems</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>gameTimeRanges</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>visitMaps</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>班尼迪克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,1,2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1014,1089143</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001,1007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>玛德琳</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1002,1004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,1,2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>948,1070089</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>948,1068306</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001,1007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1002,1004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,1,2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>948,1071156</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>948,1068306</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>丝特芬妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900,1081513</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900,1079546</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>格吉尔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001,1007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,1,2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900,1080132</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>亚度尼斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>琼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>强尼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1001,1007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>占卜婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>坎蒂丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2180,1166370</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希拉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1002,1004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>夏佐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希尔达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5013,1154408</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>莱特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1002,1004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1756,1019120</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布拉德利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1756,1019120</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布蓝达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>朵儿洁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿普敦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>摩尔根</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>考波特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>马勒第兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱格伯特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿尔杰农</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5170,1156253</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5170,1156284</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5170,1156900</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2270,1167153</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2270,1166370</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2270,1167418</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4918,1147517</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5013,1153081</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5013,1153488</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1856,1071058</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1856,1080475</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3300,1070049</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3056,1166131</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3056,1166294</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2015,1071591</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4765,1139029</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4696,1042715</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2902,1168177</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5476,1162796</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5476,1001440</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5293,1001490</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1912,1080779</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1912,1080613</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4800,1144907</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>纺织婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5309,1081691</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5309,1159783</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6,0,9,0,9,0,17,30,17,30,19,30,19,30, 22,0,22,0,24,0</t>
-  </si>
-  <si>
-    <t>60001,60002,60003,60004,60005</t>
-  </si>
-  <si>
-    <t>6,0,9,0,9,0,17,30,17,30,19,30,19,30, 22,0,22,0,24,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3056,1019972</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2180,1165443</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4800,1143244</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,11,12,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>workMap</t>
+    <t>homeAreas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visitShops</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>List&lt;int&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>homeAreas</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>wrokMapAreas</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>List&lt;int2&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>visitShops</t>
-  </si>
-  <si>
-    <t>1000,500|1001,500|1002,500|1003,500|1004,500|1005,500|1006,500|1007,500|1008,500|1009,500|1010,500|1011,500</t>
+  </si>
+  <si>
+    <t>workMapAreas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -919,13 +923,13 @@
         <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>0</v>
+        <v>134</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>20</v>
@@ -978,13 +982,13 @@
         <v>9</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="G3" s="1" t="s">
         <v>133</v>
@@ -1023,21 +1027,21 @@
         <v>32</v>
       </c>
       <c r="S3" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="T3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="T3" s="2" t="s">
+      <c r="U3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="U3" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+    </row>
+    <row r="4" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C4" s="1">
         <v>1014</v>
@@ -1045,11 +1049,8 @@
       <c r="E4" s="1">
         <v>0</v>
       </c>
-      <c r="F4" s="1">
-        <v>0</v>
-      </c>
       <c r="G4" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>7</v>
@@ -1076,19 +1077,19 @@
         <v>30005</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -1104,14 +1105,11 @@
       <c r="E5" s="1">
         <v>0</v>
       </c>
-      <c r="F5" s="1">
-        <v>0</v>
-      </c>
       <c r="G5" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I5" s="1" t="s">
         <v>8</v>
@@ -1135,15 +1133,16 @@
         <v>0</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>41</v>
-      </c>
+        <v>40</v>
+      </c>
+      <c r="Q5" s="2"/>
     </row>
     <row r="6" spans="1:21" ht="57" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C6" s="1">
         <v>948</v>
@@ -1151,53 +1150,50 @@
       <c r="E6" s="1">
         <v>948</v>
       </c>
-      <c r="F6" s="1">
-        <v>0</v>
-      </c>
       <c r="G6" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I6" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="J6" s="1">
+        <v>30000</v>
+      </c>
+      <c r="K6" s="1">
+        <v>30001</v>
+      </c>
+      <c r="L6" s="1">
+        <v>30002</v>
+      </c>
+      <c r="M6" s="1">
+        <v>30003</v>
+      </c>
+      <c r="N6" s="1">
+        <v>30004</v>
+      </c>
+      <c r="O6" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P6" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q6" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="J6" s="1">
-        <v>30000</v>
-      </c>
-      <c r="K6" s="1">
-        <v>30001</v>
-      </c>
-      <c r="L6" s="1">
-        <v>30002</v>
-      </c>
-      <c r="M6" s="1">
-        <v>30003</v>
-      </c>
-      <c r="N6" s="1">
-        <v>30004</v>
-      </c>
-      <c r="O6" s="1">
-        <v>30005</v>
-      </c>
-      <c r="P6" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q6" s="1" t="s">
+      <c r="R6" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="S6" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="S6" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="T6" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -1205,7 +1201,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C7" s="1">
         <v>948</v>
@@ -1213,53 +1209,50 @@
       <c r="E7" s="1">
         <v>948</v>
       </c>
-      <c r="F7" s="1">
-        <v>0</v>
-      </c>
       <c r="G7" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H7" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="I7" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="I7" s="1" t="s">
+      <c r="J7" s="1">
+        <v>30000</v>
+      </c>
+      <c r="K7" s="1">
+        <v>30001</v>
+      </c>
+      <c r="L7" s="1">
+        <v>30002</v>
+      </c>
+      <c r="M7" s="1">
+        <v>30003</v>
+      </c>
+      <c r="N7" s="1">
+        <v>30004</v>
+      </c>
+      <c r="O7" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Q7" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="J7" s="1">
-        <v>30000</v>
-      </c>
-      <c r="K7" s="1">
-        <v>30001</v>
-      </c>
-      <c r="L7" s="1">
-        <v>30002</v>
-      </c>
-      <c r="M7" s="1">
-        <v>30003</v>
-      </c>
-      <c r="N7" s="1">
-        <v>30004</v>
-      </c>
-      <c r="O7" s="1">
-        <v>30005</v>
-      </c>
-      <c r="P7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="Q7" s="1" t="s">
+      <c r="R7" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="R7" s="2" t="s">
+      <c r="S7" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="T7" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -1267,7 +1260,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C8" s="1">
         <v>900</v>
@@ -1275,14 +1268,11 @@
       <c r="E8" s="1">
         <v>900</v>
       </c>
-      <c r="F8" s="1">
-        <v>0</v>
-      </c>
       <c r="G8" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I8" s="1" t="s">
         <v>8</v>
@@ -1306,22 +1296,22 @@
         <v>30005</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="S8" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="S8" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="T8" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -1329,7 +1319,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="C9" s="1">
         <v>900</v>
@@ -1337,14 +1327,11 @@
       <c r="E9" s="1">
         <v>900</v>
       </c>
-      <c r="F9" s="1">
-        <v>0</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I9" s="1" t="s">
         <v>8</v>
@@ -1368,22 +1355,22 @@
         <v>30005</v>
       </c>
       <c r="P9" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="Q9" s="1" t="s">
+      <c r="R9" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="R9" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="S9" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -1391,7 +1378,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C10" s="1">
         <v>5170</v>
@@ -1402,17 +1389,14 @@
       <c r="E10" s="1">
         <v>0</v>
       </c>
-      <c r="F10" s="1">
-        <v>0</v>
-      </c>
       <c r="G10" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J10" s="1">
         <v>30000</v>
@@ -1433,19 +1417,19 @@
         <v>30005</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -1453,7 +1437,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C11" s="1">
         <v>5170</v>
@@ -1464,11 +1448,8 @@
       <c r="E11" s="1">
         <v>3115</v>
       </c>
-      <c r="F11" s="1">
-        <v>0</v>
-      </c>
       <c r="G11" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H11" s="1" t="s">
         <v>7</v>
@@ -1495,22 +1476,22 @@
         <v>30005</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>10</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -1518,7 +1499,7 @@
         <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C12" s="1">
         <v>5170</v>
@@ -1529,14 +1510,11 @@
       <c r="E12" s="1">
         <v>3115</v>
       </c>
-      <c r="F12" s="1">
-        <v>0</v>
-      </c>
       <c r="G12" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="I12" s="1" t="s">
         <v>8</v>
@@ -1560,22 +1538,22 @@
         <v>30005</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>10</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -1583,7 +1561,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C13" s="1">
         <v>4800</v>
@@ -1591,11 +1569,8 @@
       <c r="E13" s="1">
         <v>4800</v>
       </c>
-      <c r="F13" s="1">
-        <v>0</v>
-      </c>
       <c r="G13" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H13" s="1" t="s">
         <v>7</v>
@@ -1622,22 +1597,22 @@
         <v>30005</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -1645,7 +1620,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C14" s="1">
         <v>2270</v>
@@ -1653,17 +1628,14 @@
       <c r="E14" s="1">
         <v>2180</v>
       </c>
-      <c r="F14" s="1">
-        <v>0</v>
-      </c>
       <c r="G14" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J14" s="1">
         <v>30000</v>
@@ -1684,22 +1656,22 @@
         <v>30005</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -1707,7 +1679,7 @@
         <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C15" s="1">
         <v>2270</v>
@@ -1715,11 +1687,8 @@
       <c r="E15" s="1">
         <v>2180</v>
       </c>
-      <c r="F15" s="1">
-        <v>0</v>
-      </c>
       <c r="G15" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>7</v>
@@ -1746,22 +1715,22 @@
         <v>30005</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -1777,11 +1746,8 @@
       <c r="E16" s="1">
         <v>2180</v>
       </c>
-      <c r="F16" s="1">
-        <v>0</v>
-      </c>
       <c r="G16" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H16" s="1" t="s">
         <v>7</v>
@@ -1808,22 +1774,22 @@
         <v>30005</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -1831,7 +1797,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C17" s="1">
         <v>1112</v>
@@ -1839,11 +1805,8 @@
       <c r="E17" s="1">
         <v>1014</v>
       </c>
-      <c r="F17" s="1">
-        <v>0</v>
-      </c>
       <c r="G17" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H17" s="1" t="s">
         <v>7</v>
@@ -1870,10 +1833,10 @@
         <v>30005</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R17" s="2" t="s">
         <v>12</v>
@@ -1882,10 +1845,10 @@
         <v>18</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -1893,7 +1856,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C18" s="1">
         <v>1112</v>
@@ -1901,17 +1864,14 @@
       <c r="E18" s="1">
         <v>1014</v>
       </c>
-      <c r="F18" s="1">
-        <v>0</v>
-      </c>
       <c r="G18" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I18" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J18" s="1">
         <v>30000</v>
@@ -1932,19 +1892,19 @@
         <v>30005</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R18" s="2" t="s">
         <v>13</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -1952,7 +1912,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C19" s="1">
         <v>4918</v>
@@ -1960,11 +1920,8 @@
       <c r="E19" s="1">
         <v>0</v>
       </c>
-      <c r="F19" s="1">
-        <v>0</v>
-      </c>
       <c r="G19" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H19" s="1" t="s">
         <v>7</v>
@@ -1991,19 +1948,19 @@
         <v>30005</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="20" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -2011,7 +1968,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C20" s="1">
         <v>5013</v>
@@ -2019,11 +1976,8 @@
       <c r="E20" s="1">
         <v>5013</v>
       </c>
-      <c r="F20" s="1">
-        <v>0</v>
-      </c>
       <c r="G20" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H20" s="1" t="s">
         <v>7</v>
@@ -2050,22 +2004,22 @@
         <v>30005</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="21" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -2073,7 +2027,7 @@
         <v>38</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C21" s="1">
         <v>5013</v>
@@ -2081,17 +2035,14 @@
       <c r="E21" s="1">
         <v>5013</v>
       </c>
-      <c r="F21" s="1">
-        <v>0</v>
-      </c>
       <c r="G21" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J21" s="1">
         <v>30000</v>
@@ -2112,22 +2063,22 @@
         <v>30005</v>
       </c>
       <c r="P21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q21" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="Q21" s="1" t="s">
-        <v>38</v>
-      </c>
       <c r="R21" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="S21" s="2" t="s">
         <v>14</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="22" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -2135,7 +2086,7 @@
         <v>37</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C22" s="1">
         <v>1856</v>
@@ -2143,53 +2094,50 @@
       <c r="E22" s="1">
         <v>1756</v>
       </c>
-      <c r="F22" s="1">
-        <v>0</v>
-      </c>
       <c r="G22" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H22" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I22" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="J22" s="1">
+        <v>30000</v>
+      </c>
+      <c r="K22" s="1">
+        <v>30001</v>
+      </c>
+      <c r="L22" s="1">
+        <v>30002</v>
+      </c>
+      <c r="M22" s="1">
+        <v>30003</v>
+      </c>
+      <c r="N22" s="1">
+        <v>30004</v>
+      </c>
+      <c r="O22" s="1">
+        <v>30005</v>
+      </c>
+      <c r="P22" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="J22" s="1">
-        <v>30000</v>
-      </c>
-      <c r="K22" s="1">
-        <v>30001</v>
-      </c>
-      <c r="L22" s="1">
-        <v>30002</v>
-      </c>
-      <c r="M22" s="1">
-        <v>30003</v>
-      </c>
-      <c r="N22" s="1">
-        <v>30004</v>
-      </c>
-      <c r="O22" s="1">
-        <v>30005</v>
-      </c>
-      <c r="P22" s="1" t="s">
+      <c r="Q22" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="R22" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="S22" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="Q22" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="R22" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="S22" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="T22" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -2197,7 +2145,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C23" s="1">
         <v>1856</v>
@@ -2205,17 +2153,14 @@
       <c r="E23" s="1">
         <v>1756</v>
       </c>
-      <c r="F23" s="1">
-        <v>0</v>
-      </c>
       <c r="G23" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H23" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I23" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J23" s="1">
         <v>30000</v>
@@ -2236,22 +2181,22 @@
         <v>30005</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="24" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -2259,7 +2204,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C24" s="1">
         <v>3300</v>
@@ -2267,11 +2212,8 @@
       <c r="E24" s="1">
         <v>3297</v>
       </c>
-      <c r="F24" s="1">
-        <v>0</v>
-      </c>
       <c r="G24" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H24" s="1" t="s">
         <v>7</v>
@@ -2298,19 +2240,19 @@
         <v>30005</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -2326,11 +2268,8 @@
       <c r="E25" s="1">
         <v>3056</v>
       </c>
-      <c r="F25" s="1">
-        <v>0</v>
-      </c>
       <c r="G25" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H25" s="1" t="s">
         <v>7</v>
@@ -2357,22 +2296,22 @@
         <v>30005</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -2388,11 +2327,8 @@
       <c r="E26" s="1">
         <v>3056</v>
       </c>
-      <c r="F26" s="1">
-        <v>0</v>
-      </c>
       <c r="G26" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H26" s="1" t="s">
         <v>7</v>
@@ -2419,19 +2355,19 @@
         <v>30005</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -2439,7 +2375,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C27" s="1">
         <v>2015</v>
@@ -2447,14 +2383,11 @@
       <c r="E27" s="1">
         <v>0</v>
       </c>
-      <c r="F27" s="1">
-        <v>0</v>
-      </c>
       <c r="G27" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="I27" s="1" t="s">
         <v>8</v>
@@ -2478,19 +2411,19 @@
         <v>30005</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U27" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -2498,7 +2431,7 @@
         <v>24</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C28" s="1">
         <v>4765</v>
@@ -2506,14 +2439,11 @@
       <c r="E28" s="1">
         <v>0</v>
       </c>
-      <c r="F28" s="1">
-        <v>0</v>
-      </c>
       <c r="G28" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="I28" s="1" t="s">
         <v>8</v>
@@ -2537,19 +2467,19 @@
         <v>30005</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="29" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -2557,7 +2487,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C29" s="1">
         <v>4696</v>
@@ -2565,17 +2495,14 @@
       <c r="E29" s="1">
         <v>0</v>
       </c>
-      <c r="F29" s="1">
-        <v>0</v>
-      </c>
       <c r="G29" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H29" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I29" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J29" s="1">
         <v>30000</v>
@@ -2596,19 +2523,19 @@
         <v>30005</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U29" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="30" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -2616,7 +2543,7 @@
         <v>26</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C30" s="1">
         <v>2902</v>
@@ -2624,11 +2551,8 @@
       <c r="E30" s="1">
         <v>0</v>
       </c>
-      <c r="F30" s="1">
-        <v>0</v>
-      </c>
       <c r="G30" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H30" s="1" t="s">
         <v>7</v>
@@ -2655,22 +2579,22 @@
         <v>30005</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="S30" s="2" t="s">
         <v>17</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -2678,7 +2602,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C31" s="1">
         <v>5476</v>
@@ -2689,17 +2613,14 @@
       <c r="E31" s="1">
         <v>0</v>
       </c>
-      <c r="F31" s="1">
-        <v>0</v>
-      </c>
       <c r="G31" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H31" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I31" s="1" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="J31" s="1">
         <v>30000</v>
@@ -2720,19 +2641,19 @@
         <v>30005</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U31" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="32" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -2740,7 +2661,7 @@
         <v>27</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C32" s="1">
         <v>5476</v>
@@ -2751,14 +2672,11 @@
       <c r="E32" s="1">
         <v>0</v>
       </c>
-      <c r="F32" s="1">
-        <v>0</v>
-      </c>
       <c r="G32" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I32" s="1" t="s">
         <v>8</v>
@@ -2782,19 +2700,19 @@
         <v>30005</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U32" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="33" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -2802,7 +2720,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C33" s="1">
         <v>5293</v>
@@ -2810,11 +2728,8 @@
       <c r="E33" s="1">
         <v>0</v>
       </c>
-      <c r="F33" s="1">
-        <v>0</v>
-      </c>
       <c r="G33" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H33" s="1" t="s">
         <v>7</v>
@@ -2841,19 +2756,19 @@
         <v>30005</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U33" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="34" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -2861,7 +2776,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="C34" s="1">
         <v>1912</v>
@@ -2869,11 +2784,8 @@
       <c r="E34" s="1">
         <v>0</v>
       </c>
-      <c r="F34" s="1">
-        <v>0</v>
-      </c>
       <c r="G34" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H34" s="1" t="s">
         <v>7</v>
@@ -2900,19 +2812,19 @@
         <v>30005</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U34" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -2920,7 +2832,7 @@
         <v>39</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C35" s="1">
         <v>1912</v>
@@ -2928,17 +2840,14 @@
       <c r="E35" s="1">
         <v>0</v>
       </c>
-      <c r="F35" s="1">
-        <v>0</v>
-      </c>
       <c r="G35" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H35" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I35" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J35" s="1">
         <v>30000</v>
@@ -2959,19 +2868,19 @@
         <v>30005</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U35" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="36" spans="1:21" ht="57" x14ac:dyDescent="0.2">
@@ -2979,7 +2888,7 @@
         <v>41</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="C36" s="1">
         <v>5309</v>
@@ -2994,13 +2903,13 @@
         <v>539001</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="H36" s="1" t="s">
         <v>7</v>
       </c>
       <c r="I36" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="J36" s="1">
         <v>30000</v>
@@ -3021,22 +2930,22 @@
         <v>30005</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="R36" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="S36" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="S36" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="T36" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="U36" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/Datas/NPCBehaviorData.xlsx
+++ b/Datas/NPCBehaviorData.xlsx
@@ -1620,13 +1620,13 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="C14" s="1">
-        <v>2270</v>
+        <v>1112</v>
       </c>
       <c r="E14" s="1">
-        <v>2180</v>
+        <v>1014</v>
       </c>
       <c r="G14" s="1" t="s">
         <v>130</v>
@@ -1635,7 +1635,7 @@
         <v>7</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>48</v>
+        <v>8</v>
       </c>
       <c r="J14" s="1">
         <v>30000</v>
@@ -1656,16 +1656,16 @@
         <v>30005</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="Q14" s="1" t="s">
         <v>37</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>97</v>
+        <v>12</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>124</v>
+        <v>18</v>
       </c>
       <c r="T14" s="2" t="s">
         <v>120</v>
@@ -1797,13 +1797,13 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="C17" s="1">
-        <v>1112</v>
+        <v>2270</v>
       </c>
       <c r="E17" s="1">
-        <v>1014</v>
+        <v>2180</v>
       </c>
       <c r="G17" s="1" t="s">
         <v>130</v>
@@ -1812,7 +1812,7 @@
         <v>7</v>
       </c>
       <c r="I17" s="1" t="s">
-        <v>8</v>
+        <v>48</v>
       </c>
       <c r="J17" s="1">
         <v>30000</v>
@@ -1833,16 +1833,16 @@
         <v>30005</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="Q17" s="1" t="s">
         <v>37</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>12</v>
+        <v>97</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>18</v>
+        <v>124</v>
       </c>
       <c r="T17" s="2" t="s">
         <v>120</v>

--- a/Datas/NPCBehaviorData.xlsx
+++ b/Datas/NPCBehaviorData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="170">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -559,6 +559,109 @@
   <si>
     <t>workMapAreas</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npcFriends</t>
+  </si>
+  <si>
+    <t>List&lt;int2&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|27,100|30,100|35,100|36,100|39,100|41,100|37,100</t>
+  </si>
+  <si>
+    <t>3,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|27,100|30,100|35,100|36,100|39,100|41,100|7,100|18,100|24,100|16,100|17,100</t>
+  </si>
+  <si>
+    <t>5,100|12,100|14,100|16,100|17,100|21,100|22,100|24,100|36,100|38,100|41,100|40,100|23,100|10,100</t>
+  </si>
+  <si>
+    <t>5,100|3,100|10,100|17,100|12,100|6,100|23,100|25,100|26,100|28,100|29,100|30,100|32,100|35,100|39,100|41,100</t>
+  </si>
+  <si>
+    <t>5,100|3,100|27,100|35,100|39,100|41,100|25,100|29,100</t>
+  </si>
+  <si>
+    <t>3,100|5,100|7,100|10,100|12,100|16,100|17,100|18,100|21,100|22,100|36,100|14,100|38,100|41,100|23,100</t>
+  </si>
+  <si>
+    <t>3,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|27,100|30,100|35,100|5,100|39,100|41,100|7,100|18,100|24,100|16,100|17,100</t>
+  </si>
+  <si>
+    <t>3,100|5,100|7,100|10,100|12,100|16,100|17,100|18,100|21,100|22,100|36,100|38,100|40,100|41,100|23,100</t>
+  </si>
+  <si>
+    <t>12,100|21,100|35,100|41,100|5,100|25,100</t>
+  </si>
+  <si>
+    <t>3,100|5,100|7,100|10,100|12,100|16,100|17,100|18,100|21,100|22,100|36,100|14,100|40,100|41,100|23,100</t>
+  </si>
+  <si>
+    <t>3,100|5,100|6,100|7,100|10,100|9,100|12,100|16,100|17,100|18,100|23,100|27,100|28,100|29,100|30,100|35,100|36,100|37,100|39,100|41,100</t>
+  </si>
+  <si>
+    <t>5,100|12,100|14,100|16,100|17,100|21,100|7,100|24,100|36,100|38,100|41,100|40,100|23,100|10,100</t>
+  </si>
+  <si>
+    <t>12,100|41,100|35,100|21,100|5,100|29,100|3,100|27,100|39,100</t>
+  </si>
+  <si>
+    <t>10,100|12,100|21,100|35,100|41,100|5,100|25,100</t>
+  </si>
+  <si>
+    <t>5,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|27,100|30,100|3,100|36,100|39,100|41,100|37,100</t>
+  </si>
+  <si>
+    <t>5,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|3,100|30,100|35,100|36,100|39,100|41,100|37,100</t>
+  </si>
+  <si>
+    <t>5,100|3,100|10,100|17,100|12,100|6,100|23,100|25,100|26,100|28,100|29,100|9,100|32,100|35,100|39,100|41,100</t>
+  </si>
+  <si>
+    <t>5,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|27,100|30,100|35,100|36,100|3,100|41,100|37,100</t>
+  </si>
+  <si>
+    <t>3,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|27,100|30,100|35,100|36,100|39,100|5,100|7,100|18,100|24,100|16,100|17,100</t>
+  </si>
+  <si>
+    <t>8,100|9,100|10,100|12,100|14,100|16,100|18,100|19,100|22,100|23,100|26,100|28,100|30,100|34,100|38,100|41,100|40,100</t>
+  </si>
+  <si>
+    <t>3,100|5,100|6,100|7,100|8,100|9,100|10,100|12,100|14,100|16,100|17,100|18,100|19,100|21,100|22,100|23,100|24,100|25,100|26,100|27,100|28,100|29,100|30,100|31,100|34,100|35,100|36,100|37,100|38,100|39,100|40,100|41,100</t>
+  </si>
+  <si>
+    <t>3,100|5,100|6,100|8,100|9,100|10,100|12,100|21,100|23,100|26,100|27,100|28,100|29,100|30,100|34,100|35,100|36,100|37,100|39,100|41,100</t>
+  </si>
+  <si>
+    <t>3,100|5,100|6,100|7,100|9,100|10,100|12,100|16,100|17,100|18,100|19,100|21,100|25,100|26,100|27,100|28,100|29,100|30,100|31,100|34,100|35,100|36,100|37,100|39,100|41,100</t>
+  </si>
+  <si>
+    <t>8,100|9,100|10,100|12,100|14,100|16,100|18,100|19,100|6,100|22,100|23,100|28,100|30,100|34,100|38,100|41,100|40,100</t>
+  </si>
+  <si>
+    <t>3,100|6,100|9,100|12,100|18,100|19,100|21,100|22,100|26,100|27,100|8,100|30,100|29,100|34,100|35,100|39,100|41,100|31,100</t>
+  </si>
+  <si>
+    <t>3,100|6,100|9,100|12,100|18,100|19,100|21,100|22,100|26,100|27,100|28,100|30,100|29,100|34,100|35,100|39,100|41,100|8,100</t>
+  </si>
+  <si>
+    <t>3,100|6,100|9,100|12,100|18,100|19,100|21,100|22,100|26,100|27,100|28,100|30,100|29,100|31,100|35,100|39,100|41,100|8,100</t>
+  </si>
+  <si>
+    <t>3,100|6,100|9,100|12,100|18,100|19,100|21,100|22,100|26,100|27,100|28,100|30,100|29,100|34,100|35,100|39,100|41,100|31,100</t>
+  </si>
+  <si>
+    <t>8,100|9,100|10,100|12,100|14,100|16,100|18,100|19,100|22,100|23,100|28,100|30,100|34,100|38,100|41,100|40,100</t>
+  </si>
+  <si>
+    <t>3,100|5,100|7,100|10,100|12,100|16,100|17,100|18,100|21,100|22,100|36,100|38,100|40,100|41,100|14,100|23,100|30,100|39,100</t>
+  </si>
+  <si>
+    <t>3,100|5,100|7,100|10,100|12,100|16,100|18,100|21,100|22,100|36,100|38,100|40,100|41,100|14,100|23,100|30,100|39,100</t>
+  </si>
+  <si>
+    <t>3,100|5,100|7,100|10,100|12,100|16,100|21,100|22,100|36,100|38,100|40,100|41,100|14,100|23,100|30,100|39,100|17,100</t>
   </si>
 </sst>
 </file>
@@ -889,11 +992,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A2:U36"/>
+  <dimension ref="A2:V36"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="26.5" style="1" customWidth="1"/>
+    <col min="7" max="7" width="52" style="1" customWidth="1"/>
     <col min="8" max="9" width="16.25" style="1" customWidth="1"/>
     <col min="10" max="11" width="8.875" style="1" customWidth="1"/>
     <col min="12" max="13" width="9.25" style="1" customWidth="1"/>
@@ -901,12 +1004,13 @@
     <col min="16" max="16" width="16.25" style="1" customWidth="1"/>
     <col min="17" max="17" width="11.25" style="1" customWidth="1"/>
     <col min="18" max="19" width="16.25" style="2" customWidth="1"/>
-    <col min="20" max="20" width="42.875" style="2" customWidth="1"/>
-    <col min="21" max="21" width="47.625" style="2" customWidth="1"/>
-    <col min="22" max="16384" width="9" style="1"/>
+    <col min="20" max="20" width="35.375" style="2" customWidth="1"/>
+    <col min="21" max="21" width="42.875" style="2" customWidth="1"/>
+    <col min="22" max="22" width="47.625" style="2" customWidth="1"/>
+    <col min="23" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -965,13 +1069,16 @@
         <v>23</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>24</v>
+        <v>137</v>
       </c>
       <c r="U2" s="2" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="3" spans="1:21" ht="28.5" x14ac:dyDescent="0.2">
+      <c r="V2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
@@ -1030,13 +1137,16 @@
         <v>131</v>
       </c>
       <c r="T3" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="U3" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="U3" s="2" t="s">
+      <c r="V3" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="4" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -1086,13 +1196,16 @@
         <v>38</v>
       </c>
       <c r="T4" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="U4" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="U4" s="2" t="s">
+      <c r="V4" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="5" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1137,7 +1250,7 @@
       </c>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" ht="57" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -1190,13 +1303,16 @@
         <v>45</v>
       </c>
       <c r="T6" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="U6" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U6" s="2" t="s">
+      <c r="V6" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="7" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -1249,13 +1365,16 @@
         <v>51</v>
       </c>
       <c r="T7" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="U7" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U7" s="2" t="s">
+      <c r="V7" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="8" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -1308,13 +1427,16 @@
         <v>54</v>
       </c>
       <c r="T8" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="U8" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U8" s="2" t="s">
+      <c r="V8" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="9" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -1367,13 +1489,16 @@
         <v>54</v>
       </c>
       <c r="T9" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="U9" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U9" s="2" t="s">
+      <c r="V9" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="10" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -1426,13 +1551,16 @@
         <v>92</v>
       </c>
       <c r="T10" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="U10" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U10" s="2" t="s">
+      <c r="V10" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="11" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" ht="85.5" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -1488,13 +1616,16 @@
         <v>10</v>
       </c>
       <c r="T11" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="U11" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U11" s="2" t="s">
+      <c r="V11" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="12" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>31</v>
       </c>
@@ -1550,13 +1681,16 @@
         <v>10</v>
       </c>
       <c r="T12" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="U12" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U12" s="2" t="s">
+      <c r="V12" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="13" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -1609,13 +1743,16 @@
         <v>115</v>
       </c>
       <c r="T13" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="U13" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U13" s="2" t="s">
+      <c r="V13" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="14" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>14</v>
       </c>
@@ -1668,13 +1805,16 @@
         <v>18</v>
       </c>
       <c r="T14" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="U14" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U14" s="2" t="s">
+      <c r="V14" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="15" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>40</v>
       </c>
@@ -1727,13 +1867,16 @@
         <v>124</v>
       </c>
       <c r="T15" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="U15" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U15" s="2" t="s">
+      <c r="V15" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="16" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:22" ht="57" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>36</v>
       </c>
@@ -1786,13 +1929,16 @@
         <v>68</v>
       </c>
       <c r="T16" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="U16" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U16" s="2" t="s">
+      <c r="V16" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="17" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1845,13 +1991,16 @@
         <v>124</v>
       </c>
       <c r="T17" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="U17" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U17" s="2" t="s">
+      <c r="V17" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="18" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -1901,13 +2050,16 @@
         <v>13</v>
       </c>
       <c r="T18" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="U18" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U18" s="2" t="s">
+      <c r="V18" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="19" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>29</v>
       </c>
@@ -1957,13 +2109,16 @@
         <v>98</v>
       </c>
       <c r="T19" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="U19" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U19" s="2" t="s">
+      <c r="V19" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="20" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>18</v>
       </c>
@@ -2016,13 +2171,16 @@
         <v>74</v>
       </c>
       <c r="T20" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="U20" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U20" s="2" t="s">
+      <c r="V20" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="21" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>38</v>
       </c>
@@ -2075,13 +2233,16 @@
         <v>14</v>
       </c>
       <c r="T21" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="U21" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U21" s="2" t="s">
+      <c r="V21" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="22" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>37</v>
       </c>
@@ -2134,13 +2295,16 @@
         <v>79</v>
       </c>
       <c r="T22" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="U22" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U22" s="2" t="s">
+      <c r="V22" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="23" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:22" ht="57" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>19</v>
       </c>
@@ -2193,13 +2357,16 @@
         <v>81</v>
       </c>
       <c r="T23" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="U23" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U23" s="2" t="s">
+      <c r="V23" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="24" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:22" ht="57" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>21</v>
       </c>
@@ -2249,13 +2416,16 @@
         <v>103</v>
       </c>
       <c r="T24" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="U24" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U24" s="2" t="s">
+      <c r="V24" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="25" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>22</v>
       </c>
@@ -2308,13 +2478,16 @@
         <v>123</v>
       </c>
       <c r="T25" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="U25" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U25" s="2" t="s">
+      <c r="V25" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="26" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -2364,13 +2537,16 @@
         <v>105</v>
       </c>
       <c r="T26" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="U26" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U26" s="2" t="s">
+      <c r="V26" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="27" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:22" ht="71.25" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>23</v>
       </c>
@@ -2420,13 +2596,16 @@
         <v>106</v>
       </c>
       <c r="T27" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="U27" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U27" s="2" t="s">
+      <c r="V27" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="28" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>24</v>
       </c>
@@ -2476,13 +2655,16 @@
         <v>107</v>
       </c>
       <c r="T28" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="U28" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U28" s="2" t="s">
+      <c r="V28" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="29" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>35</v>
       </c>
@@ -2532,13 +2714,16 @@
         <v>108</v>
       </c>
       <c r="T29" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="U29" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U29" s="2" t="s">
+      <c r="V29" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="30" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>26</v>
       </c>
@@ -2591,13 +2776,16 @@
         <v>17</v>
       </c>
       <c r="T30" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="U30" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U30" s="2" t="s">
+      <c r="V30" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="31" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>28</v>
       </c>
@@ -2650,13 +2838,16 @@
         <v>110</v>
       </c>
       <c r="T31" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="U31" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U31" s="2" t="s">
+      <c r="V31" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>27</v>
       </c>
@@ -2709,13 +2900,16 @@
         <v>111</v>
       </c>
       <c r="T32" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="U32" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U32" s="2" t="s">
+      <c r="V32" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>30</v>
       </c>
@@ -2765,13 +2959,16 @@
         <v>112</v>
       </c>
       <c r="T33" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="U33" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U33" s="2" t="s">
+      <c r="V33" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>34</v>
       </c>
@@ -2821,13 +3018,16 @@
         <v>113</v>
       </c>
       <c r="T34" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="U34" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U34" s="2" t="s">
+      <c r="V34" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>39</v>
       </c>
@@ -2877,13 +3077,16 @@
         <v>114</v>
       </c>
       <c r="T35" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="U35" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U35" s="2" t="s">
+      <c r="V35" s="2" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="57" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:22" ht="57" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>41</v>
       </c>
@@ -2942,9 +3145,12 @@
         <v>119</v>
       </c>
       <c r="T36" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="U36" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="U36" s="2" t="s">
+      <c r="V36" s="2" t="s">
         <v>121</v>
       </c>
     </row>

--- a/Datas/NPCBehaviorData.xlsx
+++ b/Datas/NPCBehaviorData.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="NPCBehaviorData" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,16 +20,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="387" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="191">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>unLikeItems</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>likeTalk</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -49,14 +46,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1001,1007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1002,1004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>home</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -129,10 +118,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>likeItems</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>defaultTalk</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -177,10 +162,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1001,1007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Default</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -189,10 +170,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1002,1004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0,1,2,3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -209,14 +186,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1001,1007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1002,1004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>0,1,2,3</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -245,10 +214,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1001,1007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Default</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -273,10 +238,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1001,1007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>占卜婆婆</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -305,10 +266,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1002,1004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>夏佐</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -329,10 +286,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1002,1004</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>Default</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -531,43 +484,39 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>List&lt;int2&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000,500|1001,500|1002,500|1003,500|1004,500|1005,500|1006,500|1007,500|1008,500|1009,500|1010,500|1011,500</t>
+  </si>
+  <si>
+    <t>workItems</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>homeAreas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visitShops</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>List&lt;int&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>workMapAreas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npcFriends</t>
   </si>
   <si>
     <t>List&lt;int2&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1000,500|1001,500|1002,500|1003,500|1004,500|1005,500|1006,500|1007,500|1008,500|1009,500|1010,500|1011,500</t>
-  </si>
-  <si>
-    <t>workItems</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>homeAreas</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>visitShops</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>List&lt;int&gt;</t>
-  </si>
-  <si>
-    <t>workMapAreas</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>npcFriends</t>
-  </si>
-  <si>
-    <t>List&lt;int2&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>5,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|27,100|30,100|35,100|36,100|39,100|41,100|37,100</t>
   </si>
   <si>
@@ -662,6 +611,110 @@
   </si>
   <si>
     <t>3,100|5,100|7,100|10,100|12,100|16,100|21,100|22,100|36,100|38,100|40,100|41,100|14,100|23,100|30,100|39,100|17,100</t>
+  </si>
+  <si>
+    <t>likeItem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unLikeItem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>班尼迪克</t>
+  </si>
+  <si>
+    <t>玛德琳</t>
+  </si>
+  <si>
+    <t>布莱兹</t>
+  </si>
+  <si>
+    <t>丝特芬妮</t>
+  </si>
+  <si>
+    <t>格吉尔</t>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+  </si>
+  <si>
+    <t>琼</t>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+  </si>
+  <si>
+    <t>希拉</t>
+  </si>
+  <si>
+    <t>希尔达</t>
+  </si>
+  <si>
+    <t>布拉德利</t>
+  </si>
+  <si>
+    <t>布蓝达</t>
+  </si>
+  <si>
+    <t>希贝儿</t>
+  </si>
+  <si>
+    <t>帕特里克</t>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+  </si>
+  <si>
+    <t>梅林</t>
+  </si>
+  <si>
+    <t>摩尔根</t>
+  </si>
+  <si>
+    <t>马勒第兹</t>
+  </si>
+  <si>
+    <t>考波特</t>
+  </si>
+  <si>
+    <t>夏佐</t>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+  </si>
+  <si>
+    <t>强尼</t>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+  </si>
+  <si>
+    <t>阿普敦</t>
+  </si>
+  <si>
+    <t>艾琳娜</t>
+  </si>
+  <si>
+    <t>莱特</t>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+  </si>
+  <si>
+    <t>艾德文娜</t>
   </si>
 </sst>
 </file>
@@ -684,12 +737,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -704,12 +763,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -997,7 +1059,7 @@
   <cols>
     <col min="1" max="6" width="9" style="1"/>
     <col min="7" max="7" width="52" style="1" customWidth="1"/>
-    <col min="8" max="9" width="16.25" style="1" customWidth="1"/>
+    <col min="8" max="9" width="16.25" style="3" customWidth="1"/>
     <col min="10" max="11" width="8.875" style="1" customWidth="1"/>
     <col min="12" max="13" width="9.25" style="1" customWidth="1"/>
     <col min="14" max="15" width="10.75" style="1" customWidth="1"/>
@@ -1015,31 +1077,31 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>134</v>
+        <v>121</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>129</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>20</v>
+        <v>116</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>0</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>0</v>
@@ -1057,93 +1119,93 @@
         <v>0</v>
       </c>
       <c r="P2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="R2" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="S2" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="R2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="S2" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="T2" s="2" t="s">
-        <v>137</v>
+        <v>124</v>
       </c>
       <c r="U2" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="V2" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="O3" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="P3" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>132</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>127</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>135</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>133</v>
-      </c>
-      <c r="H3" s="1" t="s">
+      <c r="Q3" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="L3" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="M3" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="N3" s="1" t="s">
+      <c r="R3" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="S3" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="U3" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="V3" s="2" t="s">
         <v>30</v>
-      </c>
-      <c r="Q3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1151,7 +1213,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C4" s="1">
         <v>1014</v>
@@ -1160,13 +1222,15 @@
         <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I4" s="1" t="s">
-        <v>8</v>
+        <v>117</v>
+      </c>
+      <c r="H4" s="3">
+        <f>VLOOKUP(B4,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>13</v>
+      </c>
+      <c r="I4" s="3">
+        <f>VLOOKUP(B4,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>15</v>
       </c>
       <c r="J4" s="1">
         <v>30000</v>
@@ -1187,22 +1251,22 @@
         <v>30005</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="R4" s="2" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>138</v>
+        <v>125</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>122</v>
+        <v>110</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -1210,7 +1274,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C5" s="1">
         <v>0</v>
@@ -1219,13 +1283,13 @@
         <v>0</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I5" s="1" t="s">
-        <v>8</v>
+        <v>117</v>
+      </c>
+      <c r="H5" s="3">
+        <v>0</v>
+      </c>
+      <c r="I5" s="3">
+        <v>0</v>
       </c>
       <c r="J5" s="1">
         <v>0</v>
@@ -1246,7 +1310,7 @@
         <v>0</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q5" s="2"/>
     </row>
@@ -1255,7 +1319,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
       <c r="C6" s="1">
         <v>948</v>
@@ -1264,13 +1328,15 @@
         <v>948</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I6" s="1" t="s">
-        <v>42</v>
+        <v>117</v>
+      </c>
+      <c r="H6" s="3">
+        <f>VLOOKUP(B6,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>24</v>
+      </c>
+      <c r="I6" s="3">
+        <f>VLOOKUP(B6,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>11</v>
       </c>
       <c r="J6" s="1">
         <v>30000</v>
@@ -1291,25 +1357,25 @@
         <v>30005</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q6" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="R6" s="2" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="S6" s="2" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>139</v>
+        <v>126</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1317,7 +1383,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="C7" s="1">
         <v>948</v>
@@ -1326,13 +1392,15 @@
         <v>948</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I7" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
+      </c>
+      <c r="H7" s="3">
+        <f>VLOOKUP(B7,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>25</v>
+      </c>
+      <c r="I7" s="3">
+        <f>VLOOKUP(B7,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>1</v>
       </c>
       <c r="J7" s="1">
         <v>30000</v>
@@ -1353,25 +1421,25 @@
         <v>30005</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q7" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="R7" s="2" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="S7" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>157</v>
+        <v>144</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1379,7 +1447,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="C8" s="1">
         <v>900</v>
@@ -1388,13 +1456,15 @@
         <v>900</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I8" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H8" s="3">
+        <f>VLOOKUP(B8,Sheet1!$E$2:$G$33,2,FALSE)</f>
         <v>8</v>
+      </c>
+      <c r="I8" s="3">
+        <f>VLOOKUP(B8,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>4</v>
       </c>
       <c r="J8" s="1">
         <v>30000</v>
@@ -1415,25 +1485,25 @@
         <v>30005</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q8" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="R8" s="2" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="S8" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>140</v>
+        <v>127</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1441,7 +1511,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="C9" s="1">
         <v>900</v>
@@ -1450,13 +1520,15 @@
         <v>900</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>8</v>
+        <v>117</v>
+      </c>
+      <c r="H9" s="3">
+        <f>VLOOKUP(B9,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>4</v>
+      </c>
+      <c r="I9" s="3">
+        <f>VLOOKUP(B9,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>6</v>
       </c>
       <c r="J9" s="1">
         <v>30000</v>
@@ -1477,25 +1549,25 @@
         <v>30005</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="Q9" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="R9" s="2" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="S9" s="2" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1503,7 +1575,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="C10" s="1">
         <v>5170</v>
@@ -1515,13 +1587,15 @@
         <v>0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
+      </c>
+      <c r="H10" s="3">
+        <f>VLOOKUP(B10,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>10</v>
+      </c>
+      <c r="I10" s="3">
+        <f>VLOOKUP(B10,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>20</v>
       </c>
       <c r="J10" s="1">
         <v>30000</v>
@@ -1542,22 +1616,22 @@
         <v>30005</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>141</v>
+        <v>128</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="85.5" x14ac:dyDescent="0.2">
@@ -1565,7 +1639,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C11" s="1">
         <v>5170</v>
@@ -1577,13 +1651,15 @@
         <v>3115</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>8</v>
+        <v>117</v>
+      </c>
+      <c r="H11" s="3">
+        <f>VLOOKUP(B11,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>23</v>
+      </c>
+      <c r="I11" s="3">
+        <f>VLOOKUP(B11,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>21</v>
       </c>
       <c r="J11" s="1">
         <v>30000</v>
@@ -1604,25 +1680,25 @@
         <v>30005</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>93</v>
+        <v>81</v>
       </c>
       <c r="S11" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>158</v>
+        <v>145</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1630,7 +1706,7 @@
         <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="C12" s="1">
         <v>5170</v>
@@ -1642,13 +1718,15 @@
         <v>3115</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>8</v>
+        <v>117</v>
+      </c>
+      <c r="H12" s="3">
+        <f>VLOOKUP(B12,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>9</v>
+      </c>
+      <c r="I12" s="3">
+        <f>VLOOKUP(B12,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>20</v>
       </c>
       <c r="J12" s="1">
         <v>30000</v>
@@ -1669,25 +1747,25 @@
         <v>30005</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q12" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="S12" s="2" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>163</v>
+        <v>150</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -1695,7 +1773,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="C13" s="1">
         <v>4800</v>
@@ -1704,13 +1782,15 @@
         <v>4800</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>8</v>
+        <v>117</v>
+      </c>
+      <c r="H13" s="3">
+        <f>VLOOKUP(B13,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>21</v>
+      </c>
+      <c r="I13" s="3">
+        <f>VLOOKUP(B13,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>23</v>
       </c>
       <c r="J13" s="1">
         <v>30000</v>
@@ -1731,25 +1811,25 @@
         <v>30005</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>125</v>
+        <v>113</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>142</v>
+        <v>129</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1757,7 +1837,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="C14" s="1">
         <v>1112</v>
@@ -1766,13 +1846,15 @@
         <v>1014</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I14" s="1" t="s">
-        <v>8</v>
+        <v>117</v>
+      </c>
+      <c r="H14" s="3">
+        <f>VLOOKUP(B14,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>29</v>
+      </c>
+      <c r="I14" s="3">
+        <f>VLOOKUP(B14,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>14</v>
       </c>
       <c r="J14" s="1">
         <v>30000</v>
@@ -1793,25 +1875,25 @@
         <v>30005</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q14" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="R14" s="2" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="S14" s="2" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1819,7 +1901,7 @@
         <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="C15" s="1">
         <v>2270</v>
@@ -1828,13 +1910,15 @@
         <v>2180</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I15" s="1" t="s">
-        <v>8</v>
+        <v>117</v>
+      </c>
+      <c r="H15" s="3">
+        <f>VLOOKUP(B15,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>15</v>
+      </c>
+      <c r="I15" s="3">
+        <f>VLOOKUP(B15,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>17</v>
       </c>
       <c r="J15" s="1">
         <v>30000</v>
@@ -1855,25 +1939,25 @@
         <v>30005</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q15" s="1" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>143</v>
+        <v>130</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="57" x14ac:dyDescent="0.2">
@@ -1881,7 +1965,7 @@
         <v>36</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C16" s="1">
         <v>2270</v>
@@ -1890,13 +1974,15 @@
         <v>2180</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I16" s="1" t="s">
-        <v>8</v>
+        <v>117</v>
+      </c>
+      <c r="H16" s="3">
+        <f>VLOOKUP(B16,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>2</v>
+      </c>
+      <c r="I16" s="3">
+        <f>VLOOKUP(B16,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>28</v>
       </c>
       <c r="J16" s="1">
         <v>30000</v>
@@ -1917,25 +2003,25 @@
         <v>30005</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q16" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1943,7 +2029,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="C17" s="1">
         <v>2270</v>
@@ -1952,13 +2038,15 @@
         <v>2180</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H17" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I17" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
+      </c>
+      <c r="H17" s="3">
+        <f>VLOOKUP(B17,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>26</v>
+      </c>
+      <c r="I17" s="3">
+        <f>VLOOKUP(B17,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>16</v>
       </c>
       <c r="J17" s="1">
         <v>30000</v>
@@ -1979,25 +2067,25 @@
         <v>30005</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="Q17" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>124</v>
+        <v>112</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>145</v>
+        <v>132</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V17" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2005,7 +2093,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="C18" s="1">
         <v>1112</v>
@@ -2014,13 +2102,15 @@
         <v>1014</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H18" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I18" s="1" t="s">
-        <v>71</v>
+        <v>117</v>
+      </c>
+      <c r="H18" s="3">
+        <f>VLOOKUP(B18,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>16</v>
+      </c>
+      <c r="I18" s="3">
+        <f>VLOOKUP(B18,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>26</v>
       </c>
       <c r="J18" s="1">
         <v>30000</v>
@@ -2041,22 +2131,22 @@
         <v>30005</v>
       </c>
       <c r="P18" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="R18" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>168</v>
+        <v>155</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -2064,7 +2154,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C19" s="1">
         <v>4918</v>
@@ -2073,12 +2163,14 @@
         <v>0</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H19" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I19" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="H19" s="3">
+        <f>VLOOKUP(B19,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>27</v>
+      </c>
+      <c r="I19" s="3">
+        <f>VLOOKUP(B19,Sheet1!$E$2:$G$33,3,FALSE)</f>
         <v>8</v>
       </c>
       <c r="J19" s="1">
@@ -2100,22 +2192,22 @@
         <v>30005</v>
       </c>
       <c r="P19" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V19" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2123,7 +2215,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="C20" s="1">
         <v>5013</v>
@@ -2132,13 +2224,15 @@
         <v>5013</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H20" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I20" s="1" t="s">
-        <v>8</v>
+        <v>117</v>
+      </c>
+      <c r="H20" s="3">
+        <f>VLOOKUP(B20,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>3</v>
+      </c>
+      <c r="I20" s="3">
+        <f>VLOOKUP(B20,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>30</v>
       </c>
       <c r="J20" s="1">
         <v>30000</v>
@@ -2159,25 +2253,25 @@
         <v>30005</v>
       </c>
       <c r="P20" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q20" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2185,7 +2279,7 @@
         <v>38</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="C21" s="1">
         <v>5013</v>
@@ -2194,13 +2288,15 @@
         <v>5013</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I21" s="1" t="s">
-        <v>42</v>
+        <v>117</v>
+      </c>
+      <c r="H21" s="3">
+        <f>VLOOKUP(B21,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>26</v>
+      </c>
+      <c r="I21" s="3">
+        <f>VLOOKUP(B21,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>15</v>
       </c>
       <c r="J21" s="1">
         <v>30000</v>
@@ -2221,25 +2317,25 @@
         <v>30005</v>
       </c>
       <c r="P21" s="1" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="Q21" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="S21" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>147</v>
+        <v>134</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V21" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2247,7 +2343,7 @@
         <v>37</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="C22" s="1">
         <v>1856</v>
@@ -2256,13 +2352,15 @@
         <v>1756</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H22" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I22" s="1" t="s">
-        <v>77</v>
+        <v>117</v>
+      </c>
+      <c r="H22" s="3">
+        <f>VLOOKUP(B22,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>14</v>
+      </c>
+      <c r="I22" s="3">
+        <f>VLOOKUP(B22,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>5</v>
       </c>
       <c r="J22" s="1">
         <v>30000</v>
@@ -2283,25 +2381,25 @@
         <v>30005</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>79</v>
+        <v>67</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>166</v>
+        <v>153</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="57" x14ac:dyDescent="0.2">
@@ -2309,7 +2407,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>80</v>
+        <v>68</v>
       </c>
       <c r="C23" s="1">
         <v>1856</v>
@@ -2318,13 +2416,15 @@
         <v>1756</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I23" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
+      </c>
+      <c r="H23" s="3">
+        <f>VLOOKUP(B23,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>28</v>
+      </c>
+      <c r="I23" s="3">
+        <f>VLOOKUP(B23,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>12</v>
       </c>
       <c r="J23" s="1">
         <v>30000</v>
@@ -2345,25 +2445,25 @@
         <v>30005</v>
       </c>
       <c r="P23" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q23" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>81</v>
+        <v>69</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V23" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="57" x14ac:dyDescent="0.2">
@@ -2371,7 +2471,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="C24" s="1">
         <v>3300</v>
@@ -2380,13 +2480,15 @@
         <v>3297</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H24" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I24" s="1" t="s">
-        <v>8</v>
+        <v>117</v>
+      </c>
+      <c r="H24" s="3">
+        <f>VLOOKUP(B24,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>19</v>
+      </c>
+      <c r="I24" s="3">
+        <f>VLOOKUP(B24,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>18</v>
       </c>
       <c r="J24" s="1">
         <v>30000</v>
@@ -2407,22 +2509,22 @@
         <v>30005</v>
       </c>
       <c r="P24" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>148</v>
+        <v>135</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2430,7 +2532,7 @@
         <v>22</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C25" s="1">
         <v>3056</v>
@@ -2439,13 +2541,15 @@
         <v>3056</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H25" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I25" s="1" t="s">
-        <v>8</v>
+        <v>117</v>
+      </c>
+      <c r="H25" s="3">
+        <f>VLOOKUP(B25,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>20</v>
+      </c>
+      <c r="I25" s="3">
+        <f>VLOOKUP(B25,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>22</v>
       </c>
       <c r="J25" s="1">
         <v>30000</v>
@@ -2466,25 +2570,25 @@
         <v>30005</v>
       </c>
       <c r="P25" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q25" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V25" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -2492,7 +2596,7 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C26" s="1">
         <v>3056</v>
@@ -2501,13 +2605,15 @@
         <v>3056</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H26" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I26" s="1" t="s">
-        <v>8</v>
+        <v>117</v>
+      </c>
+      <c r="H26" s="3">
+        <f>VLOOKUP(B26,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>17</v>
+      </c>
+      <c r="I26" s="3">
+        <f>VLOOKUP(B26,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>1</v>
       </c>
       <c r="J26" s="1">
         <v>30000</v>
@@ -2528,22 +2634,22 @@
         <v>30005</v>
       </c>
       <c r="P26" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>105</v>
+        <v>93</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>150</v>
+        <v>137</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V26" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="71.25" x14ac:dyDescent="0.2">
@@ -2551,7 +2657,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="C27" s="1">
         <v>2015</v>
@@ -2560,13 +2666,15 @@
         <v>0</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H27" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="I27" s="1" t="s">
-        <v>8</v>
+        <v>117</v>
+      </c>
+      <c r="H27" s="3">
+        <f>VLOOKUP(B27,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>16</v>
+      </c>
+      <c r="I27" s="3">
+        <f>VLOOKUP(B27,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>27</v>
       </c>
       <c r="J27" s="1">
         <v>30000</v>
@@ -2587,22 +2695,22 @@
         <v>30005</v>
       </c>
       <c r="P27" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="U27" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V27" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -2610,7 +2718,7 @@
         <v>24</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="C28" s="1">
         <v>4765</v>
@@ -2619,13 +2727,15 @@
         <v>0</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H28" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="I28" s="1" t="s">
-        <v>8</v>
+        <v>117</v>
+      </c>
+      <c r="H28" s="3">
+        <f>VLOOKUP(B28,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>5</v>
+      </c>
+      <c r="I28" s="3">
+        <f>VLOOKUP(B28,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>1</v>
       </c>
       <c r="J28" s="1">
         <v>30000</v>
@@ -2646,22 +2756,22 @@
         <v>30005</v>
       </c>
       <c r="P28" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V28" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2669,7 +2779,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="C29" s="1">
         <v>4696</v>
@@ -2678,13 +2788,15 @@
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H29" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I29" s="1" t="s">
-        <v>71</v>
+        <v>117</v>
+      </c>
+      <c r="H29" s="3">
+        <f>VLOOKUP(B29,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>18</v>
+      </c>
+      <c r="I29" s="3">
+        <f>VLOOKUP(B29,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>2</v>
       </c>
       <c r="J29" s="1">
         <v>30000</v>
@@ -2705,22 +2817,22 @@
         <v>30005</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="R29" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="T29" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="U29" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="T29" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="U29" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="V29" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2728,7 +2840,7 @@
         <v>26</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>86</v>
+        <v>74</v>
       </c>
       <c r="C30" s="1">
         <v>2902</v>
@@ -2737,13 +2849,15 @@
         <v>0</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>8</v>
+        <v>117</v>
+      </c>
+      <c r="H30" s="3">
+        <f>VLOOKUP(B30,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I30" s="3">
+        <f>VLOOKUP(B30,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>24</v>
       </c>
       <c r="J30" s="1">
         <v>30000</v>
@@ -2764,25 +2878,25 @@
         <v>30005</v>
       </c>
       <c r="P30" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q30" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="R30" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="S30" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="T30" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="U30" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="V30" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="S30" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="T30" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="U30" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="V30" s="2" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2790,7 +2904,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>87</v>
+        <v>75</v>
       </c>
       <c r="C31" s="1">
         <v>5476</v>
@@ -2802,13 +2916,15 @@
         <v>0</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H31" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I31" s="1" t="s">
-        <v>42</v>
+        <v>117</v>
+      </c>
+      <c r="H31" s="3">
+        <f>VLOOKUP(B31,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>11</v>
+      </c>
+      <c r="I31" s="3">
+        <f>VLOOKUP(B31,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>25</v>
       </c>
       <c r="J31" s="1">
         <v>30000</v>
@@ -2829,22 +2945,22 @@
         <v>30005</v>
       </c>
       <c r="P31" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>162</v>
+        <v>149</v>
       </c>
       <c r="U31" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2852,7 +2968,7 @@
         <v>27</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="C32" s="1">
         <v>5476</v>
@@ -2864,13 +2980,15 @@
         <v>0</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H32" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="I32" s="1" t="s">
-        <v>8</v>
+        <v>117</v>
+      </c>
+      <c r="H32" s="3">
+        <f>VLOOKUP(B32,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>30</v>
+      </c>
+      <c r="I32" s="3">
+        <f>VLOOKUP(B32,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>3</v>
       </c>
       <c r="J32" s="1">
         <v>30000</v>
@@ -2891,22 +3009,22 @@
         <v>30005</v>
       </c>
       <c r="P32" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="U32" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2914,7 +3032,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C33" s="1">
         <v>5293</v>
@@ -2923,13 +3041,15 @@
         <v>0</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H33" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I33" s="1" t="s">
-        <v>8</v>
+        <v>117</v>
+      </c>
+      <c r="H33" s="3">
+        <f>VLOOKUP(B33,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>22</v>
+      </c>
+      <c r="I33" s="3">
+        <f>VLOOKUP(B33,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>10</v>
       </c>
       <c r="J33" s="1">
         <v>30000</v>
@@ -2950,22 +3070,22 @@
         <v>30005</v>
       </c>
       <c r="P33" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>154</v>
+        <v>141</v>
       </c>
       <c r="U33" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2973,7 +3093,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="C34" s="1">
         <v>1912</v>
@@ -2982,13 +3102,15 @@
         <v>0</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I34" s="1" t="s">
-        <v>8</v>
+        <v>117</v>
+      </c>
+      <c r="H34" s="3">
+        <f>VLOOKUP(B34,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>6</v>
+      </c>
+      <c r="I34" s="3">
+        <f>VLOOKUP(B34,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>12</v>
       </c>
       <c r="J34" s="1">
         <v>30000</v>
@@ -3009,22 +3131,22 @@
         <v>30005</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>78</v>
+        <v>66</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>113</v>
+        <v>101</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>164</v>
+        <v>151</v>
       </c>
       <c r="U34" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -3032,7 +3154,7 @@
         <v>39</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="C35" s="1">
         <v>1912</v>
@@ -3041,13 +3163,15 @@
         <v>0</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H35" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I35" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
+      </c>
+      <c r="H35" s="3">
+        <f>VLOOKUP(B35,Sheet1!$E$2:$G$33,2,FALSE)</f>
+        <v>1</v>
+      </c>
+      <c r="I35" s="3">
+        <f>VLOOKUP(B35,Sheet1!$E$2:$G$33,3,FALSE)</f>
+        <v>29</v>
       </c>
       <c r="J35" s="1">
         <v>30000</v>
@@ -3068,22 +3192,22 @@
         <v>30005</v>
       </c>
       <c r="P35" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>126</v>
+        <v>114</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="U35" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V35" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:22" ht="57" x14ac:dyDescent="0.2">
@@ -3091,7 +3215,7 @@
         <v>41</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>117</v>
+        <v>105</v>
       </c>
       <c r="C36" s="1">
         <v>5309</v>
@@ -3106,13 +3230,13 @@
         <v>539001</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="H36" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I36" s="1" t="s">
-        <v>48</v>
+        <v>117</v>
+      </c>
+      <c r="H36" s="3">
+        <v>12</v>
+      </c>
+      <c r="I36" s="3">
+        <v>19</v>
       </c>
       <c r="J36" s="1">
         <v>30000</v>
@@ -3133,25 +3257,25 @@
         <v>30005</v>
       </c>
       <c r="P36" s="1" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="Q36" s="1" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="R36" s="2" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="S36" s="2" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="T36" s="2" t="s">
-        <v>156</v>
+        <v>143</v>
       </c>
       <c r="U36" s="2" t="s">
-        <v>120</v>
+        <v>108</v>
       </c>
       <c r="V36" s="2" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -3159,4 +3283,367 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="E2:G33"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="2" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E2" t="s">
+        <v>159</v>
+      </c>
+      <c r="F2">
+        <v>13</v>
+      </c>
+      <c r="G2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E3" t="s">
+        <v>160</v>
+      </c>
+      <c r="F3">
+        <v>24</v>
+      </c>
+      <c r="G3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E4" t="s">
+        <v>161</v>
+      </c>
+      <c r="F4">
+        <v>25</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E5" t="s">
+        <v>162</v>
+      </c>
+      <c r="F5">
+        <v>8</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E6" t="s">
+        <v>163</v>
+      </c>
+      <c r="F6">
+        <v>4</v>
+      </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E7" t="s">
+        <v>164</v>
+      </c>
+      <c r="F7">
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E8" t="s">
+        <v>165</v>
+      </c>
+      <c r="F8">
+        <v>23</v>
+      </c>
+      <c r="G8">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="9" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E9" t="s">
+        <v>166</v>
+      </c>
+      <c r="F9">
+        <v>21</v>
+      </c>
+      <c r="G9">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="10" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E10" t="s">
+        <v>167</v>
+      </c>
+      <c r="F10">
+        <v>29</v>
+      </c>
+      <c r="G10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E11" t="s">
+        <v>168</v>
+      </c>
+      <c r="F11">
+        <v>26</v>
+      </c>
+      <c r="G11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E12" t="s">
+        <v>169</v>
+      </c>
+      <c r="F12">
+        <v>16</v>
+      </c>
+      <c r="G12">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E13" t="s">
+        <v>170</v>
+      </c>
+      <c r="F13">
+        <v>3</v>
+      </c>
+      <c r="G13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E14" t="s">
+        <v>171</v>
+      </c>
+      <c r="F14">
+        <v>28</v>
+      </c>
+      <c r="G14">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E15" t="s">
+        <v>172</v>
+      </c>
+      <c r="F15">
+        <v>19</v>
+      </c>
+      <c r="G15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E16" t="s">
+        <v>173</v>
+      </c>
+      <c r="F16">
+        <v>20</v>
+      </c>
+      <c r="G16">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E17" t="s">
+        <v>174</v>
+      </c>
+      <c r="F17">
+        <v>16</v>
+      </c>
+      <c r="G17">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="18" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E18" t="s">
+        <v>175</v>
+      </c>
+      <c r="F18">
+        <v>5</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E19" t="s">
+        <v>176</v>
+      </c>
+      <c r="F19">
+        <v>17</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E20" t="s">
+        <v>177</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E21" t="s">
+        <v>178</v>
+      </c>
+      <c r="F21">
+        <v>30</v>
+      </c>
+      <c r="G21">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="22" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E22" t="s">
+        <v>179</v>
+      </c>
+      <c r="F22">
+        <v>11</v>
+      </c>
+      <c r="G22">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E23" t="s">
+        <v>180</v>
+      </c>
+      <c r="F23">
+        <v>27</v>
+      </c>
+      <c r="G23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E24" t="s">
+        <v>181</v>
+      </c>
+      <c r="F24">
+        <v>22</v>
+      </c>
+      <c r="G24">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="25" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E25" t="s">
+        <v>182</v>
+      </c>
+      <c r="F25">
+        <v>9</v>
+      </c>
+      <c r="G25">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="26" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E26" t="s">
+        <v>183</v>
+      </c>
+      <c r="F26">
+        <v>6</v>
+      </c>
+      <c r="G26">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="27" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E27" t="s">
+        <v>184</v>
+      </c>
+      <c r="F27">
+        <v>18</v>
+      </c>
+      <c r="G27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E28" t="s">
+        <v>185</v>
+      </c>
+      <c r="F28">
+        <v>2</v>
+      </c>
+      <c r="G28">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E29" t="s">
+        <v>186</v>
+      </c>
+      <c r="F29">
+        <v>14</v>
+      </c>
+      <c r="G29">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="30" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E30" t="s">
+        <v>187</v>
+      </c>
+      <c r="F30">
+        <v>26</v>
+      </c>
+      <c r="G30">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E31" t="s">
+        <v>188</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="32" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E32" t="s">
+        <v>189</v>
+      </c>
+      <c r="F32">
+        <v>15</v>
+      </c>
+      <c r="G32">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="33" spans="5:7" x14ac:dyDescent="0.2">
+      <c r="E33" t="s">
+        <v>190</v>
+      </c>
+      <c r="F33">
+        <v>12</v>
+      </c>
+      <c r="G33">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/Datas/NPCBehaviorData.xlsx
+++ b/Datas/NPCBehaviorData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="353" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="191">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -1269,7 +1269,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="5" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1282,9 +1282,6 @@
       <c r="E5" s="1">
         <v>0</v>
       </c>
-      <c r="G5" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="H5" s="3">
         <v>0</v>
       </c>
@@ -1308,9 +1305,6 @@
       </c>
       <c r="O5" s="1">
         <v>0</v>
-      </c>
-      <c r="P5" s="1" t="s">
-        <v>35</v>
       </c>
       <c r="Q5" s="2"/>
     </row>

--- a/Datas/NPCBehaviorData.xlsx
+++ b/Datas/NPCBehaviorData.xlsx
@@ -418,10 +418,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>5476,1001440</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>5293,1001490</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -464,10 +460,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>3056,1019972</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>2180,1165443</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -715,6 +707,14 @@
   </si>
   <si>
     <t>艾德文娜</t>
+  </si>
+  <si>
+    <t>5476,1184901</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3056,1182578</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1089,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>0</v>
@@ -1131,7 +1131,7 @@
         <v>20</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="U2" s="2" t="s">
         <v>21</v>
@@ -1151,22 +1151,22 @@
         <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>1</v>
@@ -1196,10 +1196,10 @@
         <v>28</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>29</v>
@@ -1222,7 +1222,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H4" s="3">
         <f>VLOOKUP(B4,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1251,22 +1251,22 @@
         <v>30005</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>34</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
@@ -1322,7 +1322,7 @@
         <v>948</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H6" s="3">
         <f>VLOOKUP(B6,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1363,13 +1363,13 @@
         <v>39</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="U6" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V6" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1386,7 +1386,7 @@
         <v>948</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H7" s="3">
         <f>VLOOKUP(B7,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1427,13 +1427,13 @@
         <v>43</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="U7" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V7" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1450,7 +1450,7 @@
         <v>900</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H8" s="3">
         <f>VLOOKUP(B8,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1491,13 +1491,13 @@
         <v>46</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="U8" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V8" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1514,7 +1514,7 @@
         <v>900</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H9" s="3">
         <f>VLOOKUP(B9,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1555,13 +1555,13 @@
         <v>46</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="U9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V9" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1581,7 +1581,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H10" s="3">
         <f>VLOOKUP(B10,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1613,19 +1613,19 @@
         <v>35</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R10" s="2" t="s">
         <v>80</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="U10" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V10" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="85.5" x14ac:dyDescent="0.2">
@@ -1645,7 +1645,7 @@
         <v>3115</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H11" s="3">
         <f>VLOOKUP(B11,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1686,13 +1686,13 @@
         <v>7</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="U11" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V11" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1712,7 +1712,7 @@
         <v>3115</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H12" s="3">
         <f>VLOOKUP(B12,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1753,13 +1753,13 @@
         <v>7</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="U12" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V12" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -1776,7 +1776,7 @@
         <v>4800</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H13" s="3">
         <f>VLOOKUP(B13,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1811,19 +1811,19 @@
         <v>49</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="U13" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V13" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1840,7 +1840,7 @@
         <v>1014</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H14" s="3">
         <f>VLOOKUP(B14,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1881,13 +1881,13 @@
         <v>15</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="U14" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V14" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V14" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1904,7 +1904,7 @@
         <v>2180</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H15" s="3">
         <f>VLOOKUP(B15,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1942,16 +1942,16 @@
         <v>83</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="U15" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V15" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V15" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="57" x14ac:dyDescent="0.2">
@@ -1968,7 +1968,7 @@
         <v>2180</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H16" s="3">
         <f>VLOOKUP(B16,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2009,13 +2009,13 @@
         <v>58</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="U16" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V16" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V16" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2032,7 +2032,7 @@
         <v>2180</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H17" s="3">
         <f>VLOOKUP(B17,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2070,16 +2070,16 @@
         <v>85</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="U17" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V17" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2096,7 +2096,7 @@
         <v>1014</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H18" s="3">
         <f>VLOOKUP(B18,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2128,19 +2128,19 @@
         <v>32</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="U18" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V18" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V18" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -2157,7 +2157,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H19" s="3">
         <f>VLOOKUP(B19,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2189,19 +2189,19 @@
         <v>35</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R19" s="2" t="s">
         <v>86</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="U19" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V19" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V19" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2218,7 +2218,7 @@
         <v>5013</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H20" s="3">
         <f>VLOOKUP(B20,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2259,13 +2259,13 @@
         <v>63</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="U20" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V20" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V20" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2282,7 +2282,7 @@
         <v>5013</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H21" s="3">
         <f>VLOOKUP(B21,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2323,13 +2323,13 @@
         <v>11</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="U21" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V21" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V21" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2346,7 +2346,7 @@
         <v>1756</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H22" s="3">
         <f>VLOOKUP(B22,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2387,13 +2387,13 @@
         <v>67</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="U22" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V22" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V22" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="57" x14ac:dyDescent="0.2">
@@ -2410,7 +2410,7 @@
         <v>1756</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H23" s="3">
         <f>VLOOKUP(B23,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2451,13 +2451,13 @@
         <v>69</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="U23" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V23" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V23" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="57" x14ac:dyDescent="0.2">
@@ -2474,7 +2474,7 @@
         <v>3297</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H24" s="3">
         <f>VLOOKUP(B24,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2506,19 +2506,19 @@
         <v>35</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R24" s="2" t="s">
         <v>91</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="U24" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V24" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V24" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2535,7 +2535,7 @@
         <v>3056</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H25" s="3">
         <f>VLOOKUP(B25,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2573,16 +2573,16 @@
         <v>92</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>111</v>
+        <v>190</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="U25" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V25" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V25" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -2599,7 +2599,7 @@
         <v>3056</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H26" s="3">
         <f>VLOOKUP(B26,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2631,19 +2631,19 @@
         <v>35</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R26" s="2" t="s">
         <v>93</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="U26" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V26" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V26" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="71.25" x14ac:dyDescent="0.2">
@@ -2660,7 +2660,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H27" s="3">
         <f>VLOOKUP(B27,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2692,19 +2692,19 @@
         <v>35</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R27" s="2" t="s">
         <v>94</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="U27" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V27" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V27" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -2721,7 +2721,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H28" s="3">
         <f>VLOOKUP(B28,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2753,19 +2753,19 @@
         <v>35</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R28" s="2" t="s">
         <v>95</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="U28" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V28" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V28" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2782,7 +2782,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H29" s="3">
         <f>VLOOKUP(B29,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2814,19 +2814,19 @@
         <v>56</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R29" s="2" t="s">
         <v>96</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="U29" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V29" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V29" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2843,7 +2843,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H30" s="3">
         <f>VLOOKUP(B30,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2884,13 +2884,13 @@
         <v>14</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="U30" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V30" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V30" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2910,7 +2910,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H31" s="3">
         <f>VLOOKUP(B31,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2942,19 +2942,19 @@
         <v>35</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R31" s="2" t="s">
         <v>98</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="U31" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V31" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V31" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2974,7 +2974,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H32" s="3">
         <f>VLOOKUP(B32,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -3006,19 +3006,19 @@
         <v>35</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>99</v>
+        <v>189</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="U32" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V32" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V32" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -3035,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H33" s="3">
         <f>VLOOKUP(B33,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -3067,19 +3067,19 @@
         <v>35</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="U33" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V33" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V33" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -3096,7 +3096,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H34" s="3">
         <f>VLOOKUP(B34,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -3128,19 +3128,19 @@
         <v>66</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="U34" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V34" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V34" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="35" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -3157,7 +3157,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H35" s="3">
         <f>VLOOKUP(B35,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -3189,19 +3189,19 @@
         <v>35</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="U35" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="V35" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V35" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
     <row r="36" spans="1:22" ht="57" x14ac:dyDescent="0.2">
@@ -3209,7 +3209,7 @@
         <v>41</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C36" s="1">
         <v>5309</v>
@@ -3224,7 +3224,7 @@
         <v>539001</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="H36" s="3">
         <v>12</v>
@@ -3257,19 +3257,19 @@
         <v>33</v>
       </c>
       <c r="R36" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="S36" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="S36" s="2" t="s">
+      <c r="T36" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="U36" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="T36" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="U36" s="2" t="s">
+      <c r="V36" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="V36" s="2" t="s">
-        <v>109</v>
       </c>
     </row>
   </sheetData>
@@ -3286,7 +3286,7 @@
   <sheetData>
     <row r="2" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E2" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F2">
         <v>13</v>
@@ -3297,7 +3297,7 @@
     </row>
     <row r="3" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="F3">
         <v>24</v>
@@ -3308,7 +3308,7 @@
     </row>
     <row r="4" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E4" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F4">
         <v>25</v>
@@ -3319,7 +3319,7 @@
     </row>
     <row r="5" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E5" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F5">
         <v>8</v>
@@ -3330,7 +3330,7 @@
     </row>
     <row r="6" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E6" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -3341,7 +3341,7 @@
     </row>
     <row r="7" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E7" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F7">
         <v>10</v>
@@ -3352,7 +3352,7 @@
     </row>
     <row r="8" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F8">
         <v>23</v>
@@ -3363,7 +3363,7 @@
     </row>
     <row r="9" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E9" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="F9">
         <v>21</v>
@@ -3374,7 +3374,7 @@
     </row>
     <row r="10" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E10" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F10">
         <v>29</v>
@@ -3385,7 +3385,7 @@
     </row>
     <row r="11" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E11" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="F11">
         <v>26</v>
@@ -3396,7 +3396,7 @@
     </row>
     <row r="12" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E12" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F12">
         <v>16</v>
@@ -3407,7 +3407,7 @@
     </row>
     <row r="13" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E13" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="F13">
         <v>3</v>
@@ -3418,7 +3418,7 @@
     </row>
     <row r="14" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E14" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="F14">
         <v>28</v>
@@ -3429,7 +3429,7 @@
     </row>
     <row r="15" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E15" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="F15">
         <v>19</v>
@@ -3440,7 +3440,7 @@
     </row>
     <row r="16" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E16" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="F16">
         <v>20</v>
@@ -3451,7 +3451,7 @@
     </row>
     <row r="17" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E17" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="F17">
         <v>16</v>
@@ -3462,7 +3462,7 @@
     </row>
     <row r="18" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E18" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -3473,7 +3473,7 @@
     </row>
     <row r="19" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E19" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="F19">
         <v>17</v>
@@ -3484,7 +3484,7 @@
     </row>
     <row r="20" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E20" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -3495,7 +3495,7 @@
     </row>
     <row r="21" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E21" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="F21">
         <v>30</v>
@@ -3506,7 +3506,7 @@
     </row>
     <row r="22" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E22" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="F22">
         <v>11</v>
@@ -3517,7 +3517,7 @@
     </row>
     <row r="23" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E23" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F23">
         <v>27</v>
@@ -3528,7 +3528,7 @@
     </row>
     <row r="24" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E24" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F24">
         <v>22</v>
@@ -3539,7 +3539,7 @@
     </row>
     <row r="25" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E25" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="F25">
         <v>9</v>
@@ -3550,7 +3550,7 @@
     </row>
     <row r="26" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E26" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F26">
         <v>6</v>
@@ -3561,7 +3561,7 @@
     </row>
     <row r="27" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E27" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F27">
         <v>18</v>
@@ -3572,7 +3572,7 @@
     </row>
     <row r="28" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E28" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F28">
         <v>2</v>
@@ -3583,7 +3583,7 @@
     </row>
     <row r="29" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E29" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F29">
         <v>14</v>
@@ -3594,7 +3594,7 @@
     </row>
     <row r="30" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E30" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F30">
         <v>26</v>
@@ -3605,7 +3605,7 @@
     </row>
     <row r="31" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E31" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -3616,7 +3616,7 @@
     </row>
     <row r="32" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E32" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F32">
         <v>15</v>
@@ -3627,7 +3627,7 @@
     </row>
     <row r="33" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E33" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F33">
         <v>12</v>

--- a/Datas/NPCBehaviorData.xlsx
+++ b/Datas/NPCBehaviorData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="351" uniqueCount="189">
   <si>
     <t>int</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -254,10 +254,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>2180,1166370</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>奥蒂莉亚</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -290,18 +286,10 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1756,1019120</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>布拉德利</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1756,1019120</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>布蓝达</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -714,6 +702,10 @@
   </si>
   <si>
     <t>3056,1182578</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1756,1181866</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1089,10 +1081,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>0</v>
@@ -1131,7 +1123,7 @@
         <v>20</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="U2" s="2" t="s">
         <v>21</v>
@@ -1151,22 +1143,22 @@
         <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>120</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>1</v>
@@ -1196,10 +1188,10 @@
         <v>28</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>29</v>
@@ -1222,7 +1214,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H4" s="3">
         <f>VLOOKUP(B4,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1251,22 +1243,22 @@
         <v>30005</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>34</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
@@ -1322,7 +1314,7 @@
         <v>948</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H6" s="3">
         <f>VLOOKUP(B6,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1363,13 +1355,13 @@
         <v>39</v>
       </c>
       <c r="T6" s="2" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="U6" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V6" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1386,7 +1378,7 @@
         <v>948</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H7" s="3">
         <f>VLOOKUP(B7,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1427,13 +1419,13 @@
         <v>43</v>
       </c>
       <c r="T7" s="2" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="U7" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V7" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1450,7 +1442,7 @@
         <v>900</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H8" s="3">
         <f>VLOOKUP(B8,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1491,13 +1483,13 @@
         <v>46</v>
       </c>
       <c r="T8" s="2" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="U8" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V8" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1514,7 +1506,7 @@
         <v>900</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H9" s="3">
         <f>VLOOKUP(B9,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1555,13 +1547,13 @@
         <v>46</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="U9" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V9" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1581,7 +1573,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H10" s="3">
         <f>VLOOKUP(B10,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1613,19 +1605,19 @@
         <v>35</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="U10" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V10" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="85.5" x14ac:dyDescent="0.2">
@@ -1645,7 +1637,7 @@
         <v>3115</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H11" s="3">
         <f>VLOOKUP(B11,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1680,19 +1672,19 @@
         <v>49</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c r="U11" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V11" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1712,7 +1704,7 @@
         <v>3115</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H12" s="3">
         <f>VLOOKUP(B12,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1747,19 +1739,19 @@
         <v>33</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="U12" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V12" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -1776,7 +1768,7 @@
         <v>4800</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H13" s="3">
         <f>VLOOKUP(B13,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1811,19 +1803,19 @@
         <v>49</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="U13" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V13" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1831,7 +1823,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C14" s="1">
         <v>1112</v>
@@ -1840,7 +1832,7 @@
         <v>1014</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H14" s="3">
         <f>VLOOKUP(B14,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1881,13 +1873,13 @@
         <v>15</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="U14" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V14" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1904,7 +1896,7 @@
         <v>2180</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H15" s="3">
         <f>VLOOKUP(B15,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1939,19 +1931,19 @@
         <v>37</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="U15" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V15" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="57" x14ac:dyDescent="0.2">
@@ -1968,7 +1960,7 @@
         <v>2180</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H16" s="3">
         <f>VLOOKUP(B16,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2003,19 +1995,19 @@
         <v>33</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>58</v>
+        <v>107</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="U16" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V16" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2032,7 +2024,7 @@
         <v>2180</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H17" s="3">
         <f>VLOOKUP(B17,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2067,19 +2059,19 @@
         <v>33</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="U17" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V17" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2087,7 +2079,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C18" s="1">
         <v>1112</v>
@@ -2096,7 +2088,7 @@
         <v>1014</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H18" s="3">
         <f>VLOOKUP(B18,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2128,19 +2120,19 @@
         <v>32</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="R18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="U18" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V18" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -2148,7 +2140,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C19" s="1">
         <v>4918</v>
@@ -2157,7 +2149,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H19" s="3">
         <f>VLOOKUP(B19,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2189,19 +2181,19 @@
         <v>35</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="U19" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V19" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2209,7 +2201,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C20" s="1">
         <v>5013</v>
@@ -2218,7 +2210,7 @@
         <v>5013</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H20" s="3">
         <f>VLOOKUP(B20,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2253,19 +2245,19 @@
         <v>33</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="U20" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V20" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2273,7 +2265,7 @@
         <v>38</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C21" s="1">
         <v>5013</v>
@@ -2282,7 +2274,7 @@
         <v>5013</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H21" s="3">
         <f>VLOOKUP(B21,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2317,19 +2309,19 @@
         <v>33</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="S21" s="2" t="s">
         <v>11</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="U21" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V21" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2337,7 +2329,7 @@
         <v>37</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C22" s="1">
         <v>1856</v>
@@ -2346,7 +2338,7 @@
         <v>1756</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H22" s="3">
         <f>VLOOKUP(B22,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2375,25 +2367,25 @@
         <v>30005</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q22" s="1" t="s">
         <v>41</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>67</v>
+        <v>188</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="U22" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V22" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="57" x14ac:dyDescent="0.2">
@@ -2401,7 +2393,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C23" s="1">
         <v>1856</v>
@@ -2410,7 +2402,7 @@
         <v>1756</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H23" s="3">
         <f>VLOOKUP(B23,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2445,19 +2437,19 @@
         <v>33</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>69</v>
+        <v>188</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="U23" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V23" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="57" x14ac:dyDescent="0.2">
@@ -2465,7 +2457,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C24" s="1">
         <v>3300</v>
@@ -2474,7 +2466,7 @@
         <v>3297</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H24" s="3">
         <f>VLOOKUP(B24,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2506,19 +2498,19 @@
         <v>35</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>133</v>
+        <v>130</v>
       </c>
       <c r="U24" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V24" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2535,7 +2527,7 @@
         <v>3056</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H25" s="3">
         <f>VLOOKUP(B25,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2570,19 +2562,19 @@
         <v>33</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="U25" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V25" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -2599,7 +2591,7 @@
         <v>3056</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H26" s="3">
         <f>VLOOKUP(B26,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2631,19 +2623,19 @@
         <v>35</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="U26" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V26" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="71.25" x14ac:dyDescent="0.2">
@@ -2651,7 +2643,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C27" s="1">
         <v>2015</v>
@@ -2660,7 +2652,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H27" s="3">
         <f>VLOOKUP(B27,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2692,19 +2684,19 @@
         <v>35</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="U27" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V27" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -2712,7 +2704,7 @@
         <v>24</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="C28" s="1">
         <v>4765</v>
@@ -2721,7 +2713,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H28" s="3">
         <f>VLOOKUP(B28,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2753,19 +2745,19 @@
         <v>35</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="U28" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V28" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2773,7 +2765,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C29" s="1">
         <v>4696</v>
@@ -2782,7 +2774,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H29" s="3">
         <f>VLOOKUP(B29,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2814,19 +2806,19 @@
         <v>56</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="U29" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V29" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2834,7 +2826,7 @@
         <v>26</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="C30" s="1">
         <v>2902</v>
@@ -2843,7 +2835,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H30" s="3">
         <f>VLOOKUP(B30,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2878,19 +2870,19 @@
         <v>33</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="S30" s="2" t="s">
         <v>14</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="U30" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V30" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2898,7 +2890,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="C31" s="1">
         <v>5476</v>
@@ -2910,7 +2902,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H31" s="3">
         <f>VLOOKUP(B31,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2942,19 +2934,19 @@
         <v>35</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="U31" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V31" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2962,7 +2954,7 @@
         <v>27</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C32" s="1">
         <v>5476</v>
@@ -2974,7 +2966,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H32" s="3">
         <f>VLOOKUP(B32,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -3006,19 +2998,19 @@
         <v>35</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="U32" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V32" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -3026,7 +3018,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="C33" s="1">
         <v>5293</v>
@@ -3035,7 +3027,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H33" s="3">
         <f>VLOOKUP(B33,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -3067,19 +3059,19 @@
         <v>35</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="U33" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V33" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -3087,7 +3079,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C34" s="1">
         <v>1912</v>
@@ -3096,7 +3088,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H34" s="3">
         <f>VLOOKUP(B34,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -3125,22 +3117,22 @@
         <v>30005</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="U34" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V34" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -3148,7 +3140,7 @@
         <v>39</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="C35" s="1">
         <v>1912</v>
@@ -3157,7 +3149,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H35" s="3">
         <f>VLOOKUP(B35,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -3189,19 +3181,19 @@
         <v>35</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="U35" s="2" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="V35" s="2" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:22" ht="57" x14ac:dyDescent="0.2">
@@ -3209,7 +3201,7 @@
         <v>41</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="C36" s="1">
         <v>5309</v>
@@ -3224,7 +3216,7 @@
         <v>539001</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="H36" s="3">
         <v>12</v>
@@ -3257,19 +3249,19 @@
         <v>33</v>
       </c>
       <c r="R36" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="S36" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T36" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="U36" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="V36" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="S36" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="T36" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="U36" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="V36" s="2" t="s">
-        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -3286,7 +3278,7 @@
   <sheetData>
     <row r="2" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E2" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="F2">
         <v>13</v>
@@ -3297,7 +3289,7 @@
     </row>
     <row r="3" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="F3">
         <v>24</v>
@@ -3308,7 +3300,7 @@
     </row>
     <row r="4" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E4" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="F4">
         <v>25</v>
@@ -3319,7 +3311,7 @@
     </row>
     <row r="5" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E5" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="F5">
         <v>8</v>
@@ -3330,7 +3322,7 @@
     </row>
     <row r="6" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E6" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -3341,7 +3333,7 @@
     </row>
     <row r="7" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E7" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F7">
         <v>10</v>
@@ -3352,7 +3344,7 @@
     </row>
     <row r="8" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E8" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="F8">
         <v>23</v>
@@ -3363,7 +3355,7 @@
     </row>
     <row r="9" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E9" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="F9">
         <v>21</v>
@@ -3374,7 +3366,7 @@
     </row>
     <row r="10" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E10" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="F10">
         <v>29</v>
@@ -3385,7 +3377,7 @@
     </row>
     <row r="11" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E11" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="F11">
         <v>26</v>
@@ -3396,7 +3388,7 @@
     </row>
     <row r="12" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E12" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="F12">
         <v>16</v>
@@ -3407,7 +3399,7 @@
     </row>
     <row r="13" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E13" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F13">
         <v>3</v>
@@ -3418,7 +3410,7 @@
     </row>
     <row r="14" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E14" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F14">
         <v>28</v>
@@ -3429,7 +3421,7 @@
     </row>
     <row r="15" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E15" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="F15">
         <v>19</v>
@@ -3440,7 +3432,7 @@
     </row>
     <row r="16" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E16" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="F16">
         <v>20</v>
@@ -3451,7 +3443,7 @@
     </row>
     <row r="17" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E17" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="F17">
         <v>16</v>
@@ -3462,7 +3454,7 @@
     </row>
     <row r="18" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E18" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -3473,7 +3465,7 @@
     </row>
     <row r="19" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E19" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="F19">
         <v>17</v>
@@ -3484,7 +3476,7 @@
     </row>
     <row r="20" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E20" t="s">
-        <v>175</v>
+        <v>172</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -3495,7 +3487,7 @@
     </row>
     <row r="21" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E21" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="F21">
         <v>30</v>
@@ -3506,7 +3498,7 @@
     </row>
     <row r="22" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E22" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="F22">
         <v>11</v>
@@ -3517,7 +3509,7 @@
     </row>
     <row r="23" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E23" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F23">
         <v>27</v>
@@ -3528,7 +3520,7 @@
     </row>
     <row r="24" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E24" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="F24">
         <v>22</v>
@@ -3539,7 +3531,7 @@
     </row>
     <row r="25" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E25" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="F25">
         <v>9</v>
@@ -3550,7 +3542,7 @@
     </row>
     <row r="26" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E26" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="F26">
         <v>6</v>
@@ -3561,7 +3553,7 @@
     </row>
     <row r="27" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E27" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="F27">
         <v>18</v>
@@ -3572,7 +3564,7 @@
     </row>
     <row r="28" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E28" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="F28">
         <v>2</v>
@@ -3583,7 +3575,7 @@
     </row>
     <row r="29" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E29" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F29">
         <v>14</v>
@@ -3594,7 +3586,7 @@
     </row>
     <row r="30" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E30" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="F30">
         <v>26</v>
@@ -3605,7 +3597,7 @@
     </row>
     <row r="31" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E31" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -3616,7 +3608,7 @@
     </row>
     <row r="32" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E32" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="F32">
         <v>15</v>
@@ -3627,7 +3619,7 @@
     </row>
     <row r="33" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E33" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="F33">
         <v>12</v>

--- a/Datas/NPCBehaviorData.xlsx
+++ b/Datas/NPCBehaviorData.xlsx
@@ -174,538 +174,538 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>948,1068306</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布莱兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,1,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>948,1071156</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>948,1068306</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>丝特芬妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900,1081513</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900,1079546</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>格吉尔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>0,1,2,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>900,1080132</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>琼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强尼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希拉</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>夏佐</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>希尔达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5013,1154408</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>莱特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布拉德利</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>布蓝达</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>帕特里克</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿普敦</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>摩尔根</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>考波特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>马勒第兹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5170,1156253</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5170,1156284</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5170,1156900</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2270,1167153</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2270,1166370</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2270,1167418</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4918,1147517</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5013,1153081</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5013,1153488</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1856,1071058</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1856,1080475</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3300,1070049</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3056,1166131</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3056,1166294</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2015,1071591</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4765,1139029</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4696,1042715</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2902,1168177</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5476,1162796</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5293,1001490</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1912,1080779</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1912,1080613</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4800,1144907</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>纺织婆婆</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5309,1081691</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5309,1159783</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6,0,9,0,9,0,17,30,17,30,19,30,19,30, 22,0,22,0,24,0</t>
+  </si>
+  <si>
+    <t>60001,60002,60003,60004,60005</t>
+  </si>
+  <si>
+    <t>6,0,9,0,9,0,17,30,17,30,19,30,19,30, 22,0,22,0,24,0</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2180,1165443</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>4800,1143244</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10,11,12,3</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>workMap</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int2&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000,500|1001,500|1002,500|1003,500|1004,500|1005,500|1006,500|1007,500|1008,500|1009,500|1010,500|1011,500</t>
+  </si>
+  <si>
+    <t>workItems</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>homeAreas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>visitShops</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>List&lt;int&gt;</t>
+  </si>
+  <si>
+    <t>workMapAreas</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>npcFriends</t>
+  </si>
+  <si>
+    <t>List&lt;int2&gt;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|27,100|30,100|35,100|36,100|39,100|41,100|37,100</t>
+  </si>
+  <si>
+    <t>3,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|27,100|30,100|35,100|36,100|39,100|41,100|7,100|18,100|24,100|16,100|17,100</t>
+  </si>
+  <si>
+    <t>5,100|12,100|14,100|16,100|17,100|21,100|22,100|24,100|36,100|38,100|41,100|40,100|23,100|10,100</t>
+  </si>
+  <si>
+    <t>5,100|3,100|10,100|17,100|12,100|6,100|23,100|25,100|26,100|28,100|29,100|30,100|32,100|35,100|39,100|41,100</t>
+  </si>
+  <si>
+    <t>5,100|3,100|27,100|35,100|39,100|41,100|25,100|29,100</t>
+  </si>
+  <si>
+    <t>3,100|5,100|7,100|10,100|12,100|16,100|17,100|18,100|21,100|22,100|36,100|14,100|38,100|41,100|23,100</t>
+  </si>
+  <si>
+    <t>3,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|27,100|30,100|35,100|5,100|39,100|41,100|7,100|18,100|24,100|16,100|17,100</t>
+  </si>
+  <si>
+    <t>3,100|5,100|7,100|10,100|12,100|16,100|17,100|18,100|21,100|22,100|36,100|38,100|40,100|41,100|23,100</t>
+  </si>
+  <si>
+    <t>12,100|21,100|35,100|41,100|5,100|25,100</t>
+  </si>
+  <si>
+    <t>3,100|5,100|7,100|10,100|12,100|16,100|17,100|18,100|21,100|22,100|36,100|14,100|40,100|41,100|23,100</t>
+  </si>
+  <si>
+    <t>3,100|5,100|6,100|7,100|10,100|9,100|12,100|16,100|17,100|18,100|23,100|27,100|28,100|29,100|30,100|35,100|36,100|37,100|39,100|41,100</t>
+  </si>
+  <si>
+    <t>5,100|12,100|14,100|16,100|17,100|21,100|7,100|24,100|36,100|38,100|41,100|40,100|23,100|10,100</t>
+  </si>
+  <si>
+    <t>12,100|41,100|35,100|21,100|5,100|29,100|3,100|27,100|39,100</t>
+  </si>
+  <si>
+    <t>10,100|12,100|21,100|35,100|41,100|5,100|25,100</t>
+  </si>
+  <si>
+    <t>5,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|27,100|30,100|3,100|36,100|39,100|41,100|37,100</t>
+  </si>
+  <si>
+    <t>5,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|3,100|30,100|35,100|36,100|39,100|41,100|37,100</t>
+  </si>
+  <si>
+    <t>5,100|3,100|10,100|17,100|12,100|6,100|23,100|25,100|26,100|28,100|29,100|9,100|32,100|35,100|39,100|41,100</t>
+  </si>
+  <si>
+    <t>5,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|27,100|30,100|35,100|36,100|3,100|41,100|37,100</t>
+  </si>
+  <si>
+    <t>3,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|27,100|30,100|35,100|36,100|39,100|5,100|7,100|18,100|24,100|16,100|17,100</t>
+  </si>
+  <si>
+    <t>8,100|9,100|10,100|12,100|14,100|16,100|18,100|19,100|22,100|23,100|26,100|28,100|30,100|34,100|38,100|41,100|40,100</t>
+  </si>
+  <si>
+    <t>3,100|5,100|6,100|7,100|8,100|9,100|10,100|12,100|14,100|16,100|17,100|18,100|19,100|21,100|22,100|23,100|24,100|25,100|26,100|27,100|28,100|29,100|30,100|31,100|34,100|35,100|36,100|37,100|38,100|39,100|40,100|41,100</t>
+  </si>
+  <si>
+    <t>3,100|5,100|6,100|8,100|9,100|10,100|12,100|21,100|23,100|26,100|27,100|28,100|29,100|30,100|34,100|35,100|36,100|37,100|39,100|41,100</t>
+  </si>
+  <si>
+    <t>3,100|5,100|6,100|7,100|9,100|10,100|12,100|16,100|17,100|18,100|19,100|21,100|25,100|26,100|27,100|28,100|29,100|30,100|31,100|34,100|35,100|36,100|37,100|39,100|41,100</t>
+  </si>
+  <si>
+    <t>8,100|9,100|10,100|12,100|14,100|16,100|18,100|19,100|6,100|22,100|23,100|28,100|30,100|34,100|38,100|41,100|40,100</t>
+  </si>
+  <si>
+    <t>3,100|6,100|9,100|12,100|18,100|19,100|21,100|22,100|26,100|27,100|8,100|30,100|29,100|34,100|35,100|39,100|41,100|31,100</t>
+  </si>
+  <si>
+    <t>3,100|6,100|9,100|12,100|18,100|19,100|21,100|22,100|26,100|27,100|28,100|30,100|29,100|34,100|35,100|39,100|41,100|8,100</t>
+  </si>
+  <si>
+    <t>3,100|6,100|9,100|12,100|18,100|19,100|21,100|22,100|26,100|27,100|28,100|30,100|29,100|31,100|35,100|39,100|41,100|8,100</t>
+  </si>
+  <si>
+    <t>3,100|6,100|9,100|12,100|18,100|19,100|21,100|22,100|26,100|27,100|28,100|30,100|29,100|34,100|35,100|39,100|41,100|31,100</t>
+  </si>
+  <si>
+    <t>8,100|9,100|10,100|12,100|14,100|16,100|18,100|19,100|22,100|23,100|28,100|30,100|34,100|38,100|41,100|40,100</t>
+  </si>
+  <si>
+    <t>3,100|5,100|7,100|10,100|12,100|16,100|17,100|18,100|21,100|22,100|36,100|38,100|40,100|41,100|14,100|23,100|30,100|39,100</t>
+  </si>
+  <si>
+    <t>3,100|5,100|7,100|10,100|12,100|16,100|18,100|21,100|22,100|36,100|38,100|40,100|41,100|14,100|23,100|30,100|39,100</t>
+  </si>
+  <si>
+    <t>3,100|5,100|7,100|10,100|12,100|16,100|21,100|22,100|36,100|38,100|40,100|41,100|14,100|23,100|30,100|39,100|17,100</t>
+  </si>
+  <si>
+    <t>likeItem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unLikeItem</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>班尼迪克</t>
+  </si>
+  <si>
+    <t>玛德琳</t>
+  </si>
+  <si>
+    <t>布莱兹</t>
+  </si>
+  <si>
+    <t>丝特芬妮</t>
+  </si>
+  <si>
+    <t>格吉尔</t>
+  </si>
+  <si>
+    <t>亚度尼斯</t>
+  </si>
+  <si>
+    <t>琼</t>
+  </si>
+  <si>
+    <t>占卜婆婆</t>
+  </si>
+  <si>
+    <t>奥蒂莉亚</t>
+  </si>
+  <si>
+    <t>坎蒂丝</t>
+  </si>
+  <si>
+    <t>希拉</t>
+  </si>
+  <si>
+    <t>希尔达</t>
+  </si>
+  <si>
+    <t>布拉德利</t>
+  </si>
+  <si>
+    <t>布蓝达</t>
+  </si>
+  <si>
+    <t>希贝儿</t>
+  </si>
+  <si>
+    <t>帕特里克</t>
+  </si>
+  <si>
+    <t>朵儿洁</t>
+  </si>
+  <si>
+    <t>梅林</t>
+  </si>
+  <si>
+    <t>摩尔根</t>
+  </si>
+  <si>
+    <t>马勒第兹</t>
+  </si>
+  <si>
+    <t>考波特</t>
+  </si>
+  <si>
+    <t>夏佐</t>
+  </si>
+  <si>
+    <t>爱格伯特</t>
+  </si>
+  <si>
+    <t>强尼</t>
+  </si>
+  <si>
+    <t>瓦尔特</t>
+  </si>
+  <si>
+    <t>阿普敦</t>
+  </si>
+  <si>
+    <t>艾琳娜</t>
+  </si>
+  <si>
+    <t>莱特</t>
+  </si>
+  <si>
+    <t>爱丽丝</t>
+  </si>
+  <si>
+    <t>阿尔杰农</t>
+  </si>
+  <si>
+    <t>黛芙妮</t>
+  </si>
+  <si>
+    <t>艾德文娜</t>
+  </si>
+  <si>
+    <t>5476,1184901</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3056,1182578</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1756,1181866</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>948,1070089</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>948,1068306</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布莱兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,1,2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>948,1071156</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>948,1068306</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>丝特芬妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900,1081513</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900,1079546</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>格吉尔</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>0,1,2,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>900,1080132</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>亚度尼斯</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>琼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>强尼</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>占卜婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>坎蒂丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>黛芙妮</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>奥蒂莉亚</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希拉</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>夏佐</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>希尔达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5013,1154408</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱丽丝</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>莱特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布拉德利</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>布蓝达</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>帕特里克</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>朵儿洁</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿普敦</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>摩尔根</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>考波特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>马勒第兹</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>爱格伯特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>瓦尔特</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>阿尔杰农</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5170,1156253</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5170,1156284</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5170,1156900</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2270,1167153</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2270,1166370</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2270,1167418</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4918,1147517</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5013,1153081</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5013,1153488</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1856,1071058</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1856,1080475</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3300,1070049</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3056,1166131</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3056,1166294</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2015,1071591</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4765,1139029</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4696,1042715</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2902,1168177</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5476,1162796</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5293,1001490</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1912,1080779</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1912,1080613</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4800,1144907</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>Default</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>纺织婆婆</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5309,1081691</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5309,1159783</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6,0,9,0,9,0,17,30,17,30,19,30,19,30, 22,0,22,0,24,0</t>
-  </si>
-  <si>
-    <t>60001,60002,60003,60004,60005</t>
-  </si>
-  <si>
-    <t>6,0,9,0,9,0,17,30,17,30,19,30,19,30, 22,0,22,0,24,0</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2180,1165443</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>4800,1143244</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10,11,12,3</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>workMap</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>List&lt;int2&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1000,500|1001,500|1002,500|1003,500|1004,500|1005,500|1006,500|1007,500|1008,500|1009,500|1010,500|1011,500</t>
-  </si>
-  <si>
-    <t>workItems</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>homeAreas</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>visitShops</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>List&lt;int&gt;</t>
-  </si>
-  <si>
-    <t>workMapAreas</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>npcFriends</t>
-  </si>
-  <si>
-    <t>List&lt;int2&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>5,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|27,100|30,100|35,100|36,100|39,100|41,100|37,100</t>
-  </si>
-  <si>
-    <t>3,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|27,100|30,100|35,100|36,100|39,100|41,100|7,100|18,100|24,100|16,100|17,100</t>
-  </si>
-  <si>
-    <t>5,100|12,100|14,100|16,100|17,100|21,100|22,100|24,100|36,100|38,100|41,100|40,100|23,100|10,100</t>
-  </si>
-  <si>
-    <t>5,100|3,100|10,100|17,100|12,100|6,100|23,100|25,100|26,100|28,100|29,100|30,100|32,100|35,100|39,100|41,100</t>
-  </si>
-  <si>
-    <t>5,100|3,100|27,100|35,100|39,100|41,100|25,100|29,100</t>
-  </si>
-  <si>
-    <t>3,100|5,100|7,100|10,100|12,100|16,100|17,100|18,100|21,100|22,100|36,100|14,100|38,100|41,100|23,100</t>
-  </si>
-  <si>
-    <t>3,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|27,100|30,100|35,100|5,100|39,100|41,100|7,100|18,100|24,100|16,100|17,100</t>
-  </si>
-  <si>
-    <t>3,100|5,100|7,100|10,100|12,100|16,100|17,100|18,100|21,100|22,100|36,100|38,100|40,100|41,100|23,100</t>
-  </si>
-  <si>
-    <t>12,100|21,100|35,100|41,100|5,100|25,100</t>
-  </si>
-  <si>
-    <t>3,100|5,100|7,100|10,100|12,100|16,100|17,100|18,100|21,100|22,100|36,100|14,100|40,100|41,100|23,100</t>
-  </si>
-  <si>
-    <t>3,100|5,100|6,100|7,100|10,100|9,100|12,100|16,100|17,100|18,100|23,100|27,100|28,100|29,100|30,100|35,100|36,100|37,100|39,100|41,100</t>
-  </si>
-  <si>
-    <t>5,100|12,100|14,100|16,100|17,100|21,100|7,100|24,100|36,100|38,100|41,100|40,100|23,100|10,100</t>
-  </si>
-  <si>
-    <t>12,100|41,100|35,100|21,100|5,100|29,100|3,100|27,100|39,100</t>
-  </si>
-  <si>
-    <t>10,100|12,100|21,100|35,100|41,100|5,100|25,100</t>
-  </si>
-  <si>
-    <t>5,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|27,100|30,100|3,100|36,100|39,100|41,100|37,100</t>
-  </si>
-  <si>
-    <t>5,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|3,100|30,100|35,100|36,100|39,100|41,100|37,100</t>
-  </si>
-  <si>
-    <t>5,100|3,100|10,100|17,100|12,100|6,100|23,100|25,100|26,100|28,100|29,100|9,100|32,100|35,100|39,100|41,100</t>
-  </si>
-  <si>
-    <t>5,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|27,100|30,100|35,100|36,100|3,100|41,100|37,100</t>
-  </si>
-  <si>
-    <t>3,100|9,100|10,100|12,100|21,100|23,100|25,100|26,100|27,100|30,100|35,100|36,100|39,100|5,100|7,100|18,100|24,100|16,100|17,100</t>
-  </si>
-  <si>
-    <t>8,100|9,100|10,100|12,100|14,100|16,100|18,100|19,100|22,100|23,100|26,100|28,100|30,100|34,100|38,100|41,100|40,100</t>
-  </si>
-  <si>
-    <t>3,100|5,100|6,100|7,100|8,100|9,100|10,100|12,100|14,100|16,100|17,100|18,100|19,100|21,100|22,100|23,100|24,100|25,100|26,100|27,100|28,100|29,100|30,100|31,100|34,100|35,100|36,100|37,100|38,100|39,100|40,100|41,100</t>
-  </si>
-  <si>
-    <t>3,100|5,100|6,100|8,100|9,100|10,100|12,100|21,100|23,100|26,100|27,100|28,100|29,100|30,100|34,100|35,100|36,100|37,100|39,100|41,100</t>
-  </si>
-  <si>
-    <t>3,100|5,100|6,100|7,100|9,100|10,100|12,100|16,100|17,100|18,100|19,100|21,100|25,100|26,100|27,100|28,100|29,100|30,100|31,100|34,100|35,100|36,100|37,100|39,100|41,100</t>
-  </si>
-  <si>
-    <t>8,100|9,100|10,100|12,100|14,100|16,100|18,100|19,100|6,100|22,100|23,100|28,100|30,100|34,100|38,100|41,100|40,100</t>
-  </si>
-  <si>
-    <t>3,100|6,100|9,100|12,100|18,100|19,100|21,100|22,100|26,100|27,100|8,100|30,100|29,100|34,100|35,100|39,100|41,100|31,100</t>
-  </si>
-  <si>
-    <t>3,100|6,100|9,100|12,100|18,100|19,100|21,100|22,100|26,100|27,100|28,100|30,100|29,100|34,100|35,100|39,100|41,100|8,100</t>
-  </si>
-  <si>
-    <t>3,100|6,100|9,100|12,100|18,100|19,100|21,100|22,100|26,100|27,100|28,100|30,100|29,100|31,100|35,100|39,100|41,100|8,100</t>
-  </si>
-  <si>
-    <t>3,100|6,100|9,100|12,100|18,100|19,100|21,100|22,100|26,100|27,100|28,100|30,100|29,100|34,100|35,100|39,100|41,100|31,100</t>
-  </si>
-  <si>
-    <t>8,100|9,100|10,100|12,100|14,100|16,100|18,100|19,100|22,100|23,100|28,100|30,100|34,100|38,100|41,100|40,100</t>
-  </si>
-  <si>
-    <t>3,100|5,100|7,100|10,100|12,100|16,100|17,100|18,100|21,100|22,100|36,100|38,100|40,100|41,100|14,100|23,100|30,100|39,100</t>
-  </si>
-  <si>
-    <t>3,100|5,100|7,100|10,100|12,100|16,100|18,100|21,100|22,100|36,100|38,100|40,100|41,100|14,100|23,100|30,100|39,100</t>
-  </si>
-  <si>
-    <t>3,100|5,100|7,100|10,100|12,100|16,100|21,100|22,100|36,100|38,100|40,100|41,100|14,100|23,100|30,100|39,100|17,100</t>
-  </si>
-  <si>
-    <t>likeItem</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>unLikeItem</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>班尼迪克</t>
-  </si>
-  <si>
-    <t>玛德琳</t>
-  </si>
-  <si>
-    <t>布莱兹</t>
-  </si>
-  <si>
-    <t>丝特芬妮</t>
-  </si>
-  <si>
-    <t>格吉尔</t>
-  </si>
-  <si>
-    <t>亚度尼斯</t>
-  </si>
-  <si>
-    <t>琼</t>
-  </si>
-  <si>
-    <t>占卜婆婆</t>
-  </si>
-  <si>
-    <t>奥蒂莉亚</t>
-  </si>
-  <si>
-    <t>坎蒂丝</t>
-  </si>
-  <si>
-    <t>希拉</t>
-  </si>
-  <si>
-    <t>希尔达</t>
-  </si>
-  <si>
-    <t>布拉德利</t>
-  </si>
-  <si>
-    <t>布蓝达</t>
-  </si>
-  <si>
-    <t>希贝儿</t>
-  </si>
-  <si>
-    <t>帕特里克</t>
-  </si>
-  <si>
-    <t>朵儿洁</t>
-  </si>
-  <si>
-    <t>梅林</t>
-  </si>
-  <si>
-    <t>摩尔根</t>
-  </si>
-  <si>
-    <t>马勒第兹</t>
-  </si>
-  <si>
-    <t>考波特</t>
-  </si>
-  <si>
-    <t>夏佐</t>
-  </si>
-  <si>
-    <t>爱格伯特</t>
-  </si>
-  <si>
-    <t>强尼</t>
-  </si>
-  <si>
-    <t>瓦尔特</t>
-  </si>
-  <si>
-    <t>阿普敦</t>
-  </si>
-  <si>
-    <t>艾琳娜</t>
-  </si>
-  <si>
-    <t>莱特</t>
-  </si>
-  <si>
-    <t>爱丽丝</t>
-  </si>
-  <si>
-    <t>阿尔杰农</t>
-  </si>
-  <si>
-    <t>黛芙妮</t>
-  </si>
-  <si>
-    <t>艾德文娜</t>
-  </si>
-  <si>
-    <t>5476,1184901</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3056,1182578</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1756,1181866</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -755,7 +755,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -764,6 +764,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1081,10 +1084,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>0</v>
@@ -1123,7 +1126,7 @@
         <v>20</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="U2" s="2" t="s">
         <v>21</v>
@@ -1143,22 +1146,22 @@
         <v>6</v>
       </c>
       <c r="D3" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G3" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="H3" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>152</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>153</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>1</v>
@@ -1188,10 +1191,10 @@
         <v>28</v>
       </c>
       <c r="S3" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="U3" s="2" t="s">
         <v>29</v>
@@ -1214,7 +1217,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H4" s="3">
         <f>VLOOKUP(B4,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1243,22 +1246,22 @@
         <v>30005</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q4" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R4" s="2" t="s">
         <v>34</v>
       </c>
       <c r="T4" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="U4" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="V4" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.2">
@@ -1300,21 +1303,21 @@
       </c>
       <c r="Q5" s="2"/>
     </row>
-    <row r="6" spans="1:22" ht="57" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
+    <row r="6" spans="1:22" s="3" customFormat="1" ht="57" x14ac:dyDescent="0.2">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
+      <c r="B6" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="1">
+      <c r="C6" s="3">
         <v>948</v>
       </c>
-      <c r="E6" s="1">
+      <c r="E6" s="3">
         <v>948</v>
       </c>
-      <c r="G6" s="1" t="s">
-        <v>112</v>
+      <c r="G6" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="H6" s="3">
         <f>VLOOKUP(B6,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1324,61 +1327,61 @@
         <f>VLOOKUP(B6,Sheet1!$E$2:$G$33,3,FALSE)</f>
         <v>11</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="3">
         <v>30000</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K6" s="3">
         <v>30001</v>
       </c>
-      <c r="L6" s="1">
+      <c r="L6" s="3">
         <v>30002</v>
       </c>
-      <c r="M6" s="1">
+      <c r="M6" s="3">
         <v>30003</v>
       </c>
-      <c r="N6" s="1">
+      <c r="N6" s="3">
         <v>30004</v>
       </c>
-      <c r="O6" s="1">
+      <c r="O6" s="3">
         <v>30005</v>
       </c>
-      <c r="P6" s="1" t="s">
+      <c r="P6" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Q6" s="1" t="s">
+      <c r="Q6" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="R6" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="S6" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="S6" s="2" t="s">
+      <c r="T6" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="U6" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="V6" s="4" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="7" spans="1:22" s="3" customFormat="1" ht="42.75" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="T6" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="U6" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="V6" s="2" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C7" s="1">
+      <c r="C7" s="3">
         <v>948</v>
       </c>
-      <c r="E7" s="1">
+      <c r="E7" s="3">
         <v>948</v>
       </c>
-      <c r="G7" s="1" t="s">
-        <v>112</v>
+      <c r="G7" s="3" t="s">
+        <v>111</v>
       </c>
       <c r="H7" s="3">
         <f>VLOOKUP(B7,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1388,44 +1391,44 @@
         <f>VLOOKUP(B7,Sheet1!$E$2:$G$33,3,FALSE)</f>
         <v>1</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="3">
         <v>30000</v>
       </c>
-      <c r="K7" s="1">
+      <c r="K7" s="3">
         <v>30001</v>
       </c>
-      <c r="L7" s="1">
+      <c r="L7" s="3">
         <v>30002</v>
       </c>
-      <c r="M7" s="1">
+      <c r="M7" s="3">
         <v>30003</v>
       </c>
-      <c r="N7" s="1">
+      <c r="N7" s="3">
         <v>30004</v>
       </c>
-      <c r="O7" s="1">
+      <c r="O7" s="3">
         <v>30005</v>
       </c>
-      <c r="P7" s="1" t="s">
+      <c r="P7" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="Q7" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="R7" s="2" t="s">
+      <c r="Q7" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="R7" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="S7" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="S7" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T7" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="U7" s="2" t="s">
+      <c r="T7" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="U7" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="V7" s="4" t="s">
         <v>104</v>
-      </c>
-      <c r="V7" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="8" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1433,7 +1436,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8" s="1">
         <v>900</v>
@@ -1442,7 +1445,7 @@
         <v>900</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H8" s="3">
         <f>VLOOKUP(B8,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1477,19 +1480,19 @@
         <v>33</v>
       </c>
       <c r="R8" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="S8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="S8" s="2" t="s">
-        <v>46</v>
-      </c>
       <c r="T8" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="U8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V8" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V8" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="9" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1497,7 +1500,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C9" s="1">
         <v>900</v>
@@ -1506,7 +1509,7 @@
         <v>900</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H9" s="3">
         <f>VLOOKUP(B9,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1535,25 +1538,25 @@
         <v>30005</v>
       </c>
       <c r="P9" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q9" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="Q9" s="1" t="s">
+      <c r="R9" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="R9" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="S9" s="2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="T9" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="U9" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V9" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V9" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="10" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1561,7 +1564,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C10" s="1">
         <v>5170</v>
@@ -1573,7 +1576,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H10" s="3">
         <f>VLOOKUP(B10,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1605,19 +1608,19 @@
         <v>35</v>
       </c>
       <c r="Q10" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R10" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="T10" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="U10" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V10" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="11" spans="1:22" ht="85.5" x14ac:dyDescent="0.2">
@@ -1625,7 +1628,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C11" s="1">
         <v>5170</v>
@@ -1637,7 +1640,7 @@
         <v>3115</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H11" s="3">
         <f>VLOOKUP(B11,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1669,22 +1672,22 @@
         <v>35</v>
       </c>
       <c r="Q11" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R11" s="2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="S11" s="2" t="s">
         <v>7</v>
       </c>
       <c r="T11" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="U11" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V11" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V11" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1692,7 +1695,7 @@
         <v>31</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C12" s="1">
         <v>5170</v>
@@ -1704,7 +1707,7 @@
         <v>3115</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H12" s="3">
         <f>VLOOKUP(B12,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1739,19 +1742,19 @@
         <v>33</v>
       </c>
       <c r="R12" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S12" s="2" t="s">
         <v>7</v>
       </c>
       <c r="T12" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="U12" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V12" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V12" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -1759,7 +1762,7 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C13" s="1">
         <v>4800</v>
@@ -1768,7 +1771,7 @@
         <v>4800</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H13" s="3">
         <f>VLOOKUP(B13,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1800,22 +1803,22 @@
         <v>35</v>
       </c>
       <c r="Q13" s="1" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="R13" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="S13" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="T13" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="U13" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V13" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V13" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="14" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1823,7 +1826,7 @@
         <v>14</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="C14" s="1">
         <v>1112</v>
@@ -1832,7 +1835,7 @@
         <v>1014</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H14" s="3">
         <f>VLOOKUP(B14,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1873,13 +1876,13 @@
         <v>15</v>
       </c>
       <c r="T14" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="U14" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V14" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V14" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="15" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -1887,7 +1890,7 @@
         <v>40</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C15" s="1">
         <v>2270</v>
@@ -1896,7 +1899,7 @@
         <v>2180</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H15" s="3">
         <f>VLOOKUP(B15,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1931,19 +1934,19 @@
         <v>37</v>
       </c>
       <c r="R15" s="2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="S15" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T15" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="U15" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V15" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V15" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="16" spans="1:22" ht="57" x14ac:dyDescent="0.2">
@@ -1960,7 +1963,7 @@
         <v>2180</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H16" s="3">
         <f>VLOOKUP(B16,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -1995,19 +1998,19 @@
         <v>33</v>
       </c>
       <c r="R16" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="S16" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T16" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="U16" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V16" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V16" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2015,7 +2018,7 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C17" s="1">
         <v>2270</v>
@@ -2024,7 +2027,7 @@
         <v>2180</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H17" s="3">
         <f>VLOOKUP(B17,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2053,25 +2056,25 @@
         <v>30005</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q17" s="1" t="s">
         <v>33</v>
       </c>
       <c r="R17" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="S17" s="2" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="T17" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="U17" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V17" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V17" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2079,7 +2082,7 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="C18" s="1">
         <v>1112</v>
@@ -2088,7 +2091,7 @@
         <v>1014</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H18" s="3">
         <f>VLOOKUP(B18,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2120,19 +2123,19 @@
         <v>32</v>
       </c>
       <c r="Q18" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R18" s="2" t="s">
         <v>10</v>
       </c>
       <c r="T18" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="U18" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V18" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V18" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -2140,7 +2143,7 @@
         <v>29</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="C19" s="1">
         <v>4918</v>
@@ -2149,7 +2152,7 @@
         <v>0</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H19" s="3">
         <f>VLOOKUP(B19,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2181,19 +2184,19 @@
         <v>35</v>
       </c>
       <c r="Q19" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R19" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="T19" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="U19" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V19" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V19" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2201,7 +2204,7 @@
         <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C20" s="1">
         <v>5013</v>
@@ -2210,7 +2213,7 @@
         <v>5013</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H20" s="3">
         <f>VLOOKUP(B20,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2245,19 +2248,19 @@
         <v>33</v>
       </c>
       <c r="R20" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="S20" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="T20" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="U20" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V20" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V20" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2265,7 +2268,7 @@
         <v>38</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C21" s="1">
         <v>5013</v>
@@ -2274,7 +2277,7 @@
         <v>5013</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H21" s="3">
         <f>VLOOKUP(B21,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2309,19 +2312,19 @@
         <v>33</v>
       </c>
       <c r="R21" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="S21" s="2" t="s">
         <v>11</v>
       </c>
       <c r="T21" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="U21" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V21" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V21" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2329,7 +2332,7 @@
         <v>37</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C22" s="1">
         <v>1856</v>
@@ -2338,7 +2341,7 @@
         <v>1756</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H22" s="3">
         <f>VLOOKUP(B22,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2367,25 +2370,25 @@
         <v>30005</v>
       </c>
       <c r="P22" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q22" s="1" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="R22" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="S22" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="T22" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="U22" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V22" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V22" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="57" x14ac:dyDescent="0.2">
@@ -2393,7 +2396,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C23" s="1">
         <v>1856</v>
@@ -2402,7 +2405,7 @@
         <v>1756</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H23" s="3">
         <f>VLOOKUP(B23,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2437,19 +2440,19 @@
         <v>33</v>
       </c>
       <c r="R23" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="S23" s="2" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="T23" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="U23" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V23" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V23" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="57" x14ac:dyDescent="0.2">
@@ -2457,7 +2460,7 @@
         <v>21</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C24" s="1">
         <v>3300</v>
@@ -2466,7 +2469,7 @@
         <v>3297</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H24" s="3">
         <f>VLOOKUP(B24,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2498,19 +2501,19 @@
         <v>35</v>
       </c>
       <c r="Q24" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R24" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="T24" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="U24" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V24" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V24" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2527,7 +2530,7 @@
         <v>3056</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H25" s="3">
         <f>VLOOKUP(B25,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2562,19 +2565,19 @@
         <v>33</v>
       </c>
       <c r="R25" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="S25" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="T25" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="U25" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V25" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V25" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -2591,7 +2594,7 @@
         <v>3056</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H26" s="3">
         <f>VLOOKUP(B26,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2623,19 +2626,19 @@
         <v>35</v>
       </c>
       <c r="Q26" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R26" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="T26" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="U26" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V26" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V26" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="71.25" x14ac:dyDescent="0.2">
@@ -2643,7 +2646,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C27" s="1">
         <v>2015</v>
@@ -2652,7 +2655,7 @@
         <v>0</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H27" s="3">
         <f>VLOOKUP(B27,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2684,19 +2687,19 @@
         <v>35</v>
       </c>
       <c r="Q27" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R27" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="T27" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="U27" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V27" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V27" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="28.5" x14ac:dyDescent="0.2">
@@ -2704,7 +2707,7 @@
         <v>24</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="C28" s="1">
         <v>4765</v>
@@ -2713,7 +2716,7 @@
         <v>0</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H28" s="3">
         <f>VLOOKUP(B28,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2745,19 +2748,19 @@
         <v>35</v>
       </c>
       <c r="Q28" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R28" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="T28" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="U28" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V28" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V28" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="29" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2765,7 +2768,7 @@
         <v>35</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C29" s="1">
         <v>4696</v>
@@ -2774,7 +2777,7 @@
         <v>0</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H29" s="3">
         <f>VLOOKUP(B29,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2803,22 +2806,22 @@
         <v>30005</v>
       </c>
       <c r="P29" s="1" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="Q29" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R29" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="T29" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="U29" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V29" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V29" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2826,7 +2829,7 @@
         <v>26</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="C30" s="1">
         <v>2902</v>
@@ -2835,7 +2838,7 @@
         <v>0</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H30" s="3">
         <f>VLOOKUP(B30,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2870,19 +2873,19 @@
         <v>33</v>
       </c>
       <c r="R30" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="S30" s="2" t="s">
         <v>14</v>
       </c>
       <c r="T30" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="U30" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V30" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V30" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="31" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2890,7 +2893,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C31" s="1">
         <v>5476</v>
@@ -2902,7 +2905,7 @@
         <v>0</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H31" s="3">
         <f>VLOOKUP(B31,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2934,19 +2937,19 @@
         <v>35</v>
       </c>
       <c r="Q31" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R31" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="T31" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="U31" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V31" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V31" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -2954,7 +2957,7 @@
         <v>27</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C32" s="1">
         <v>5476</v>
@@ -2966,7 +2969,7 @@
         <v>0</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H32" s="3">
         <f>VLOOKUP(B32,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -2998,19 +3001,19 @@
         <v>35</v>
       </c>
       <c r="Q32" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R32" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="T32" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="U32" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V32" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V32" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="33" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -3018,7 +3021,7 @@
         <v>30</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C33" s="1">
         <v>5293</v>
@@ -3027,7 +3030,7 @@
         <v>0</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H33" s="3">
         <f>VLOOKUP(B33,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -3059,19 +3062,19 @@
         <v>35</v>
       </c>
       <c r="Q33" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R33" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="T33" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="U33" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V33" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V33" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -3079,7 +3082,7 @@
         <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C34" s="1">
         <v>1912</v>
@@ -3088,7 +3091,7 @@
         <v>0</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H34" s="3">
         <f>VLOOKUP(B34,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -3117,22 +3120,22 @@
         <v>30005</v>
       </c>
       <c r="P34" s="1" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="Q34" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R34" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="T34" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="U34" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V34" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V34" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="35" spans="1:22" ht="42.75" x14ac:dyDescent="0.2">
@@ -3140,7 +3143,7 @@
         <v>39</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C35" s="1">
         <v>1912</v>
@@ -3149,7 +3152,7 @@
         <v>0</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H35" s="3">
         <f>VLOOKUP(B35,Sheet1!$E$2:$G$33,2,FALSE)</f>
@@ -3181,19 +3184,19 @@
         <v>35</v>
       </c>
       <c r="Q35" s="1" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="R35" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="T35" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="U35" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="V35" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V35" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="36" spans="1:22" ht="57" x14ac:dyDescent="0.2">
@@ -3201,7 +3204,7 @@
         <v>41</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="C36" s="1">
         <v>5309</v>
@@ -3216,7 +3219,7 @@
         <v>539001</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="H36" s="3">
         <v>12</v>
@@ -3249,19 +3252,19 @@
         <v>33</v>
       </c>
       <c r="R36" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="S36" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="S36" s="2" t="s">
+      <c r="T36" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="U36" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="T36" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="U36" s="2" t="s">
+      <c r="V36" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="V36" s="2" t="s">
-        <v>105</v>
       </c>
     </row>
   </sheetData>
@@ -3278,7 +3281,7 @@
   <sheetData>
     <row r="2" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F2">
         <v>13</v>
@@ -3289,7 +3292,7 @@
     </row>
     <row r="3" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F3">
         <v>24</v>
@@ -3300,7 +3303,7 @@
     </row>
     <row r="4" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F4">
         <v>25</v>
@@ -3311,7 +3314,7 @@
     </row>
     <row r="5" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E5" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F5">
         <v>8</v>
@@ -3322,7 +3325,7 @@
     </row>
     <row r="6" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F6">
         <v>4</v>
@@ -3333,7 +3336,7 @@
     </row>
     <row r="7" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E7" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F7">
         <v>10</v>
@@ -3344,7 +3347,7 @@
     </row>
     <row r="8" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E8" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F8">
         <v>23</v>
@@ -3355,7 +3358,7 @@
     </row>
     <row r="9" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F9">
         <v>21</v>
@@ -3366,7 +3369,7 @@
     </row>
     <row r="10" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E10" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F10">
         <v>29</v>
@@ -3377,7 +3380,7 @@
     </row>
     <row r="11" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E11" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F11">
         <v>26</v>
@@ -3388,7 +3391,7 @@
     </row>
     <row r="12" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E12" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F12">
         <v>16</v>
@@ -3399,7 +3402,7 @@
     </row>
     <row r="13" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F13">
         <v>3</v>
@@ -3410,7 +3413,7 @@
     </row>
     <row r="14" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F14">
         <v>28</v>
@@ -3421,7 +3424,7 @@
     </row>
     <row r="15" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E15" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F15">
         <v>19</v>
@@ -3432,7 +3435,7 @@
     </row>
     <row r="16" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E16" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F16">
         <v>20</v>
@@ -3443,7 +3446,7 @@
     </row>
     <row r="17" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E17" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F17">
         <v>16</v>
@@ -3454,7 +3457,7 @@
     </row>
     <row r="18" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E18" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F18">
         <v>5</v>
@@ -3465,7 +3468,7 @@
     </row>
     <row r="19" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E19" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F19">
         <v>17</v>
@@ -3476,7 +3479,7 @@
     </row>
     <row r="20" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E20" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -3487,7 +3490,7 @@
     </row>
     <row r="21" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E21" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F21">
         <v>30</v>
@@ -3498,7 +3501,7 @@
     </row>
     <row r="22" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E22" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F22">
         <v>11</v>
@@ -3509,7 +3512,7 @@
     </row>
     <row r="23" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E23" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F23">
         <v>27</v>
@@ -3520,7 +3523,7 @@
     </row>
     <row r="24" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F24">
         <v>22</v>
@@ -3531,7 +3534,7 @@
     </row>
     <row r="25" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E25" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F25">
         <v>9</v>
@@ -3542,7 +3545,7 @@
     </row>
     <row r="26" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F26">
         <v>6</v>
@@ -3553,7 +3556,7 @@
     </row>
     <row r="27" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E27" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F27">
         <v>18</v>
@@ -3564,7 +3567,7 @@
     </row>
     <row r="28" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E28" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F28">
         <v>2</v>
@@ -3575,7 +3578,7 @@
     </row>
     <row r="29" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E29" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F29">
         <v>14</v>
@@ -3586,7 +3589,7 @@
     </row>
     <row r="30" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E30" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F30">
         <v>26</v>
@@ -3597,7 +3600,7 @@
     </row>
     <row r="31" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E31" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -3608,7 +3611,7 @@
     </row>
     <row r="32" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E32" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F32">
         <v>15</v>
@@ -3619,7 +3622,7 @@
     </row>
     <row r="33" spans="5:7" x14ac:dyDescent="0.2">
       <c r="E33" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F33">
         <v>12</v>
